--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0005.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0005.xlsx
@@ -575,8 +575,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Ripple]: Dodge thành công sẽ hồi một lượng STA nhất định và tăng Crit. DMG thêm 10% trong 5 giây, tối đa 5 lần cộng dồn.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Ripple]: Né tránh thành công sẽ hồi một lượng STA nhất định và tăng Crit. DMG thêm 10% trong 5 giây, tối đa 5 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,10 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Sóng Gợn]: Dodge thành công sẽ phục hồi một lượng STA nhất định và tăng Crit. DMG của Resonators lên 10% trong 5 giây, tối đa 5 lần.
-[Gió Biển]: Khi kẻ địch chịu Sát Thương Erosion Aero, HP tối đa của tất cả Resonators trong đội sẽ tăng 5% trong 10 giây, tối đa 6 lần.
-[Điệu Nhảy Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng cự]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Sóng Gợn]: Né thành công sẽ phục hồi một lượng STA nhất định và tăng Crit. DMG của Resonator lên 10% trong 5 giây, tối đa 5 lần.
+[Gió Biển]: Khi kẻ địch chịu Sát Thương Xói Mòn Aero, HP tối đa của tất cả Resonator trong đội sẽ tăng 5% trong 10 giây, tối đa 6 lần.
+[Điệu Nhảy Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -714,9 +714,9 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.
-[Dòng Ngầm]: Dodge thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
-[Ban Phước]: Sử dụng Intro Skill sẽ tăng 20% Tấn Công và giảm 30% Sát Thương Nhận Vào của người dùng trong 10 giây.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; và &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; cao hơn.
+[Dòng Ngầm]: Né thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
+[Ban Phước]: Sử dụng Kỹ Năng Khởi Động sẽ tăng 20% ATK và giảm 30% Sát Thương Nhận Vào của người dùng trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -784,10 +784,10 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; cao hơn.
-[Dòng Ngầm]: Dodge thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
-[Ban Phước]: Sử dụng Intro Skill sẽ tăng 20% Tấn Công và giảm 30% Sát Thương Nhận Vào của người dùng trong 10 giây.
-[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; và &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; cao hơn.
+[Dòng Ngầm]: Né thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
+[Ban Phước]: Sử dụng Kỹ Năng Khởi Động sẽ tăng 20% ATK và giảm 30% Sát Thương Nhận Vào của người dùng trong 10 giây.
+[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -853,8 +853,8 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Dòng Ngầm]: Dodge thành công sẽ hồi một lượng STA và Concerto Energy nhất định.</t>
+          <t>[Kháng Hiệu Ứng]: This enemy has a higher &lt;color=Wind&gt;Aero RES&lt;/color&gt;.
+[Undercurrent]: A successful Dodge recovers certain STA and Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Aero RES&lt;/color&gt; cao hơn.
-[Dòng Ngầm]: Dodge thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
-[Thủy Triều]: Khi nhận Shield, Resonators được bảo vệ sẽ tăng 30% Tấn Công và giảm 30% Sát Thương Nhận Vào trong 3 giây.
-[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng Hiệu Ứng]: Kẻ địch này có &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; cao hơn.
+[Dòng Ngầm]: Né thành công sẽ hồi một lượng STA và Concerto Energy nhất định.
+[Thủy Triều]: Khi nhận Khiên, Resonator được bảo vệ sẽ tăng 30% ATK và giảm 30% Sát Thương Nhận Vào trong 3 giây.
+[Điệu Vũ Tử Thần]: Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương Nhận Vào cũng sẽ tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Mọi Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -991,8 +991,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[Kháng cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Chiến Đấu Cô Đơn]: Giảm hiệu ứng giảm Độ rung của Intro Skill. Dodge thành công sẽ phục hồi một lượng STA và Concerto Energy nhất định. Dodge Counter sẽ giảm Vibration Strength.</t>
+          <t>[Kháng cự]: This enemy has a higher &lt;color=Fire&gt;Fusion RES&lt;/color&gt;.
+[Lonesome Fight]: Intro Skill's Vibration Strength Reduction is decreased. A successful Dodge recovers certain STA and Concerto Energy. Dodge Counter reduces Vibration Strength.</t>
         </is>
       </c>
     </row>
@@ -1060,10 +1060,10 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Chiến Đấu Cô Đơn]: Hiệu ứng deplete Vibration Strength của Intro Skill bị suy yếu. Dodge thành công sẽ hồi một lượng STA và Concerto Energy nhất định. Phản Đòn sẽ làm giảm Vibration Strength.
-[Vết Thương Chiến]: Khi Resonators chịu sát thương, STA của tất cả Resonators trong đội sẽ giảm 3% mỗi giây, và Hiệu Quả Healing giảm 15% trong 10 giây, tối đa chồng 5 lần.
-[Điệu Nhảy Tử Thần]: Sau 3 phút giao tranh, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn chồng. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.
+[Chiến Đấu Cô Đơn]: Hiệu ứng Giảm Sức Rung của Kỹ Năng Khởi Động bị suy yếu. Né thành công sẽ hồi một lượng STA và Concerto Energy nhất định. Phản Đòn sẽ làm giảm Sức Rung.
+[Vết Thương Chiến]: Khi Resonator chịu DMG, STA của tất cả Resonator trong đội sẽ giảm 3% mỗi giây, và Hiệu Quả Hồi Phục giảm 15% trong 10 giây, tối đa chồng 5 lần.
+[Điệu Nhảy Tử Thần]: Sau 3 phút giao tranh, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. DMG nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn chồng. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1129,8 +1129,8 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Phá Triều]: Giảm hiệu ứng deplete Vibration Strength từ Intro Skill, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của False Sovereign.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; và &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Phá Triều]: Giảm hiệu ứng Giảm Sức Rung từ Kỹ Năng Khởi Động, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của Kẻ Giả Vương.</t>
         </is>
       </c>
     </row>
@@ -1197,9 +1197,9 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Phá Triều]: Giảm hiệu ứng deplete Vibration Strength từ Intro Skill, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của False Sovereign.
-[Điệu Vũ Tử Thần]: Sau 3 phút giao tranh, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; và &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Phá Triều]: Giảm hiệu ứng Giảm Sức Rung từ Kỹ Năng Khởi Động, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của Kẻ Giả Vương.
+[Điệu Vũ Tử Thần]: Sau 3 phút giao tranh, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1267,10 +1267,10 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Phá Triều]: Giảm hiệu ứng deplete Vibration Strength từ Intro Skill, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của False Sovereign.
-[Huyền Thoại Đại Hồng Thủy]: Nếu không bị Phản Đòn gián đoạn, một số đòn tấn công của False Sovereign sẽ để lại [Hạt Giả Triều]. Khi tích lũy đủ 3 hạt, False Sovereign lập tức bước vào trạng thái [Chúa Tể Đại Hồng Thủy], giải phóng [Đại Hồng Thủy] nhấn chìm chiến trường. Khi [Hạt Giả Triều] hoặc [Đại Hồng Thủy] còn tồn tại, hiệu ứng Healing của tất cả Resonators trong đội giảm 50%.
-[Điệu Vũ Tử Thần]: Sau 3 phút giao tranh, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng]: Kẻ địch này có &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt; và &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Phá Triều]: Giảm hiệu ứng Giảm Sức Rung từ Kỹ Năng Khởi Động, nhưng tăng hiệu ứng này cho các Phản Đòn làm gián đoạn đòn tấn công của Kẻ Giả Vương.
+[Huyền Thoại Đại Hồng Thủy]: Nếu không bị Phản Đòn gián đoạn, một số đòn tấn công của Kẻ Giả Vương sẽ để lại [Hạt Giả Triều]. Khi tích lũy đủ 3 hạt, Kẻ Giả Vương lập tức bước vào trạng thái [Chúa Tể Đại Hồng Thủy], giải phóng [Đại Hồng Thủy] nhấn chìm chiến trường. Khi [Hạt Giả Triều] hoặc [Đại Hồng Thủy] còn tồn tại, hiệu ứng Hồi Phục của tất cả Resonator trong đội giảm 50%.
+[Điệu Vũ Tử Thần]: Sau 3 phút giao tranh, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn cộng dồn. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1337,8 +1337,8 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Dreamless] Sau khi thoát khỏi trạng thái Bất Động lần đầu, Dreamless sẽ bước vào trạng thái Looming Turmoil. Trong trạng thái này, Dreamless sẽ phóng ra Halberd of Destruction và Vectors of Ruin có thể đánh chặn, nếu thành công sẽ làm giảm Vibration Strength của Dreamless. Dodge tránh Halberd of Destruction và Vectors of Ruin sẽ không kích hoạt Dodge Thành Công.
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Dreamless] Sau khi thoát khỏi trạng thái Bất Động lần đầu, Dreamless sẽ bước vào trạng thái Looming Turmoil. Trong trạng thái này, Dreamless sẽ phóng ra Halberd of Destruction và Vectors of Ruin có thể đánh chặn, nếu thành công sẽ làm giảm Vibration Strength của Dreamless. Né tránh Halberd of Destruction và Vectors of Ruin sẽ không kích hoạt Né Tránh Thành Công.
 [Endless] Sau khi bước vào Looming Turmoil, Dreamless sẽ thi triển Twilight Eve. Hạ Vibration Strength của Dreamless xuống dưới 50% để ngăn chặn việc thi triển này.</t>
         </is>
       </c>
@@ -1407,10 +1407,10 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Havoc RES&lt;/color&gt; cao hơn.
-[Dreamless] Sau khi thoát khỏi trạng thái Bất Động lần đầu, Dreamless sẽ bước vào trạng thái Looming Turmoil. Trong trạng thái này, Dreamless sẽ phóng ra Halberd of Destruction và Vectors of Ruin có thể đánh chặn, nếu thành công sẽ làm giảm Vibration Strength của Dreamless. Dodge tránh Halberd of Destruction và Vectors of Ruin sẽ không kích hoạt Dodge Thành Công.
+          <t>[Kháng]: Kẻ địch này có &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; cao hơn.
+[Dreamless] Sau khi thoát khỏi trạng thái Bất Động lần đầu, Dreamless sẽ bước vào trạng thái Looming Turmoil. Trong trạng thái này, Dreamless sẽ phóng ra Halberd of Destruction và Vectors of Ruin có thể đánh chặn, nếu thành công sẽ làm giảm Vibration Strength của Dreamless. Né tránh Halberd of Destruction và Vectors of Ruin sẽ không kích hoạt Né Tránh Thành Công.
 [Endless] Sau khi bước vào Looming Turmoil, Dreamless sẽ thi triển Twilight Eve. Hạ Vibration Strength của Dreamless xuống dưới 50% để ngăn chặn việc thi triển này.
-[Death's Dance]: 3 phút sau khi trận chiến bắt đầu, Tấn Công của Resonators sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn số lần cộng dồn. Mọi Resonators trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+[Death's Dance]: 3 phút sau khi trận chiến bắt đầu, ATK của Resonator sẽ tăng 10% mỗi 10 giây, tối đa 100%. Sát Thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn số lần cộng dồn. Mọi Resonator trong đội sẽ mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1477,9 +1477,9 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Fire&gt;Fusion RES&lt;/color&gt; cao hơn.
-[Shift Đỏ]: Khi hồi phục khỏi Trạng Thái Bất Động lần đầu, Reactor Husk bước vào trạng thái Săn Lửa. Trong trạng thái này, Vulnerable Core trên cánh tay trái sẽ không còn lộ ra khi chịu Trạng Thái Tiêu Cực. Khi Vulnerable Core lộ ra, Reactor Husk nhận sát thương tăng thêm. Trạng thái Săn Lửa kết thúc khi Reactor Husk bị Bất Động lần nữa hoặc khi giáp cánh tay trái bị phá hủy.
-[Điệu Nhảy Tử Thần]: Sau 3 phút giao tranh, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn chồng. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng Cự]: Kẻ địch này có &lt;color=Fire&gt;Kháng Fusion&lt;/color&gt; cao hơn.
+[Dịch Chuyển Đỏ]: Khi hồi phục khỏi Trạng Thái Bất Động lần đầu, Reactor Husk bước vào trạng thái Săn Lửa. Trong trạng thái này, Lõi Dễ Tổn Thương trên cánh tay trái sẽ không còn lộ ra khi chịu Trạng Thái Tiêu Cực. Khi Lõi Dễ Tổn Thương lộ ra, Reactor Husk nhận DMG tăng thêm. Trạng thái Săn Lửa kết thúc khi Reactor Husk bị Bất Động lần nữa hoặc khi giáp cánh tay trái bị phá hủy.
+[Điệu Nhảy Tử Thần]: Sau 3 phút giao tranh, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. DMG nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn chồng. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1546,9 +1546,9 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
-[Ảo Giác] Khi một Resonators Dodge thành công, tất cả Resonators trong đội nhận được 1 tầng [Transcendence]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonators chịu sát thương, tất cả Resonators trong đội mất 1 tầng [Transcendence]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
-[Transcendence] Tỷ lệ giảm Vibration Strength của Resonators tăng lên. Hiệu quả hồi phục nhận được tăng 20%.</t>
+          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
+[Ảo Giác] Khi một Resonator né thành công, tất cả Resonator trong đội nhận được 1 tầng [Siêu Việt]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonator chịu sát thương, tất cả Resonator trong đội mất 1 tầng [Siêu Việt]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
+[Siêu Việt] Tỷ lệ giảm Sức Rung của Resonator tăng lên. Hiệu quả hồi phục nhận được tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
-[Ảo Giác] Khi một Resonators Dodge thành công, tất cả Resonators trong đội nhận được 1 tầng [Transcendence]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonators chịu sát thương, tất cả Resonators trong đội mất 1 tầng [Transcendence]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
-[Transcendence] Tỷ lệ giảm Vibration Strength của Resonators tăng lên. Hiệu quả hồi phục nhận được tăng 20%.
-[Chân Thực] Khi một Resonators chịu sát thương, tất cả Resonators trong đội nhận được 1 tầng [Lock Mục Tiêu]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonators Dodge thành công, tất cả Resonators trong đội mất 1 tầng [Lock Mục Tiêu]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
-[Lock Mục Tiêu]: Tỷ lệ giảm Vibration Strength của Resonators bị giảm. Hiệu quả hồi phục nhận được giảm 20%.
-[Điệu Vũ Tử Thần] Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn tầng. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
+[Ảo Giác] Khi một Resonator né thành công, tất cả Resonator trong đội nhận được 1 tầng [Siêu Việt]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonator chịu DMG, tất cả Resonator trong đội mất 1 tầng [Siêu Việt]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
+[Siêu Việt] Tỷ lệ giảm Sức Rung của Resonator tăng lên. Hiệu quả hồi phục nhận được tăng 20%.
+[Chân Thực] Khi một Resonator chịu DMG, tất cả Resonator trong đội nhận được 1 tầng [Khóa Mục Tiêu]. Hiệu ứng này có thể kích hoạt mỗi 5 giây, tối đa 5 tầng. Khi một Resonator né thành công, tất cả Resonator trong đội mất 1 tầng [Khóa Mục Tiêu]. Hiệu ứng này có thể kích hoạt mỗi 5 giây.
+[Khóa Mục Tiêu]: Tỷ lệ giảm Sức Rung của Resonator bị giảm. Hiệu quả hồi phục nhận được giảm 20%.
+[Điệu Vũ Tử Thần] Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. DMG nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn tầng. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1691,10 +1691,10 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
+          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
 [Về Nhà] Khi Sigillum sắp bị đánh bại, nó trở nên bất tử, hồi phục toàn bộ HP trong 3 giây và nhận hiệu ứng Giấc Mơ Về Nhà.
 [Giấc Mơ Về Nhà] HP tối đa của Sigillum tăng mạnh.
-[Paradox] Sử dụng Kỹ Năng Echo của Sigillum có thể làm gián đoạn hiệu ứng Trì Trệ của nó.</t>
+[Nghịch Lý] Sử dụng Kỹ Năng Echo của Sigillum có thể làm gián đoạn hiệu ứng Trì Trệ của nó.</t>
         </is>
       </c>
     </row>
@@ -1765,13 +1765,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Spectro RES&lt;/color&gt; cao hơn.
+          <t>[Kháng cự] Kẻ địch này có &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; cao hơn.
 [Về Nhà] Khi Sigillum sắp bị đánh bại, nó trở nên bất tử, hồi phục toàn bộ HP trong 3 giây và nhận hiệu ứng Giấc Mơ Về Nhà.
 [Giấc Mơ Về Nhà] HP tối đa của Sigillum tăng mạnh.
-[Paradox] Sử dụng Kỹ Năng Echo của Sigillum có thể làm gián đoạn hiệu ứng Trì Trệ của nó.
-[Lạc Lối] Khi đòn tấn công của Sigillum bị phản đòn, Resonators trong đội nhận được 1 tầng Thức Tỉnh, tối đa 3 tầng. Mỗi lần Resonators chịu sát thương, họ mất 1 tầng Thức Tỉnh. Có thể kích hoạt mỗi 5 giây.
-[Thức Tỉnh] Resonators nhận thêm 10% Sát Thương và giảm 10% sát thương nhận vào.
-[Điệu Vũ Tử Thần] Sau 3 phút kể từ khi trận chiến bắt đầu, Tấn Công của Resonators tăng 10% mỗi 10 giây, tối đa 100%. Sát thương nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn tầng. Tất cả Resonators trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
+[Nghịch Lý] Sử dụng Kỹ Năng Echo của Sigillum có thể làm gián đoạn hiệu ứng Trì Trệ của nó.
+[Lạc Lối] Khi đòn tấn công của Sigillum bị phản đòn, các Resonator trong đội nhận được 1 tầng Thức Tỉnh, tối đa 3 tầng. Mỗi lần Resonator chịu DMG, họ mất 1 tầng Thức Tỉnh. Có thể kích hoạt mỗi 5 giây.
+[Thức Tỉnh] Resonator nhận thêm 10% Sát Thương và giảm 10% DMG nhận vào.
+[Điệu Vũ Tử Thần] Sau 3 phút kể từ khi trận chiến bắt đầu, ATK của Resonator tăng 10% mỗi 10 giây, tối đa 100%. DMG nhận vào cũng tăng 10% mỗi 10 giây, không giới hạn tầng. Tất cả Resonator trong đội mất 10% HP tối đa mỗi 2 giây, cho đến khi HP còn dưới 20%.</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Panhua bảo cô ấy có bí quyết làm Nước Lẩu Cay: 2 Dầu, 2 Ớt, 1 Muối và 1 Fowl Meat để tăng hương vị.</t>
+          <t>Panhua bảo cô ấy có bí quyết làm Nước Lẩu Cay: 2 Dầu, 2 Ớt, 1 Muối và 1 Thịt Gia Cầm để tăng hương vị.</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Panhua bảo cô ấy có bí quyết làm Nước Lẩu Cay: 2 Dầu, 2 Ớt, 1 Muối và 1 Fowl Meat để tăng hương vị.</t>
+          <t>Panhua bảo cô ấy có bí quyết làm Nước Lẩu Cay: 2 Dầu, 2 Ớt, 1 Muối và 1 Thịt Gia Cầm để tăng hương vị.</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trong giai đoạn hiện tại, mỗi cấp độ tăng Tấn Công và HP Tối Đa thêm 0.8% và Phòng Ngự thêm 0.25%.</t>
+          <t>Trong giai đoạn hiện tại, mỗi cấp độ tăng ATK và HP Tối Đa thêm 0.8% và Phòng Ngự thêm 0.25%.</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>["Tự Do"] Flight không còn tốn STA nữa.</t>
+          <t>["Tự Do"] Bay không còn tốn STA nữa.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Vòng Hào Quang: Battle Engagement Points có thể tăng thêm tối đa 200 cấp Glory.</t>
+          <t>Vòng Hào Quang: Điểm Tham Chiến có thể tăng thêm tối đa 200 cấp Vinh Quang.</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>[Đập Tan]: Sát thương gây ra lên mục tiêu Class Common và Class Elite được Khuếch Đại 100%.</t>
+          <t>[Đập Tan]: Sát thương gây ra lên mục tiêu Hạng Thường và Hạng Tinh Anh được Khuếch Đại 100%.</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Dodge Counter sẽ giảm Vibration Strength của mục tiêu đi 5%. Đánh trúng mục tiêu bằng Phản Công sẽ giảm Vibration Strength của mục tiêu đi 12,5%. Cả hai hiệu ứng chỉ kích hoạt một lần mỗi 3 giây.</t>
+          <t>Đánh trúng mục tiêu bằng Dodge Counter Tránh sẽ giảm Sức Rung của mục tiêu đi 5%. Đánh trúng mục tiêu bằng Phản Công sẽ giảm Sức Rung của mục tiêu đi 12,5%. Cả hai hiệu ứng chỉ kích hoạt một lần mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội nhận thêm 1000% Hiệu Quả Healing. Khi Cấp Độ Glory từ Điểm Tham Chiến không dưới 100, HP của Resonators sẽ giảm xuống còn 1 thay vì bị đánh bại khi nhận đòn chí mạng, kích hoạt mỗi 30 giây một lần.</t>
+          <t>Tất cả Resonator trong đội nhận thêm 1000% Hiệu Quả Hồi Phục. Khi Cấp Độ Vinh Quang từ Điểm Tham Chiến không dưới 100, HP của Resonator sẽ giảm xuống còn 1 thay vì bị đánh bại khi nhận đòn chí mạng, kích hoạt mỗi 30 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Concerto Energy phục hồi 10 điểm mỗi giây khi không chiến đấu.</t>
+          <t>Năng lượng Concerto phục hồi 10 điểm mỗi giây khi không chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Dodge Counter trúng mục tiêu sẽ gây Sát Thương Physical bằng 1% HP tối đa của mục tiêu. Phản Đòn trúng mục tiêu sẽ gây Sát Thương Physical bằng 5% HP tối đa của mục tiêu. Cả hai hiệu ứng đều có thể kích hoạt mỗi 3 giây một lần.</t>
+          <t>Dodge Counter trúng mục tiêu sẽ gây Sát Thương Vật Lý bằng 1% HP tối đa của mục tiêu. Phản Đòn trúng mục tiêu sẽ gây Sát Thương Vật Lý bằng 5% HP tối đa của mục tiêu. Cả hai hiệu ứng đều có thể kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cooldown kỹ năng Cộng hưởng giảm 50%.</t>
+          <t>Thời gian hồi kỹ năng Cộng hưởng giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cooldown chiêu Resonance Liberation giảm 50%.</t>
+          <t>Thời gian hồi chiêu Resonance Liberation giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Intro Skill sẽ hồi 25 Concerto Energy, kích hoạt một lần mỗi 20 giây.</t>
+          <t>Đánh trúng mục tiêu bằng Kỹ Năng Khởi Động sẽ hồi 25 Concerto Energy, kích hoạt một lần mỗi 20 giây.</t>
         </is>
       </c>
     </row>
@@ -3009,10 +3009,10 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi ở trạng thái Synergy Burst:
-- Basic Attack hoặc Heavy Attack tiếp theo trúng mục tiêu, hoặc Dodge thành công kích hoạt Consecutive Punches, liên tục tấn công mục tiêu phía trước, gây Physical DMG bằng {1} ATK {0} times, được tính là Basic Attack DMG.
-- Khi trúng mục tiêu bằng Basic Attack hoặc Heavy Attack hoặc thực hiện Dodge thành công, nhận thêm &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=tầng P=tầng SapTag=2} Invisibility.</t>
+          <t>Kích hoạt khi đội hình có 3 thành viên Liên Kết
+Khi ở trạng thái Đồng Bộ Bùng Nổ:
+- Đòn Basic Attack hoặc Heavy Attack tiếp theo trúng đích, hoặc né thành công sẽ kích hoạt Liên Tiếp Cú Đấm, liên tục đánh vào mục tiêu phía trước, gây DMG Vật Lý bằng {1} ATK {0} lần, được tính là DMG Basic Attack.
+- Khi đánh trúng mục tiêu bằng Basic Attack hoặc Heavy Attack, hoặc né thành công, nhận thêm &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; lớp Ẩn Mình.</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, tổng Sát Thương của Đòn Liên Tiếp và Siết Chặt được tăng thêm {0}.</t>
         </is>
       </c>
@@ -3145,8 +3145,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
-Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, nhận tất cả hiệu ứng của Thế Đứng Chủ Nhân, và Hệ Số Sát Thương của Thế Đứng Chủ Nhân tăng từ {0} lên {1} Tấn Công.</t>
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
+Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, nhận tất cả hiệu ứng của Thế Đứng Chủ Nhân, và Hệ Số Sát Thương của Thế Đứng Chủ Nhân tăng từ {0} lên {1} ATK.</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Activated upon having 3 Bond Members in the team&lt;/color&gt;
+          <t>&lt;color=Highlight&gt;Kích hoạt khi có 3 thành viên Liên Kết trong đội&lt;/color&gt;
 Khi trong trạng thái Cơn Bùng Nổ Đồng Điệu, Sát Thương từ Thế Đứng Chủ Nhân sẽ bỏ qua {0} Phòng Ngự của mục tiêu.</t>
         </is>
       </c>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Tất cả Vũ Khí +11% Tấn Công</t>
+          <t>Tất cả Vũ Khí +11% ATK</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tất cả Vũ Khí +13,5% Tấn Công</t>
+          <t>Tất cả Vũ Khí +13,5% ATK</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Tất cả Vũ Khí +18% Tấn Công</t>
+          <t>Tất cả Vũ Khí +18% ATK</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Giảm DMG +9%</t>
+          <t>Giảm Sát Thương +9%</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Giảm DMG +10.5%</t>
+          <t>Giảm Sát Thương +10,5%</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Giảm DMG +12%</t>
+          <t>Giảm Sát Thương +12%</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Thể lực tối đa và Recovery +18%</t>
+          <t>STA tối đa và Hồi phục +18%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Thể lực tối đa và Recovery +22,5%</t>
+          <t>STA tối đa và Hồi phục +22,5%</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Thể lực tối đa và Recovery +30%</t>
+          <t>STA tối đa và Hồi phục +30%</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khi nhặt Mô-đun Tăng Cường, sát thương gây ra sẽ tăng vĩnh viễn thêm 0.02%.</t>
+          <t>Khi nhặt Mô-đun Tăng Cường, DMG gây ra sẽ tăng vĩnh viễn thêm 0.02%.</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>HP tối đa tăng 100%, nhưng Resonator chịu thêm 50% sát thương.</t>
+          <t>HP tối đa tăng 100%, nhưng Resonator chịu thêm 50% DMG.</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ở đợt sóng tiếp theo, tăng mạnh Sát Thương, Movement Speed và Attack Speed trong 10 giây.</t>
+          <t>Ở đợt sóng tiếp theo, tăng mạnh Sát Thương, Tốc Độ Di Chuyển và Tốc Độ Tấn Công trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Hệ Số DMG +12.5%</t>
+          <t>Hệ Số Sát Thương +12.5%</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Hệ Số DMG +15%</t>
+          <t>Hệ Số Sát Thương +15%</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Hệ Số DMG +19%</t>
+          <t>Hệ Số Sát Thương +19%</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Hệ Số DMG +25%</t>
+          <t>Hệ Số Sát Thương +25%</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Xuyên DEF +15%</t>
+          <t>Xuyên Phòng Ngự +15%</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Xuyên DEF +18%</t>
+          <t>Xuyên Phòng Ngự +18%</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Xuyên DEF +22.5%</t>
+          <t>Xuyên Phòng Ngự +22.5%</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Xuyên DEF +30%</t>
+          <t>Xuyên Phòng Ngự +30%</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Movement Speed của Resonator tăng 16%. Tấn công kẻ địch tăng Sát Thương Vũ Khí thêm 2.5% trong 6 giây, tối đa 15 lần.</t>
+          <t>Tốc Độ Di Chuyển của Resonator tăng 16%. Tấn công kẻ địch tăng Sát Thương Vũ Khí thêm 2.5% trong 6 giây, tối đa 15 lần.</t>
         </is>
       </c>
     </row>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Mỗi khi Movement Speed của Resonator tăng 1%, Vũ Khí gây thêm 1,5% Sát Thương.</t>
+          <t>Mỗi khi Tốc Độ Di Chuyển của Resonator tăng 1%, Vũ Khí gây thêm 1,5% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Attack Speed của vũ khí tăng 1% mỗi 2 giây, tối đa 50 lần cộng dồn. Toàn bộ cộng dồn sẽ mất khi Resonator chịu sát thương.</t>
+          <t>Tốc Độ Tấn Công của vũ khí tăng 1% mỗi 2 giây, tối đa 50 lần cộng dồn. Toàn bộ cộng dồn sẽ mất khi Resonator chịu sát thương.</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Movement Speed của Resonator tăng 20%. Khi Vũ Khí tấn công ít nhất 10 kẻ địch cùng lúc, mỗi 1% Movement Speed cộng thêm sẽ tăng 1% Crit. DMG Vũ Khí trong 5 giây.</t>
+          <t>Tốc Độ Di Chuyển của Resonator tăng 20%. Khi Vũ Khí tấn công ít nhất 10 kẻ địch cùng lúc, mỗi 1% Tốc Độ Di Chuyển cộng thêm sẽ tăng 1% Crit. DMG Vũ Khí trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Khi trúng địch, Vũ Khí gây thêm sát thương vùng bằng 10% Tấn Công lên kẻ địch xung quanh mục tiêu trúng đòn.</t>
+          <t>Khi trúng địch, Vũ Khí gây thêm sát thương vùng bằng 10% ATK lên kẻ địch xung quanh mục tiêu trúng đòn.</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Gây sát thương làm tăng Crit. DMG của Vũ Khí thêm 0,6% trong 6 giây, có thể chồng chất lên đến 60 lần.</t>
+          <t>Gây DMG làm tăng Crit. DMG của Vũ Khí thêm 0,6% trong 6 giây, có thể chồng chất lên đến 60 lần.</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Gây ra đòn bạo kích sẽ tăng Sát Thương Critical Hit và Attack Speed của vũ khí lên 1% trong 10 giây, tối đa 20 lần cộng dồn.</t>
+          <t>Gây ra đòn bạo kích sẽ tăng Crit. DMG và Tốc Độ Tấn Công của vũ khí lên 1% trong 10 giây, tối đa 20 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Đánh trúng kẻ địch 50 lần sẽ tăng Attack Speed của Vũ Khí thêm 50% trong 8 giây.</t>
+          <t>Đánh trúng kẻ địch 50 lần sẽ tăng Tốc Độ Tấn Công của Vũ Khí thêm 50% trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tấn công kẻ địch Common Class có 20% cơ hội tiêu diệt ngay lập tức. Tấn công kẻ địch Class Elite hoặc Class Thống Soái có 20% cơ hội gây sát thương bằng 25% Tấn Công của vũ khí.</t>
+          <t>ATK kẻ địch Hạng Thường có 20% cơ hội tiêu diệt ngay lập tức. ATK kẻ địch Hạng Tinh Anh hoặc Hạng Thống Soái có 20% cơ hội gây DMG bằng 25% ATK của vũ khí.</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Weapon gây thêm 35% Sát Thương lên kẻ địch ở xa.</t>
+          <t>Vũ khí gây thêm 35% Sát Thương lên kẻ địch ở xa.</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Weapon bỏ qua 45% Phòng Ngự của kẻ địch đang bị làm chậm.</t>
+          <t>Vũ khí bỏ qua 45% Phòng Ngự của kẻ địch đang bị làm chậm.</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Gây sát thương khiến kẻ địch chậm lại 30% trong 3 giây. Crit. Rate và Crit. DMG của tất cả vũ khí tăng 20% khi tấn công kẻ địch bị làm chậm.</t>
+          <t>Gây DMG khiến kẻ địch chậm lại 30% trong 3 giây. Crit. Rate và Crit. DMG của tất cả vũ khí tăng 20% khi tấn công kẻ địch bị làm chậm.</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Weapon làm giảm 60% Movement Speed của kẻ địch bị trúng đòn trong 1.5 giây.</t>
+          <t>Vũ khí làm giảm 60% Tốc Độ Di Chuyển của kẻ địch bị trúng đòn trong 1.5 giây.</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Gây sát thương làm tăng Sát Thương nhận vào của kẻ địch thêm 2,5% và giảm Sát Thương chúng gây ra đi 4% trong 6 giây, có thể chồng chất lên đến 10 lần.</t>
+          <t>Gây DMG làm tăng Sát Thương nhận vào của kẻ địch thêm 2,5% và giảm Sát Thương chúng gây ra đi 4% trong 6 giây, có thể chồng chất lên đến 10 lần.</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Movement Speed của Resonator tăng 20%. Gây sát thương tăng Crit. Rate Vũ Khí thêm 2.5%, tối đa 20 lần. Mọi cộng dồn sẽ mất khi Resonator chịu sát thương.</t>
+          <t>Tốc Độ Di Chuyển của Resonator tăng 20%. Gây sát thương tăng Crit. Rate Vũ Khí thêm 2.5%, tối đa 20 lần. Mọi cộng dồn sẽ mất khi Resonator chịu sát thương.</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Mỗi điểm HP tối đa của Resonator sẽ tăng 0,35% Tấn Công cho Vũ Khí.</t>
+          <t>Mỗi điểm HP tối đa của Resonator sẽ tăng 0,35% ATK cho Vũ Khí.</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Gây sát thương làm tăng Sát Thương của Vũ Khí và HP tối đa của Resonator thêm 1% trong 6 giây, có thể chồng chất lên đến 25 lần.</t>
+          <t>Gây DMG làm tăng Sát Thương của Vũ Khí và HP tối đa của Resonator thêm 1% trong 6 giây, có thể chồng chất lên đến 25 lần.</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Khi nhặt Enhancement Mô-đun, sát thương của Vũ Khí tăng vĩnh viễn 0.1%.</t>
+          <t>Khi nhặt Enhancement Module, DMG của Vũ Khí tăng vĩnh viễn 0.1%.</t>
         </is>
       </c>
     </row>
@@ -8415,9 +8415,9 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Off-Tune Level&lt;/color&gt; của mục tiêu đạt tối đa, mục tiêu sẽ rơi vào trạng thái &lt;color=Highlight&gt;Mistune&lt;/color&gt;:
-Resonators đang hoạt động trong đội có thể thực hiện &lt;color=Highlight&gt;Tune Break Skill&lt;/color&gt; lên mục tiêu, gây sát thương và khiến mục tiêu thoát khỏi trạng thái &lt;color=Highlight&gt;Mistune&lt;/color&gt;.
-Nếu mục tiêu thuộc Class Phổ Thông, Resonators trong đội có thể trực tiếp gây &lt;color=Highlight&gt;Tune Break DMG&lt;/color&gt; bằng một số kỹ năng thông thường khi tấn công. Mục tiêu sẽ thoát khỏi trạng thái &lt;color=Highlight&gt;Mistune&lt;/color&gt; sau đó.</t>
+          <t>Khi &lt;color=Highlight&gt;Mức Lệch Tần&lt;/color&gt; của mục tiêu đạt tối đa, mục tiêu sẽ rơi vào trạng thái &lt;color=Highlight&gt;Lệch Tần&lt;/color&gt;:
+Resonator đang hoạt động trong đội có thể thực hiện &lt;color=Highlight&gt;Kỹ Năng Phá Tần&lt;/color&gt; lên mục tiêu, gây DMG và khiến mục tiêu thoát khỏi trạng thái &lt;color=Highlight&gt;Lệch Tần&lt;/color&gt;.
+Nếu mục tiêu thuộc Hạng Phổ Thông, Resonator trong đội có thể trực tiếp gây &lt;color=Highlight&gt;Sát Thương Phá Tần&lt;/color&gt; bằng một số kỹ năng thông thường khi tấn công. Mục tiêu sẽ thoát khỏi trạng thái &lt;color=Highlight&gt;Lệch Tần&lt;/color&gt; sau đó.</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Một số Resonators có thể gây &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt; lên mục tiêu. Trong trạng thái này, nếu mục tiêu bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt; sẽ bị thay thế bằng &lt;color=Highlight&gt;Tune Rupture - Interfered&lt;/color&gt;.</t>
+          <t>Một số Resonator có thể gây &lt;color=Highlight&gt;Đứt Giai Điệu - Dịch Chuyển&lt;/color&gt; lên mục tiêu. Trong trạng thái này, nếu mục tiêu bị trúng &lt;color=Highlight&gt;Phá Giai Điệu&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Đứt Giai Điệu - Dịch Chuyển&lt;/color&gt; sẽ bị thay thế bằng &lt;color=Highlight&gt;Đứt Giai Điệu - Nhiễu Loạn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Một số Resonators có thể gây &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt; lên mục tiêu. Trong trạng thái này, nếu mục tiêu bị trúng &lt;color=Highlight&gt;Tune Break&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt; sẽ bị thay thế bằng &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt;.</t>
+          <t>Một số Resonator có thể gây &lt;color=Highlight&gt;Căng Giai Điệu - Dịch Chuyển&lt;/color&gt; lên mục tiêu. Trong trạng thái này, nếu mục tiêu bị trúng &lt;color=Highlight&gt;Phá Giai Điệu&lt;/color&gt;, trạng thái &lt;color=Highlight&gt;Căng Giai Điệu - Dịch Chuyển&lt;/color&gt; sẽ bị thay thế bằng &lt;color=Highlight&gt;Căng Giai Điệu - Nhiễu Loạn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Mục tiêu sẽ rơi vào trạng thái này khi bị &lt;color=Highlight&gt;Tune Break&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt;. Resonators có thể phản ứng với &lt;color=Highlight&gt;Tune Rupture- Interfered&lt;/color&gt; sẽ gây thêm hiệu ứng khi tấn công mục tiêu trong trạng thái này. &lt;color=Highlight&gt;Tune Rupture- Interfered&lt;/color&gt; kéo dài trong 8 giây.</t>
+          <t>Mục tiêu sẽ rơi vào trạng thái này khi bị &lt;color=Highlight&gt;Đoạn Tần Phá&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Đứt Tần - Dịch Chuyển&lt;/color&gt;. Resonator có thể phản ứng với &lt;color=Highlight&gt;Đứt Tần - Giao Thoa&lt;/color&gt; sẽ gây thêm hiệu ứng khi tấn công mục tiêu trong trạng thái này. &lt;color=Highlight&gt;Đứt Tần - Giao Thoa&lt;/color&gt; kéo dài trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Mục tiêu sẽ rơi vào trạng thái này khi bị &lt;color=Highlight&gt;Tune Break&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt;. Resonators có thể phản ứng với &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; sẽ gây thêm hiệu ứng khi tấn công mục tiêu trong trạng thái này. &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; kéo dài trong 30 giây.</t>
+          <t>Mục tiêu sẽ rơi vào trạng thái này khi bị &lt;color=Highlight&gt;Đoạn Tần Phá&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Căng Tần - Dịch Chuyển&lt;/color&gt;. Resonator có thể phản ứng với &lt;color=Highlight&gt;Căng Tần - Giao Thoa&lt;/color&gt; sẽ gây thêm hiệu ứng khi tấn công mục tiêu trong trạng thái này. &lt;color=Highlight&gt;Căng Tần - Giao Thoa&lt;/color&gt; kéo dài trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -8745,10 +8745,10 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Galbrena có thể giữ tối đa {0} điểm &lt;color=Highlight&gt;Afterflame&lt;/color&gt;.
-Trong &lt;color=Highlight&gt;Threshold State&lt;/color&gt;, Galbrena hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} &lt;color=Highlight&gt;Afterflame&lt;/color&gt; khi Resonators trong đội sử dụng Skills Echoes gần đó. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Hiệu ứng này sẽ được đặt lại khi Galbrena thoát khỏi &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.
-Trong thời gian &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; diễn ra, mỗi điểm &lt;color=Highlight&gt;Afterflame&lt;/color&gt; sẽ tăng sát thương gây ra bởi &lt;color=Highlight&gt;Basic Attack - Seraphic Execution&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Hellsent Barrage&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Ravage&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter - Purgatory Scourge&lt;/color&gt; thêm {2}, tối đa {3}. Hiệu ứng này sẽ bị loại bỏ khi thoát khỏi &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.
-Toàn bộ &lt;color=Highlight&gt;Afterflame&lt;/color&gt; sẽ bị xóa khi Galbrena thoát khỏi &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.</t>
+          <t>Galbrena có thể giữ tối đa {0} điểm &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt;.
+Trong &lt;color=Highlight&gt;Trạng Thái Ngưỡng&lt;/color&gt;, Galbrena hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=1} &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt; khi Resonator trong đội sử dụng Kỹ Năng Echo gần đó. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Hiệu ứng này sẽ được đặt lại khi Galbrena thoát khỏi &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.
+Trong thời gian &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt; diễn ra, mỗi điểm &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt; sẽ tăng DMG gây ra bởi &lt;color=Highlight&gt;Đòn Basic Attack - Thiên Thần Trảm&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Tấn Công Mạnh - Phán Quyết Cánh Lửa&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Mid-air Attack - Bão Hỏa Ngục&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Tàn Phá&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter Tránh - Quét Luyện Ngục&lt;/color&gt; thêm {2}, tối đa {3}. Hiệu ứng này sẽ bị loại bỏ khi thoát khỏi &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.
+Toàn bộ &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt; sẽ bị xóa khi Galbrena thoát khỏi &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8816,10 +8816,10 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Galbrena có thể chứa tối đa {0} điểm &lt;color=Highlight&gt;Sinflame&lt;/color&gt;.
-Trong trạng thái &lt;color=Highlight&gt;Threshold State&lt;/color&gt;, các đòn Basic Attack, Heavy Attack - Bão Tử Thần, Mid-air Attack - Mưa Tro Tàn, Resonance Skill - Xâm Lấn và Intro Skill - Bộc Phát Hỏa Ngục sẽ hồi phục &lt;color=Highlight&gt;Sinflame&lt;/color&gt; khi trúng mục tiêu.
-Khi &lt;color=Highlight&gt;Sinflame&lt;/color&gt; đạt {1} điểm, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill - Ascent of Malice&lt;/color&gt;.
-Khi sử dụng &lt;color=Highlight&gt;Resonance Skill - Ascent of Malice&lt;/color&gt;, &lt;color=Highlight&gt;Sinflame&lt;/color&gt; sẽ được chuyển hóa thành lượng &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; tương đương.</t>
+          <t>Galbrena có thể chứa tối đa {0} điểm &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt;.
+Trong trạng thái &lt;color=Highlight&gt;Ngưỡng Giới&lt;/color&gt;, các đòn Basic Attack, Heavy Attack - Bão Tử Thần, Mid-air Attack - Mưa Tro Tàn, Resonance Skill - Xâm Lấn và Kỹ Năng Khởi Động - Bộc Phát Hỏa Ngục sẽ hồi phục &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; khi trúng mục tiêu.
+Khi &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; đạt {1} điểm, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt;.
+Khi sử dụng &lt;color=Highlight&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt;, &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; sẽ được chuyển hóa thành lượng &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; tương đương.</t>
         </is>
       </c>
     </row>
@@ -8886,9 +8886,9 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Galbrena có thể chứa tối đa {0} điểm &lt;color=Highlight&gt;Purging Flame&lt;/color&gt;.
-Khi sử dụng &lt;color=Highlight&gt;Resonance Skill - Ascent of Malice&lt;/color&gt;, &lt;color=Highlight&gt;Sinflame&lt;/color&gt; sẽ được chuyển hóa thành lượng &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; tương đương.
-Trong thời gian &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; tồn tại, các đòn Basic Attack - Thiên Sứ Trảm, Heavy Attack - Phán Quyết Cánh Lửa, Mid-air Attack - Bão Hỏa Địa Ngục, Dodge Counter - Quét Luyện Ngục và Resonance Skill - Tàn Phá sẽ tiêu hao &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Galbrena có thể chứa tối đa {0} điểm &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt;.
+Khi sử dụng &lt;color=Highlight&gt;Resonance Skill - Thăng Hoa Ác Ý&lt;/color&gt;, &lt;color=Highlight&gt;Lửa Tội&lt;/color&gt; sẽ được chuyển hóa thành lượng &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; tương đương.
+Trong thời gian &lt;color=Highlight&gt;Hóa Thân Ác Quỷ&lt;/color&gt; tồn tại, các đòn Basic Attack - Thiên Sứ Trảm, Heavy Attack - Phán Quyết Cánh Lửa, Mid-air Attack - Bão Hỏa Địa Ngục, Dodge Counter Tránh - Quét Luyện Ngục và Resonance Skill - Tàn Phá sẽ tiêu hao &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Mặc định, Galbrena ở trạng thái &lt;color=Highlight&gt;Threshold State&lt;/color&gt;, và trong trạng thái này, cô ấy tích lũy &lt;color=Highlight&gt;Afterflame&lt;/color&gt; và &lt;color=Highlight&gt;Sinflame&lt;/color&gt;.</t>
+          <t>Mặc định, Galbrena ở trạng thái &lt;color=Highlight&gt;Ngưỡng&lt;/color&gt;, và trong trạng thái này, cô ấy tích lũy &lt;color=Highlight&gt;Dư Lửa&lt;/color&gt; và &lt;color=Highlight&gt;Tội Lửa&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9020,9 +9020,9 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Skill - Ascent of Malice&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;.
-Trong &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;, Kỹ Năng Basic, Kỹ Năng Nặng - Loạt Tử Thần, Kỹ Năng Trên Không - Mưa Tro Tàn, Dodge Counter - Máu Đổi Máu và Resonance Skill - Xâm Lấn của Galbrena sẽ được thay thế bằng Kỹ Năng Basic - Hành Quyết Thiên Thần, Kỹ Năng Nặng - Phán Quyết Cánh Lửa, Kỹ Năng Trên Không - Loạn Đạn Địa Ngục, Dodge Counter - Quét Luyện Ngục và Resonance Skill - Tàn Phá, tiêu hao &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; khi trúng đích.
-&lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; sẽ kết thúc khi &lt;color=Highlight&gt;Purging Flame&lt;/color&gt; cạn kiệt hoặc khi Galbrena ở trong &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; quá 50 giây.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Resonance Skill - Thăng Hoa Của Ác Ý&lt;/color&gt; sẽ đưa Galbrena vào trạng thái &lt;color=Highlight&gt;Thể Dị Hóa Quỷ&lt;/color&gt;.
+Trong &lt;color=Highlight&gt;Thể Dị Hóa Quỷ&lt;/color&gt;, Kỹ Năng Cơ Bản, Kỹ Năng Nặng - Loạt Tử Thần, Kỹ Năng Trên Không - Mưa Tro Tàn, Dodge Counter Tránh - Máu Đổi Máu và Resonance Skill - Xâm Lấn của Galbrena sẽ được thay thế bằng Kỹ Năng Cơ Bản - Hành Quyết Thiên Thần, Kỹ Năng Nặng - Phán Quyết Cánh Lửa, Kỹ Năng Trên Không - Loạn Đạn Địa Ngục, Dodge Counter Tránh - Quét Luyện Ngục và Resonance Skill - Tàn Phá, tiêu hao &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; khi trúng đích.
+&lt;color=Highlight&gt;Thể Dị Hóa Quỷ&lt;/color&gt; sẽ kết thúc khi &lt;color=Highlight&gt;Lửa Thanh Tẩy&lt;/color&gt; cạn kiệt hoặc khi Galbrena ở trong &lt;color=Highlight&gt;Thể Dị Hóa Quỷ&lt;/color&gt; quá 50 giây.</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Khi Nút Chuỗi Resonance &lt;color=Highlight&gt;I Remain Who I am, Eternal My Flame&lt;/color&gt; được kích hoạt, &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt;. &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt; vẫn giữ lại mọi hiệu ứng của &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;. Ngoài ra, trong thời gian &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt; tồn tại, Hệ Số Sát Thương của &lt;color=Highlight&gt;Basic Attack - Seraphic Execution&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Hellsent Barrage&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter - Purgatory Scourge&lt;/color&gt; sẽ tăng thêm {0}.</t>
+          <t>Khi Nút Resonance Chain &lt;color=Highlight&gt;Ta Vẫn Là Ta, Ngọn Lửa Vĩnh Hằng&lt;/color&gt; được kích hoạt, &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt;. &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt; vẫn giữ lại mọi hiệu ứng của &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt;. Ngoài ra, trong thời gian &lt;color=Highlight&gt;Eternal Hypostasis&lt;/color&gt; tồn tại, Hệ Số Sát Thương của &lt;color=Highlight&gt;Đòn Cơ Bản - Seraphic Execution&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Nặng - Flamewing Verdict&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Trên Không - Hellsent Barrage&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter Tránh - Purgatory Scourge&lt;/color&gt; sẽ tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;, &lt;color=Highlight&gt;Hellstride&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 4&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Encroach&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Ascent of Malice&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Ravage&lt;/color&gt;, Galbrena sẽ tăng {0} Attack và Kháng Đứt Quãng trong {1} giây.</t>
+          <t>Khi sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;, &lt;color=Highlight&gt;Bước Địa Ngục&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản - Giai Đoạn Hành Quyết Thiên Thần 4&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Xâm Lấn&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Thăng Hoa Oán Hận&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Tàn Phá&lt;/color&gt;, Galbrena sẽ tăng {0} ATK và Kháng Đứt Quãng trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi ở &lt;color=Highlight&gt;Baseline Mode&lt;/color&gt; mặc định, Mornye nhận được &lt;color=Highlight&gt;Rest Mass Energy&lt;/color&gt;.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Chế Độ Cơ Bản&lt;/color&gt; mặc định, Mornye nhận được &lt;color=Highlight&gt;Năng Lượng Khối Lượng Nghỉ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9290,15 +9290,15 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kéo dài trong {11} giây.
-- Khi bước vào &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;, Mornye tạo ra một &lt;color=Highlight&gt;Trường Resonance&lt;/color&gt;.
-- Trong &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;, Mornye nhận được &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt;.
-- Nếu &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt; dưới {0} khi giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;, thực hiện &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode Stage 1 đến 3&lt;/color&gt; theo thứ tự. Nếu &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt; đạt {0} trong lúc này, thay vào đó sẽ tung ra &lt;color=Highlight&gt;Heavy Attack - Inversion&lt;/color&gt;.
-- Khi di chuyển, Mornye liên tục tiêu hao STA. STA không thể hồi phục trong &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;.
-- Khi Dodge có nhập hướng, Mornye sẽ bay với tốc độ cao, hiệu ứng kéo dài tối đa 10 giây hoặc cho đến khi STA cạn kiệt hoặc &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kết thúc.
-- Khi Mornye bị tấn công hoặc bị hất tung lên không trung, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để hồi phục ngay lập tức, được tính là Dodge thành công. Hiệu ứng này có thể kích hoạt tối đa {12} lần và sẽ được đặt lại khi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt; kết thúc.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} nhảy và Mornye sẽ từ từ hạ xuống. Trước khi cô ấy tiếp đất, &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Distributed Array&lt;/color&gt; và &lt;color=Highlight&gt;Heavy Attack - Inversion&lt;/color&gt; sẽ không khả dụng. Nếu nhảy khi STA của Mornye cạn kiệt, cô ấy sẽ thoát khỏi &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;. Cô ấy cũng sẽ rời khỏi chế độ này khi &lt;color=Highlight&gt;Dodge&lt;/color&gt;, nhảy hoặc thực hiện đòn tấn công giữa không trung.
-Ngoài ra, thực hiện tương tác với môi trường, sử dụng vật phẩm tiện ích hoặc chuyển đổi sang Resonator khác sẽ kết thúc &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;. Trạng thái này cũng kết thúc khi Mornye không còn ở trên không.</t>
+          <t>&lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt; kéo dài trong {11} giây.
+- Khi bước vào &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, Mornye tạo ra một &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt;.
+- Trong &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, Mornye nhận được &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt;.
+- Nếu &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt; dưới {0} khi giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt;, thực hiện &lt;color=Highlight&gt;Đòn Cơ Bản - Chế Độ Quan Sát Trường Rộng Giai Đoạn 1 đến 3&lt;/color&gt; theo thứ tự. Nếu &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt; đạt {0} trong lúc này, thay vào đó sẽ tung ra &lt;color=Highlight&gt;Đòn Nặng - Inversion&lt;/color&gt;.
+- Khi di chuyển, Mornye liên tục tiêu hao STA. STA không thể hồi phục trong &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;.
+- Khi né tránh có nhập hướng, Mornye sẽ bay với tốc độ cao, hiệu ứng kéo dài tối đa 10 giây hoặc cho đến khi STA cạn kiệt hoặc &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt; kết thúc.
+- Khi Mornye bị tấn công hoặc bị hất tung lên không trung, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né tránh để hồi phục ngay lập tức, được tính là né tránh thành công. Hiệu ứng này có thể kích hoạt tối đa {12} lần và sẽ được đặt lại khi &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt; kết thúc.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nhảy và Mornye sẽ từ từ hạ xuống. Trước khi cô ấy tiếp đất, &lt;color=Highlight&gt;Đòn Cơ Bản - Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Distributed Array&lt;/color&gt; và &lt;color=Highlight&gt;Đòn Nặng - Inversion&lt;/color&gt; sẽ không khả dụng. Nếu nhảy khi STA của Mornye cạn kiệt, cô ấy sẽ thoát khỏi &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;. Cô ấy cũng sẽ rời khỏi chế độ này khi &lt;color=Highlight&gt;né tránh&lt;/color&gt;, nhảy hoặc thực hiện đòn tấn công giữa không trung.
+Ngoài ra, thực hiện tương tác với môi trường, sử dụng vật phẩm tiện ích hoặc chuyển đổi sang Resonator khác sẽ kết thúc &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;. Trạng thái này cũng kết thúc khi Mornye không còn ở trên không.</t>
         </is>
       </c>
     </row>
@@ -9364,8 +9364,8 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Mornye có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Rest Mass Energy&lt;/color&gt;.
-Khi ở &lt;color=Highlight&gt;Baseline Mode&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Rest Mass Energy&lt;/color&gt; khi thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;, hoặc khi &lt;color=Highlight&gt;Resonance Skill - Optimal Solution&lt;/color&gt; trúng mục tiêu.</t>
+          <t>Mornye có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Năng Lượng Khối Lượng Nghỉ&lt;/color&gt;.
+Khi ở &lt;color=Highlight&gt;Chế Độ Cơ Bản&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Năng Lượng Khối Lượng Nghỉ&lt;/color&gt; khi thực hiện &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt;, hoặc khi &lt;color=Highlight&gt;Resonance Skill - Giải Pháp Tối Ưu&lt;/color&gt; trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9432,9 +9432,9 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mornye có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt;.
-Khi ở trong &lt;color=Highlight&gt;Wide Field Observation Mode&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt; khi &lt;color=Highlight&gt;Basic Attack - Wide Field Observation Mode&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter - Wide Field Observation Mode&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Resonance Skill - Distributed Array&lt;/color&gt; trúng mục tiêu.
-Mornye không thể nhận &lt;color=Highlight&gt;Relative Momentum&lt;/color&gt; trong &lt;color=Highlight&gt;Heavy Attack - Inversion&lt;/color&gt;.</t>
+          <t>Mornye có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt;.
+Khi ở trong &lt;color=Highlight&gt;Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, cô sẽ nhận được &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt; khi &lt;color=Highlight&gt;Đòn Basic Attack - Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter Tránh - Chế Độ Quan Sát Trường Rộng&lt;/color&gt;, hoặc &lt;color=Highlight&gt;Resonance Skill - Mảng Phân Bố&lt;/color&gt; trúng mục tiêu.
+Mornye không thể nhận &lt;color=Highlight&gt;Động Lượng Tương Đối&lt;/color&gt; trong &lt;color=Highlight&gt;Đòn Tấn Công Mạnh - Chế Độ Đảo Ngược&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Tune Rupture - Interfered&lt;/color&gt; hoặc &lt;color=Highlight&gt;Tune Strain - Interfered&lt;/color&gt; sẽ chịu sát thương tăng từ tất cả Resonators trong đội ở gần. Cứ mỗi {8} Energy Regen của Mornye vượt quá {7}, sát thương của họ sẽ tăng thêm {9}, tối đa {10}.</t>
+          <t>Mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Điệu Tan Vỡ - Nhiễu Loạn&lt;/color&gt; hoặc &lt;color=Highlight&gt;Điệu Căng Thẳng - Nhiễu Loạn&lt;/color&gt; sẽ chịu DMG tăng từ tất cả Resonator trong đội ở gần. Cứ mỗi {8} Hồi Năng Lượng của Mornye vượt quá {7}, DMG của họ sẽ tăng thêm {9}, tối đa {10}.</t>
         </is>
       </c>
     </row>
@@ -9633,11 +9633,11 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>- &lt;color=Highlight&gt;Syntony Field&lt;/color&gt; kéo dài trong {1} giây.
-- Khi &lt;color=Highlight&gt;Syntony Field&lt;/color&gt; được tạo ra, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
-- Liên tục hồi phục HP cho tất cả Resonators trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Syntony Field&lt;/color&gt;, kích hoạt mỗi {2} giây.
-- Tăng &lt;color=Highlight&gt;Off-Tune Buildup Rate&lt;/color&gt; của tất cả Resonators trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Syntony Field&lt;/color&gt; lên {3}.
-- Tăng khả năng kháng gián đoạn cho tất cả Resonators trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Syntony Field&lt;/color&gt;.</t>
+          <t>- &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; kéo dài trong {1} giây.
+- Khi &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; được tạo ra, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
+- Liên tục hồi phục HP cho tất cả Resonator trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt;, kích hoạt mỗi {2} giây.
+- Tăng &lt;color=Highlight&gt;Tốc Độ Tích Lũy Lệch Nhịp&lt;/color&gt; của tất cả Resonator trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; lên {3}.
+- Tăng khả năng kháng gián đoạn cho tất cả Resonator trong đội ở gần trong phạm vi &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -9705,10 +9705,10 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>- &lt;color=Highlight&gt;High Syntony Field&lt;/color&gt; kéo dài trong {6} giây.
-- Tăng &lt;color=Highlight&gt;Phòng Ngự&lt;/color&gt; cho tất cả Resonators trong đội trong phạm vi &lt;color=Highlight&gt;High Syntony Field&lt;/color&gt; lên {8}.
+          <t>- &lt;color=Highlight&gt;Trường Cộng Hưởng Cao&lt;/color&gt; kéo dài trong {6} giây.
+- Tăng &lt;color=Highlight&gt;Phòng Ngự&lt;/color&gt; cho tất cả Resonator trong đội trong phạm vi &lt;color=Highlight&gt;Trường Cộng Hưởng Cao&lt;/color&gt; lên {8}.
 - Kế thừa hiệu ứng tăng &lt;color=Highlight&gt;Kháng Làm Gián Đoạn&lt;/color&gt; và &lt;color=Highlight&gt;Tốc Độ Tích Lũy Off-Tune&lt;/color&gt; từ &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt;.
-- Kế thừa hiệu ứng hồi phục từ &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; và tăng Hệ Số Healing lên {7}.</t>
+- Kế thừa hiệu ứng hồi phục từ &lt;color=Highlight&gt;Trường Cộng Hưởng&lt;/color&gt; và tăng Hệ Số Hồi Phục lên {7}.</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mỗi lớp cộng dồn tăng {0} Electro DMG Bonus, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần cộng dồn SapTag=1}. Khi &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun: Everbright Protector&lt;/color&gt; kết thúc, tất cả các lớp cộng dồn của Crown of Wills sẽ bị xóa.</t>
+          <t>Mỗi lớp cộng dồn tăng {0} Tăng Sát Thương Electro, tối đa &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần cộng dồn SapTag=1}. Khi &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun: Everbright Protector&lt;/color&gt; kết thúc, tất cả các lớp cộng dồn của Crown of Wills sẽ bị xóa.</t>
         </is>
       </c>
     </row>
@@ -9841,8 +9841,8 @@
       <c r="M142" t="inlineStr">
         <is>
           <t>Augusta có thể tích lũy tối đa {0} điểm Kiên Cường.
-- Kiên Cường sẽ được nhận khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Dodge Counter&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Heavy Attack: Steelclash&lt;/color&gt; gây sát thương.
-- Sử dụng &lt;color=Highlight&gt;Intro Skill - Stride of Goldenflare&lt;/color&gt; sẽ hồi đầy Kiên Cường.</t>
+- Kiên Cường sẽ được nhận khi &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Tấn Công Mạnh - Va Chạm Thép&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter Giữa Không&lt;/color&gt;, &lt;color=Highlight&gt;Resonance Skill - Lưỡi Kiếm Chiến Binh&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter - Đòn Tấn Công Mạnh: Va Chạm Thép&lt;/color&gt; gây sát thương.
+- Sử dụng &lt;color=Highlight&gt;Kỹ Năng Khởi Động - Bước Chân Ánh Lửa Hoàng Kim&lt;/color&gt; sẽ hồi đầy Kiên Cường.</t>
         </is>
       </c>
     </row>
@@ -9912,10 +9912,10 @@
       <c r="M143" t="inlineStr">
         <is>
           <t>Augusta có thể giữ tối đa {0} điểm Uy Thế.
-- Nhận Uy Thế khi &lt;color=Highlight&gt;Normal Attacks&lt;/color&gt; gây sát thương.
-- Thi triển &lt;color=Highlight&gt;Intro Skill - Stride of Goldenflare&lt;/color&gt; hồi {1} Uy Thế.
-- Thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt; hồi {2} Uy Thế.
-- Thi triển &lt;color=Highlight&gt;Resonance Liberation - Kiếm of Eternal Oath&lt;/color&gt; hồi {3} Uy Thế.</t>
+- Nhận Uy Thế khi &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; gây sát thương.
+- Thi triển &lt;color=Highlight&gt;Kỹ Năng Intro - Bước Chân Ánh Lửa Vàng&lt;/color&gt; hồi {1} Uy Thế.
+- Thi triển &lt;color=Highlight&gt;Resonance Skill - Lưỡi Kiếm Chiến Binh&lt;/color&gt; hồi {2} Uy Thế.
+- Thi triển &lt;color=Highlight&gt;Kỹ Năng Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu&lt;/color&gt; hồi {3} Uy Thế.</t>
         </is>
       </c>
     </row>
@@ -9983,8 +9983,8 @@
       <c r="M144" t="inlineStr">
         <is>
           <t>Augusta có thể giữ tối đa 2 tầng Uy Phong.
-- Nhận 1 tầng Uy Phong khi thi triển &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.
-- Nhận 1 tầng Uy Phong khi Resonators trong đội thi triển &lt;color=Highlight&gt;Outro Skills&lt;/color&gt; dưới hiệu ứng của &lt;color=Highlight&gt;Outro Skill - Battlesong of the Unyielding&lt;/color&gt; của Augusta.</t>
+- Nhận 1 tầng Uy Phong khi thi triển &lt;color=Highlight&gt;Resonance Skill - Ánh Dương Bất Tử: Lao Xuống&lt;/color&gt;.
+- Nhận 1 tầng Uy Phong khi Resonator trong đội thi triển &lt;color=Highlight&gt;Kỹ Năng Outro&lt;/color&gt; dưới hiệu ứng của &lt;color=Highlight&gt;Kỹ Năng Outro - Khúc Chiến Ca Bất Khuất&lt;/color&gt; của Augusta.</t>
         </is>
       </c>
     </row>
@@ -10050,8 +10050,8 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>- &lt;color=Highlight&gt;Ruler's Realm&lt;/color&gt; kéo dài trong {3} giây.
-- Khi Resonators trong đội sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; trong &lt;color=Highlight&gt;Ruler's Realm&lt;/color&gt;, họ sẽ nhận một lá chắn tương đương {5} + {4} HP tối đa của Augusta trong {6} giây. Hiệu ứng này không thể chồng chất. Lá chắn này sẽ không được chuyển cho Resonators thay thế.</t>
+          <t>- &lt;color=Highlight&gt;Lãnh Địa Của Quân Chủ&lt;/color&gt; kéo dài trong {3} giây.
+- Khi Resonator trong đội sử dụng &lt;color=Highlight&gt;Kỹ Năng Intro&lt;/color&gt; trong &lt;color=Highlight&gt;Lãnh Địa Của Quân Chủ&lt;/color&gt;, họ sẽ nhận một lá chắn tương đương {5} + {4} HP tối đa của Augusta trong {6} giây. Hiệu ứng này không thể chồng chất. Lá chắn này sẽ không được chuyển cho Resonator thay thế.</t>
         </is>
       </c>
     </row>
@@ -10119,10 +10119,10 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, thời gian tạm thời ngừng trôi, và &lt;color=Highlight&gt;Resonator switching&lt;/color&gt; bị vô hiệu hóa. Chỉ có thể thực hiện &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt;, &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt; và &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;. &lt;color=Highlight&gt;Mid-air Attacks&lt;/color&gt; vẫn có thể thực hiện khi đang ở trên không trong trạng thái này.
-- Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt;. Augusta có thể đi trên mặt nước mà không tiêu hao STA trong trạng thái này.
-- Khi trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt; kết thúc, &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt; sẽ được thi triển tự động.
-- Thực hiện &lt;color=Highlight&gt;environmental, gameplay, or other interactions&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt; mà không kích hoạt &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Lời Thề Trung Kiên&lt;/color&gt;, thời gian tạm thời ngừng trôi, và &lt;color=Highlight&gt;chuyển đổi Resonator&lt;/color&gt; bị vô hiệu hóa. Chỉ có thể thực hiện &lt;color=Highlight&gt;Thái Dương Vĩ Đại - Hóa Thân Thái Dương&lt;/color&gt;, &lt;color=Highlight&gt;Thái Dương Vĩ Đại - Hộ Giá Vĩnh Quang&lt;/color&gt; và &lt;color=Highlight&gt;Né Tránh&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Lời Thề Trung Kiên&lt;/color&gt;. &lt;color=Highlight&gt;Tấn Công Giữa Không&lt;/color&gt; vẫn có thể thực hiện khi đang ở trên không trong trạng thái này.
+- Trong trạng thái &lt;color=Highlight&gt;Lời Thề Trung Kiên&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Thái Dương Vĩ Đại - Hóa Thân Thái Dương&lt;/color&gt;. Augusta có thể đi trên mặt nước mà không tiêu hao STA trong trạng thái này.
+- Khi trạng thái &lt;color=Highlight&gt;Lời Thề Trung Kiên&lt;/color&gt; kết thúc, &lt;color=Highlight&gt;Thái Dương Vĩ Đại - Hộ Giá Vĩnh Quang&lt;/color&gt; sẽ được thi triển tự động.
+- Thực hiện &lt;color=Highlight&gt;tương tác với môi trường, lối chơi hoặc các hành động khác&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;Lời Thề Trung Kiên&lt;/color&gt; mà không kích hoạt &lt;color=Highlight&gt;Thái Dương Vĩ Đại - Hộ Giá Vĩnh Quang&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10189,9 +10189,9 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Iuno có thể chuyển đổi giữa trạng thái &lt;color=Highlight&gt;Half Moon&lt;/color&gt; và &lt;color=Highlight&gt;New Moon&lt;/color&gt;.
+          <t>Iuno có thể chuyển đổi giữa trạng thái &lt;color=Highlight&gt;Trăng Khuyết&lt;/color&gt; và &lt;color=Highlight&gt;Trăng Non&lt;/color&gt;.
 Trăng Khuyết: Các đòn tấn công sẽ hồi phục Thanh Forte khi trúng mục tiêu.
-New Moon: Basic Attack, Resonance Skill và Dodge Phản Công sẽ tiêu hao Thanh Forte để tăng Hệ Số Sát Thương của kỹ năng này.</t>
+Trăng Non: Basic Attack, Resonance Skill và Né Tránh Phản Công sẽ tiêu hao Thanh Forte để tăng Hệ Số Sát Thương của kỹ năng này.</t>
         </is>
       </c>
     </row>
@@ -10325,11 +10325,11 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Iuno có thể chứa tối đa 100 điểm &lt;color=Highlight&gt;Sentience&lt;/color&gt;.
-Kích hoạt Intro Skill sẽ hồi phục 40 điểm &lt;color=Highlight&gt;Sentience&lt;/color&gt;.
-Kích hoạt Resonance Liberation sẽ hồi phục 60 điểm &lt;color=Highlight&gt;Sentience&lt;/color&gt;.
-Kích hoạt &lt;color=Highlight&gt;Closing Refrain&lt;/color&gt; hoặc &lt;color=Highlight&gt;Unfinished Refrain&lt;/color&gt; sẽ hồi phục 25 điểm &lt;color=Highlight&gt;Sentience&lt;/color&gt;.
-Khi Iuno ở trạng thái &lt;color=Highlight&gt;Lunar Cycle&lt;/color&gt;, Basic Attack - Moonring, Dodge Phản Công - Moonring và Mid-air Attack đều hồi phục &lt;color=Highlight&gt;Sentience&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Iuno có thể chứa tối đa 100 điểm &lt;color=Highlight&gt;Ý Thức&lt;/color&gt;.
+Kích hoạt Kỹ Năng Khởi Động sẽ hồi phục 40 điểm &lt;color=Highlight&gt;Ý Thức&lt;/color&gt;.
+Kích hoạt Resonance Liberation sẽ hồi phục 60 điểm &lt;color=Highlight&gt;Ý Thức&lt;/color&gt;.
+Kích hoạt &lt;color=Highlight&gt;Điệp Khúc Kết&lt;/color&gt; hoặc &lt;color=Highlight&gt;Điệp Khúc Chưa Hoàn Thành&lt;/color&gt; sẽ hồi phục 25 điểm &lt;color=Highlight&gt;Ý Thức&lt;/color&gt;.
+Khi Iuno ở trạng thái &lt;color=Highlight&gt;Chu Kỳ Mặt Trăng&lt;/color&gt;, Basic Attack - Moonring, Né Tránh Phản Công - Moonring và Tấn Công Giữa Không đều hồi phục &lt;color=Highlight&gt;Ý Thức&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10400,13 +10400,13 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Qiuyuan có thể tích lũy tối đa 600 điểm *Swordster's Soliloquy*.
-- 100 điểm *Swordster's Soliloquy* nhận được khi thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; Giai đoạn 3.
-- 100 điểm *Swordster's Soliloquy* nhận được khi thực hiện từng giai đoạn của &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt;.
-- 100 điểm *Swordster's Soliloquy* nhận được khi thực hiện &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;.
-- 400 điểm *Swordster's Soliloquy* nhận được khi thực hiện &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;.
-- Không thể nhận *Swordster's Soliloquy* trong trạng thái *Mực Tàu Tâm Trí*.
-- *Swordster's Soliloquy* sẽ bị xóa khi trạng thái *Mực Tàu Tâm Trí* kết thúc.</t>
+          <t>Qiuyuan có thể tích lũy tối đa 600 điểm *Độc Thoại Kiếm Khách*.
+- 100 điểm *Độc Thoại Kiếm Khách* nhận được khi thực hiện &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; Giai đoạn 3.
+- 100 điểm *Độc Thoại Kiếm Khách* nhận được khi thực hiện từng giai đoạn của &lt;color=Highlight&gt;Lưỡi Kiếm Lên Tiếng: Mực Tàu&lt;/color&gt;.
+- 100 điểm *Độc Thoại Kiếm Khách* nhận được khi thực hiện &lt;color=Highlight&gt;Dodge Counter Tránh&lt;/color&gt;.
+- 400 điểm *Độc Thoại Kiếm Khách* nhận được khi thực hiện &lt;color=Highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt;.
+- Không thể nhận *Độc Thoại Kiếm Khách* trong trạng thái *Mực Tàu Tâm Trí*.
+- *Độc Thoại Kiếm Khách* sẽ bị xóa khi trạng thái *Mực Tàu Tâm Trí* kết thúc.</t>
         </is>
       </c>
     </row>
@@ -10473,8 +10473,8 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Khi Độ Trữ Tâm Kiếm đạt tối đa, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt; trong 8 giây. Trong trạng thái này, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; được thay thế bằng Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt;.
-Trong trạng thái này, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao Độ Trữ Tâm Kiếm và thực hiện Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Teach&lt;/color&gt;, &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; và &lt;color=Highlight&gt;Thus Spoke the Blade: To Sacrifice&lt;/color&gt; theo thứ tự, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
+          <t>Khi Độ Trữ Tâm Kiếm đạt tối đa, Qiuyuan bước vào trạng thái &lt;color=Highlight&gt;Mực Tâm Loang&lt;/color&gt; trong 8 giây. Trong trạng thái này, &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt; được thay thế bằng Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Lời Kiếm Phán: Cứu Độ&lt;/color&gt;.
+Trong trạng thái này, giữ &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; để tiêu hao Độ Trữ Tâm Kiếm và thực hiện Đòn Tấn Công Mạnh &lt;color=Highlight&gt;Lời Kiếm Phán: Dạy Dỗ&lt;/color&gt;, &lt;color=Highlight&gt;Lời Kiếm Phán: Cứu Độ&lt;/color&gt; và &lt;color=Highlight&gt;Lời Kiếm Phán: Hy Sinh&lt;/color&gt; theo thứ tự, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, được tính là Sát Thương Đòn Tấn Công Mạnh.
 - Trạng thái Mực Tâm Loang kết thúc khi Độ Trữ Tâm Kiếm cạn kiệt.</t>
         </is>
       </c>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Khi Qiuyuan tích lũy đủ 400 điểm Ngâm Kiếm, cậu nhận hiệu ứng &lt;color=Highlight&gt;Bamboo's Shade&lt;/color&gt;, giúp tất cả Resonators trong đội gần đó nhận thêm 30% Sát Thương Kỹ Năng Hồi Âm trong 30 giây.</t>
+          <t>Khi Qiuyuan tích lũy đủ 400 điểm Ngâm Kiếm, cậu nhận hiệu ứng &lt;color=Highlight&gt;Bóng Tre&lt;/color&gt;, giúp tất cả Resonator trong đội gần đó nhận thêm 30% Sát Thương Kỹ Năng Hồi Âm trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Khi mục tiêu bị đánh dấu bởi &lt;color=Highlight&gt;Unseen Snare&lt;/color&gt; nhận sát thương trực tiếp từ Resonators, Chisa sẽ gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} &lt;color=Highlight&gt;Havoc Bane&lt;/color&gt; lên chúng. Hiệu ứng này có thể kích hoạt tối đa một lần mỗi {1} giây.</t>
+          <t>Khi mục tiêu bị đánh dấu bởi &lt;color=Highlight&gt;Unseen Snare&lt;/color&gt; nhận sát thương trực tiếp từ Resonator, Chisa sẽ gây &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=0} &lt;color=Highlight&gt;Havoc Bane&lt;/color&gt; lên chúng. Hiệu ứng này có thể kích hoạt tối đa một lần mỗi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Khi gây sát thương lên mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Unseen Snare&lt;/color&gt;, bỏ qua {0} Phòng Ngự của chúng.</t>
+          <t>Khi gây sát thương lên mục tiêu bị ảnh hưởng bởi &lt;color=Highlight&gt;Bẫy Vô Hình&lt;/color&gt;, bỏ qua {0} Phòng Ngự của chúng.</t>
         </is>
       </c>
     </row>
@@ -10738,10 +10738,10 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chisa có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt;.
-Tấn công mục tiêu bằng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt;.
-Sử dụng Resonance Liberation &lt;color=Highlight&gt;Moment of Nihility&lt;/color&gt; sẽ nhận được {1} điểm &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt;.
-Sử dụng Kỹ Năng Giới Thiệu &lt;color=Highlight&gt;Reverberance - Return&lt;/color&gt; sẽ nhận được {2} điểm &lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt;.</t>
+          <t>Chisa có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt;.
+Tấn công mục tiêu bằng &lt;color=Highlight&gt;Đòn Normal Attack&lt;/color&gt; và Resonance Skill &lt;color=Highlight&gt;Con Mắt Giải Thích&lt;/color&gt; sẽ nhận được &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt;.
+Sử dụng Resonance Liberation &lt;color=Highlight&gt;Khoảnh Khắc Hư Vô&lt;/color&gt; sẽ nhận được {1} điểm &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt;.
+Sử dụng Kỹ Năng Giới Thiệu &lt;color=Highlight&gt;Dư Âm - Trở Lại&lt;/color&gt; sẽ nhận được {2} điểm &lt;color=Highlight&gt;Vòng Cưa Xích&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10810,11 +10810,11 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Chisa có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt;. 
-Chisa liên tục nhận được &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; theo thời gian.
-Chisa nhận được {1} điểm &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; khi đánh bại mục tiêu. 
-Thoát khỏi &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; sẽ đặt lại &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; về giới hạn tối đa.
-Chisa không thể nhận &lt;color=Highlight&gt;Lifethread - Jetstream&lt;/color&gt; một cách thụ động trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.</t>
+          <t>Chisa có thể tích lũy tối đa {0} điểm &lt;color=Highlight&gt;Sợi Sinh Mệnh - Luồng Phản Lực&lt;/color&gt;. 
+Chisa liên tục nhận được &lt;color=Highlight&gt;Sợi Sinh Mệnh - Luồng Phản Lực&lt;/color&gt; theo thời gian.
+Chisa nhận được {1} điểm &lt;color=Highlight&gt;Sợi Sinh Mệnh - Luồng Phản Lực&lt;/color&gt; khi đánh bại mục tiêu. 
+Thoát khỏi &lt;color=Highlight&gt;Chế Độ Cưa Xích&lt;/color&gt; sẽ đặt lại &lt;color=Highlight&gt;Sợi Sinh Mệnh - Luồng Phản Lực&lt;/color&gt; về giới hạn tối đa.
+Chisa không thể nhận &lt;color=Highlight&gt;Sợi Sinh Mệnh - Luồng Phản Lực&lt;/color&gt; một cách thụ động trong thời gian ngắn sau khi sử dụng &lt;color=Highlight&gt;Sợi Sinh Mệnh - Lướt Bay&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -10881,8 +10881,8 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Hệ số Sát Thương của &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt;, &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; và &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; được tăng thêm {0}.
-&lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; bị tiêu hao bởi &lt;color=Highlight&gt;Sawring- Blitz&lt;/color&gt; và &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; sẽ tăng thêm hệ số Sát Thương của &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; thêm {1}.
+          <t>Hệ số Sát Thương của &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt;, &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter Tránh&lt;/color&gt; và &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; được tăng thêm {0}.
+&lt;color=Highlight&gt;Ring of Chainsaw&lt;/color&gt; bị tiêu hao bởi &lt;color=Highlight&gt;Sawring- Blitz&lt;/color&gt; và &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter Tránh&lt;/color&gt; sẽ tăng thêm hệ số Sát Thương của &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; thêm {1}.
 Thi triển &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;Woven Myriad - Convergence&lt;/color&gt;.</t>
         </is>
       </c>
@@ -10948,7 +10948,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Electro Rage gia tăng sát thương của Điện Pháo kế tiếp. Hiệu ứng sẽ biến mất sau khi kích hoạt.</t>
+          <t>Điên Loạn Điện gia tăng sát thương của Điện Pháo kế tiếp. Hiệu ứng sẽ biến mất sau khi kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Includes Spectro DMG Frazzle, Havoc DMG Bane, Fusion DMG Burst, Glacio DMG Chafe, Electro DMG Flare và Aero DMG Erosion.</t>
+          <t>Bao gồm DMG Spectro Frazzle, DMG Havoc Bane, DMG Fusion Burst, DMG Glacio Chafe, DMG Electro Flare và DMG Aero Erosion.</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Lynae mặc định ở trạng thái &lt;color=Highlight&gt;Optical Sampling Stage&lt;/color&gt;. Trong trạng thái này, &lt;color=Highlight&gt;Overflow&lt;/color&gt; sẽ hồi phục khi thực hiện Basic Attack, Lynae-Style Palettes, Mid-air Attack, hoặc Dodge Counter, hoặc khi Intro Skill được kích hoạt.</t>
+          <t>Lynae mặc định ở trạng thái &lt;color=Highlight&gt;Lấy Mẫu Quang Học&lt;/color&gt;. Trong trạng thái này, &lt;color=Highlight&gt;Tràn&lt;/color&gt; sẽ hồi phục khi thực hiện Basic Attack, Bảng Màu Kiểu Lynae, Tấn Công Giữa Không, hoặc Dodge Counter Tránh, hoặc khi Kỹ Năng Khởi Động được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Kích hoạt &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; sẽ đưa Lynae vào trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;. Trong trạng thái này, Lynae di chuyển nhanh hơn và liên tục hồi phục &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; khi di chuyển trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Ground Heavy Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Mid-air Heavy Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Mid-air Attack&lt;/color&gt;, &lt;color=Highlight&gt;Additive Color&lt;/color&gt;, Dodge, Intro Skill hoặc &lt;color=Highlight&gt;Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Đòn Basic Attack - Spark Collision&lt;/color&gt; sẽ đưa Lynae vào trạng thái &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;. Trong trạng thái này, Lynae di chuyển nhanh hơn và liên tục hồi phục &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; khi di chuyển trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Kaleidoscopic Parade - Đòn Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Đòn Heavy Attack Trên Mặt Đất&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Đòn Heavy Attack Trên Không&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Đòn Mid-air Attack&lt;/color&gt;, &lt;color=Highlight&gt;Additive Color&lt;/color&gt;, Né Tránh, Kỹ Năng Khởi Động hoặc &lt;color=Highlight&gt;Đòn Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Khi trúng mục tiêu bằng &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Polychrome Leap&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;, gây hiệu ứng &lt;color=Highlight&gt;Intro Skill - Time to Show Some Colors!&lt;/color&gt;. Khi Lynae ở trạng thái &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt;/&lt;color=Highlight&gt;Tune Rupture - Shifting&lt;/color&gt;, &lt;color=Highlight&gt;Tune Strain - Shifting&lt;/color&gt; sẽ gây &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;/&lt;color=Highlight&gt;Resonance Mode - Tune Strain&lt;/color&gt; lên mục tiêu trong 25 giây.</t>
+          <t>Khi trúng mục tiêu bằng &lt;color=Highlight&gt;Đòn Cơ Bản - Bước Nhảy Đa Sắc&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản - Tia Sáng Lấp Lánh&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản - Va Chạm Thị Giác&lt;/color&gt; hoặc &lt;color=Highlight&gt;Kỹ Năng Khởi Động - Đến Giờ Trổ Tài Rồi!&lt;/color&gt;, gây hiệu ứng &lt;color=Highlight&gt;Dòng Chảy Quang Sắc&lt;/color&gt;. Khi Lynae ở trạng thái &lt;color=Highlight&gt;Cộng Hưởng - Đứt Giai Điệu&lt;/color&gt;/&lt;color=Highlight&gt;Cộng Hưởng - Căng Giai Điệu&lt;/color&gt;, &lt;color=Highlight&gt;Dòng Chảy Quang Sắc&lt;/color&gt; sẽ gây &lt;color=Highlight&gt;Đứt Giai Điệu - Dao Động&lt;/color&gt;/&lt;color=Highlight&gt;Căng Giai Điệu - Dao Động&lt;/color&gt; lên mục tiêu trong 25 giây.</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Khi Inherent Skill &lt;color=Highlight&gt;Colors Never Fade!&lt;/color&gt; được kích hoạt, Lynae sẽ để lại &lt;color=Highlight&gt;Spray Paint&lt;/color&gt; trên mặt đất sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt;, liên tục gây &lt;color=Highlight&gt;Photochromic Flux&lt;/color&gt; lên mục tiêu trong phạm vi &lt;color=Highlight&gt;Spray Paint&lt;/color&gt;.</t>
+          <t>Khi Kỹ Năng Nội Tại &lt;color=Highlight&gt;Màu Sắc Không Bao Giờ Phai!&lt;/color&gt; được kích hoạt, Lynae sẽ để lại &lt;color=Highlight&gt;Sơn Xịt&lt;/color&gt; trên mặt đất sau khi sử dụng &lt;color=Highlight&gt;Đòn Cơ Bản - Cú Đánh Hình Ảnh&lt;/color&gt;, liên tục gây &lt;color=Highlight&gt;Dòng Chảy Quang Phổ&lt;/color&gt; lên mục tiêu trong phạm vi &lt;color=Highlight&gt;Sơn Xịt&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11342,9 +11342,9 @@
       <c r="M164" t="inlineStr">
         <is>
           <t>Tối đa 120 điểm.
-Trong &lt;color=Highlight&gt;Optical Sampling Stage&lt;/color&gt;, &lt;color=Highlight&gt;Overflow&lt;/color&gt; hồi phục khi sử dụng Basic Attack, Lynae-Style Palettes, Mid-air Attack và Dodge Counter, hoặc khi kích hoạt Intro Skill.
-Khi &lt;color=Highlight&gt;Overflow&lt;/color&gt; đầy, &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; sẽ được kích hoạt.
-Sử dụng &lt;color=Highlight&gt;Basic Attack - Spark Collision&lt;/color&gt; sẽ xóa toàn bộ &lt;color=Highlight&gt;Overflow&lt;/color&gt;.</t>
+Trong &lt;color=Highlight&gt;Giai Đoạn Lấy Mẫu Quang Học&lt;/color&gt;, &lt;color=Highlight&gt;Tràn Sáng&lt;/color&gt; hồi phục khi sử dụng Basic Attack, Bảng Màu Kiểu Lynae, Tấn Công Giữa Không Trung và Dodge Counter Tránh, hoặc khi kích hoạt Kỹ Năng Khởi Động.
+Khi &lt;color=Highlight&gt;Tràn Sáng&lt;/color&gt; đầy, &lt;color=Highlight&gt;Basic Attack - Va Chạm Tia Lửa&lt;/color&gt; sẽ được kích hoạt.
+Sử dụng &lt;color=Highlight&gt;Basic Attack - Va Chạm Tia Lửa&lt;/color&gt; sẽ xóa toàn bộ &lt;color=Highlight&gt;Tràn Sáng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11416,12 +11416,12 @@
       <c r="M165" t="inlineStr">
         <is>
           <t>Tối đa 120 điểm.
-Trong &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt;:
-- Restore 20% &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; mỗi giây khi Lynae di chuyển trên mặt đất/leo trèo, hoặc Dodge thành công trên mặt đất, hoặc trong khoảng thời gian nhất định khi sử dụng &lt;color=Highlight&gt;Kaleidoscopic Parade - Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Ground Heavy Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Mid-air Heavy Attack&lt;/color&gt;, &lt;color=Highlight&gt;Kaleidoscopic Parade - Dodge Counter&lt;/color&gt;, &lt;color=Highlight&gt;Additive Color&lt;/color&gt;, Dodge trên mặt đất, Intro Skill, hoặc &lt;color=Highlight&gt;Basic Attack - To a Vivid Tomorrow!&lt;/color&gt;.
-- &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; bắt đầu giảm 20% mỗi giây khi Lynae đứng yên trên mặt đất/leo trèo/bơi lội hoặc rời khỏi chiến trường, hoặc sau một khoảng thời gian nhất định sau khi sử dụng các kỹ năng trên.
-- &lt;color=Highlight&gt;Lumiflow&lt;/color&gt; không thay đổi khi Lynae không ở trong bất kỳ trạng thái nào kể trên.
-Thoát khỏi &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt; sẽ xóa toàn bộ &lt;color=Highlight&gt;Lumiflow&lt;/color&gt;.
-Với 120 điểm &lt;color=Highlight&gt;&lt;te href=150906&gt;Lumiflow&lt;/te&gt;&lt;/color&gt;, tốc độ trượt patin của Lynae tăng thêm. &lt;color=Highlight&gt;Speed Skating&lt;/color&gt; tiêu hao STA theo thời gian.</t>
+Trong &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt;:
+- Hồi phục 20% &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; mỗi giây khi Lynae di chuyển trên mặt đất/leo trèo, hoặc né thành công trên mặt đất, hoặc trong khoảng thời gian nhất định khi sử dụng &lt;color=Highlight&gt;Diễu Hành Sắc Màu - Basic Attack&lt;/color&gt;, &lt;color=Highlight&gt;Diễu Hành Sắc Màu - Heavy Attack Trên Mặt Đất&lt;/color&gt;, &lt;color=Highlight&gt;Diễu Hành Sắc Màu - Heavy Attack Giữa Không Trung&lt;/color&gt;, &lt;color=Highlight&gt;Diễu Hành Sắc Màu - Dodge Counter Tránh&lt;/color&gt;, &lt;color=Highlight&gt;Màu Bổ Sung&lt;/color&gt;, né tránh trên mặt đất, Kỹ Năng Khởi Động, hoặc &lt;color=Highlight&gt;Basic Attack - Hướng Tới Ngày Mai Rực Rỡ!&lt;/color&gt;.
+- &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; bắt đầu giảm 20% mỗi giây khi Lynae đứng yên trên mặt đất/leo trèo/bơi lội hoặc rời khỏi chiến trường, hoặc sau một khoảng thời gian nhất định sau khi sử dụng các kỹ năng trên.
+- &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt; không thay đổi khi Lynae không ở trong bất kỳ trạng thái nào kể trên.
+Thoát khỏi &lt;color=Highlight&gt;Diễu Hành Sắc Màu&lt;/color&gt; sẽ xóa toàn bộ &lt;color=Highlight&gt;Dòng Sáng&lt;/color&gt;.
+Với 120 điểm &lt;color=Highlight&gt;&lt;te href=150906&gt;Dòng Sáng&lt;/te&gt;&lt;/color&gt;, tốc độ trượt patin của Lynae tăng thêm. &lt;color=Highlight&gt;Trượt Tốc Độ&lt;/color&gt; tiêu hao STA theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       <c r="M166" t="inlineStr">
         <is>
           <t>Tối đa 3 điểm.
-Trong chiến đấu, mỗi lần sử dụng &lt;color=Highlight&gt;Polychrome Leap&lt;/color&gt; sẽ nhận được 1 điểm &lt;color=Highlight&gt;True Color&lt;/color&gt;. Khi tích đủ 3 điểm &lt;color=Highlight&gt;True Color&lt;/color&gt;, &lt;color=Highlight&gt;Basic Attack - Iridescent Splash&lt;/color&gt; và &lt;color=Highlight&gt;Basic Attack - Visual Impact&lt;/color&gt; sẽ được kích hoạt.
+Trong chiến đấu, mỗi lần sử dụng &lt;color=Highlight&gt;Polychrome Leap&lt;/color&gt; sẽ nhận được 1 điểm &lt;color=Highlight&gt;True Color&lt;/color&gt;. Khi tích đủ 3 điểm &lt;color=Highlight&gt;True Color&lt;/color&gt;, &lt;color=Highlight&gt;Đòn Cơ Bản - Iridescent Splash&lt;/color&gt; và &lt;color=Highlight&gt;Đòn Cơ Bản - Visual Impact&lt;/color&gt; sẽ được kích hoạt.
 Thoát khỏi &lt;color=Highlight&gt;Kaleidoscopic Parade&lt;/color&gt; sẽ xóa toàn bộ &lt;color=Highlight&gt;True Color&lt;/color&gt;.</t>
         </is>
       </c>
@@ -11560,9 +11560,9 @@
       <c r="M167" t="inlineStr">
         <is>
           <t>Phrolova có thể giữ tối đa 6 &lt;color=Highlight&gt;Âm Giai Bất Định&lt;/color&gt;. Khi &lt;color=Highlight&gt;Âm Giai Bất Định&lt;/color&gt; đạt số lượng tối đa, tất cả sẽ dịch chuyển một ô sang trái, và &lt;color=Highlight&gt;Âm Giai Bất Định - Dây&lt;/color&gt; hoặc &lt;color=Highlight&gt;Âm Giai Bất Định - Gió&lt;/color&gt; ở ô ngoài cùng bên trái sẽ bị loại bỏ.
-Tấn công mục tiêu bằng &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; hoặc &lt;color=Highlight&gt;Điệu Nhảy Fate và Tận Cùng&lt;/color&gt; sẽ nhận được 1 &lt;color=Highlight&gt;Âm Giai Bất Định - Dây&lt;/color&gt;.
+Tấn công mục tiêu bằng &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 3&lt;/color&gt; hoặc &lt;color=Highlight&gt;Điệu Nhảy Định Mệnh và Tận Cùng&lt;/color&gt; sẽ nhận được 1 &lt;color=Highlight&gt;Âm Giai Bất Định - Dây&lt;/color&gt;.
 Tấn công mục tiêu bằng Resonance Skill &lt;color=Highlight&gt;Lời Thì Thầm Trong Giấc Mơ Phù Du&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Lời Thì Thầm Trong Giấc Mơ Kinh Hoàng&lt;/color&gt; sẽ nhận được 1 &lt;color=Highlight&gt;Âm Giai Bất Định - Gió&lt;/color&gt;.
-Khi &lt;color=Highlight&gt;Inherent Skill - Ngẫu Nhiên&lt;/color&gt; được kích hoạt, sử dụng Bộ Kỹ Năng Tĩnh Lặng, Bộ Kỹ Năng Bất Tử hoặc Kỹ Năng Vọng Âm sẽ biến Âm Giai Bất Định tiếp theo thành &lt;color=Highlight&gt;Âm Giai Bất Định - Khúc Kết&lt;/color&gt;.
+Khi &lt;color=Highlight&gt;Kỹ Năng Nội Tại - Ngẫu Nhiên&lt;/color&gt; được kích hoạt, sử dụng Bộ Kỹ Năng Tĩnh Lặng, Bộ Kỹ Năng Bất Tử hoặc Kỹ Năng Vọng Âm sẽ biến Âm Giai Bất Định tiếp theo thành &lt;color=Highlight&gt;Âm Giai Bất Định - Khúc Kết&lt;/color&gt;.
 Phrolova không thể nhận &lt;color=Highlight&gt;Âm Giai Bất Định&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Giải Hợp Âm&lt;/color&gt;.</t>
         </is>
       </c>
@@ -11629,8 +11629,8 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Phrolova bước vào trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Scarlet Coda&lt;/color&gt;.
-Khi ở trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;, &lt;color=Highlight&gt;Waltz of Forsaken Depths&lt;/color&gt; sẽ được kích hoạt.</t>
+          <t>Phrolova bước vào trạng thái &lt;color=Highlight&gt;Giải Hợp Âm&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Khúc Kết Đỏ Thẫm&lt;/color&gt;.
+Khi ở trạng thái &lt;color=Highlight&gt;Giải Hợp Âm&lt;/color&gt;, &lt;color=Highlight&gt;Điệu Valse Vực Sâu Vô Định&lt;/color&gt; sẽ được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>Tối đa {0} lượt.
-Khi Phrolova không ở trên chiến trường, sử dụng &lt;color=Highlight&gt;Enhanced Attack - Hecate: Strings&lt;/color&gt;, &lt;color=Highlight&gt;Enhanced Attack - Hecate: Winds&lt;/color&gt; và &lt;color=Highlight&gt;Enhanced Attack - Hecate: Cadenza&lt;/color&gt; sẽ nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lượt P=lượt} Aftersound.
+Khi Phrolova không ở trên chiến trường, sử dụng &lt;color=Highlight&gt;Tấn Công Cường Hóa - Hecate: Strings&lt;/color&gt;, &lt;color=Highlight&gt;Tấn Công Cường Hóa - Hecate: Winds&lt;/color&gt; và &lt;color=Highlight&gt;Tấn Công Cường Hóa - Hecate: Cadenza&lt;/color&gt; sẽ nhận được &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lượt P=lượt} Aftersound.
 Khi Phrolova rời khỏi trạng thái chiến đấu, tất cả lượt Aftersound sẽ bị xóa sau mỗi {2} giây.</t>
         </is>
       </c>
@@ -11766,9 +11766,9 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Tăng {1} Tấn Công.
+          <t>Tăng {1} ATK.
 Phrolova lơ lửng trên không và ra lệnh cho Hecate chiến đấu. Hecate sẽ thừa hưởng chỉ số và trạng thái của Phrolova, và sát thương gây ra bởi Hecate sẽ được tính là đến từ Phrolova.
-Trong thời gian này, Phrolova sẽ lần lượt trình diễn các &lt;color=Highlight&gt;Volatile Notes&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Volatile Ghi chú&lt;/color&gt; duy trì trong {0} giây.</t>
+Trong thời gian này, Phrolova sẽ lần lượt trình diễn các &lt;color=Highlight&gt;Nốt Nhạc Bất Định&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Nốt Nhạc Bất Định&lt;/color&gt; duy trì trong {0} giây.</t>
         </is>
       </c>
     </row>
@@ -11837,11 +11837,11 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Movement of Fate and Finality&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;Reincarnate&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất để thi triển &lt;color=Highlight&gt;Movement of Fate and Finality&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; (được tính là &lt;color=Highlight&gt;Resonance Skill DMG&lt;/color&gt;), khiến mục tiêu bị Trì Tĩnh và kết thúc &lt;color=Highlight&gt;Reincarnate&lt;/color&gt; ngay sau đó.
+          <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Điệu Vận Mệnh và Tận Cùng&lt;/color&gt;&lt;/size&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất để thi triển &lt;color=Highlight&gt;Điệu Vận Mệnh và Tận Cùng&lt;/color&gt;, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; (được tính là &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt;), khiến mục tiêu bị Trì Tĩnh và kết thúc &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt; ngay sau đó.
 &lt;size=10&gt;&lt;/size&gt;
-&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Murmurs in a Haunting Dream&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái &lt;color=Highlight&gt;Reincarnate&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trên mặt đất để thi triển &lt;color=Highlight&gt;Murmurs in a Haunting Dream&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; (được tính là &lt;color=Highlight&gt;Resonance Skill DMG&lt;/color&gt;) và kết thúc &lt;color=Highlight&gt;Reincarnate&lt;/color&gt; ngay sau đó.</t>
+&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Lời Thì Thầm Trong Giấc Mơ U Minh&lt;/color&gt;&lt;/size&gt;
+Khi ở trạng thái &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trên mặt đất để thi triển &lt;color=Highlight&gt;Lời Thì Thầm Trong Giấc Mơ U Minh&lt;/color&gt;, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; (được tính là &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt;) và kết thúc &lt;color=Highlight&gt;Hóa Thân&lt;/color&gt; ngay sau đó.</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tất cả Resonators trong đội hồi phục HP bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng mỗi giây trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;.</t>
+          <t>Tất cả Resonator trong đội hồi phục HP bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; HP tối đa của người sử dụng mỗi giây trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tăng đáng kể Tốc Độ Di Chuyển.</t>
+          <t>Tăng mạnh tốc độ di chuyển.</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator, có thể chồng chất tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần. Hiệu ứng này có thể kích hoạt mỗi giây một lần, kéo dài trong &lt;color=Highlight&gt;{2}s&lt;/color&gt;.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator, có thể chồng chất tối đa &lt;color=Highlight&gt;{1}&lt;/color&gt; lần. Hiệu ứng này có thể kích hoạt mỗi giây một lần, kéo dài trong &lt;color=Highlight&gt;{2} giây&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công của Resonator.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nhận &lt;color=Highlight&gt;{0}&lt;/color&gt; Thêm Sát Thương Toàn Bộ trong &lt;color=Highlight&gt;{1}s&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
+          <t>Nhận &lt;color=Highlight&gt;{0}&lt;/color&gt; Thêm Sát Thương Toàn Bộ trong &lt;color=Highlight&gt;{1} giây&lt;/color&gt;, tối đa &lt;color=Highlight&gt;{2}&lt;/color&gt; tầng.</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; của Shield hiện tại.</t>
+          <t>Gây DMG bằng &lt;color=Highlight&gt;{0}&lt;/color&gt; của Khiên hiện tại.</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Immune sát thương Stability.</t>
+          <t>Miễn nhiễm DMG Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Gây sát thương lên các mục tiêu xung quanh bằng {0} HP tối đa của người sử dụng.</t>
+          <t>Gây DMG lên các mục tiêu xung quanh bằng {0} HP tối đa của người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Terminal hình đèn lồng được Resonators từ Land of Echoes sử dụng. Ban đầu là món quà của Sentinel Imperator tặng cho người dân Rinascita, giờ đây nó đã trở thành ngọn hải đăng dẫn đường cho họ.</t>
+          <t>Thiết bị đầu cuối hình đèn lồng được các Resonator từ Vùng Đất Tiếng Vọng sử dụng. Ban đầu là món quà của Sentinel Imperator tặng cho người dân Rinascita, giờ đây nó đã trở thành ngọn hải đăng dẫn đường cho họ.</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Terminal hình đèn lồng được Resonators từ Land of Echoes sử dụng. Ban đầu là món quà của Sentinel Imperator tặng cho người dân Rinascita, giờ đây nó đã trở thành ngọn hải đăng dẫn đường cho họ.</t>
+          <t>Thiết bị đầu cuối hình đèn lồng được các Resonator từ Vùng Đất Tiếng Vọng sử dụng. Ban đầu là món quà của Sentinel Imperator tặng cho người dân Rinascita, giờ đây nó đã trở thành ngọn hải đăng dẫn đường cho họ.</t>
         </is>
       </c>
     </row>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Terminal này đã thuộc về ngươi từ lần đầu tỉnh dậy. Bề ngoài giống với các Pangu Terminal của Huanglong, nó đã ghi lại từng bước hành trình của ngươi và luôn là người bạn đồng hành thầm lặng, đáng tin cậy.</t>
+          <t>Thiết bị đầu cuối này đã thuộc về ngươi từ lần đầu tỉnh dậy. Bề ngoài giống với các Thiết bị đầu cuối Pangu của Huanglong, nó đã ghi lại từng bước hành trình của ngươi và luôn là người bạn đồng hành thầm lặng, đáng tin cậy.</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; và &lt;color=Fire&gt;Fusion RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; và &lt;color=Fire&gt;Fusion&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và &lt;color=Wind&gt;Aero&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Thunder&gt;Electro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Kẻ địch bị giảm &lt;color=Dark&gt;Havoc RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; 10%, đồng thời tăng &lt;color=Light&gt;Spectro RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; 10%.</t>
+          <t>Kẻ địch bị giảm &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; và &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; 10%, đồng thời tăng &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; và &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; 10%.</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; và &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Ice&gt;Glacio&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=Dark&gt;Havoc RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt;, đồng thời &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Thunder&gt;Electro RES&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=Dark&gt;giảm 10% Kháng Havoc&lt;/color&gt; và &lt;color=Light&gt;Kháng Spectro&lt;/color&gt;, đồng thời &lt;color=Ice&gt;tăng 10% Kháng Glacio&lt;/color&gt; và &lt;color=Thunder&gt;Kháng Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Wind&gt;Aero&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Kẻ địch bị giảm &lt;color=Dark&gt;Havoc RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; 10%, đồng thời tăng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; 10%.</t>
+          <t>Kẻ địch bị giảm &lt;color=Dark&gt;Kháng Havoc&lt;/color&gt; và &lt;color=Wind&gt;Kháng Aero&lt;/color&gt; 10%, đồng thời tăng &lt;color=Ice&gt;Kháng Glacio&lt;/color&gt; và &lt;color=Light&gt;Kháng Spectro&lt;/color&gt; 10%.</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Dark&gt;Havoc RES&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và kháng &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch giảm 10%, trong khi kháng &lt;color=Dark&gt;Havoc&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; và kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; và kháng &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Ice&gt;Glacio RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và &lt;color=Ice&gt;Glacio&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -14116,7 +14116,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Khi Resonators sử dụng Intro Skill, Tấn Công của họ tăng 20% trong 15 giây. Khi sử dụng Resonance Skill, sát thương Resonance Liberation của họ tăng 30% trong 5 giây. Kích hoạt lại các hiệu ứng này sẽ làm mới thời gian.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Intro, ATK của họ tăng 20% trong 15 giây. Khi sử dụng Resonance Skill, DMG Resonance Liberation của họ tăng 30% trong 5 giây. Kích hoạt lại các hiệu ứng này sẽ làm mới thời gian.</t>
         </is>
       </c>
     </row>
@@ -14181,7 +14181,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu bằng Heavy Attack sẽ gây 2 lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi 2 giây. Mỗi lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; sẽ khiến mục tiêu chịu thêm 5% sát thương.</t>
+          <t>Đánh trúng mục tiêu bằng Đòn Heavy Attack sẽ gây 2 lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;. Hiệu ứng này chỉ kích hoạt một lần mỗi 2 giây. Mỗi lớp &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; sẽ khiến mục tiêu chịu thêm 5% DMG.</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Khi Resonators thực hiện Heavy Attack, Attack của tất cả Resonators trong đội tăng 10% và Sát Thương Basic Attack tăng 10% trong 18 giây, có thể tích lũy tối đa 3 lần. Thời gian duy trì hiệu ứng sẽ được làm mới với mỗi tầng mới.</t>
+          <t>Khi Resonator thực hiện Đòn Heavy Attack, ATK của tất cả Resonator trong đội tăng 10% và Sát Thương Đòn Cơ Bản tăng 10% trong 18 giây, có thể tích lũy tối đa 3 lần. Thời gian duy trì hiệu ứng sẽ được làm mới với mỗi tầng mới.</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14311,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Khi bất kỳ Resonators nào nhận hồi máu, Tấn Công của tất cả Resonators trong đội tăng 30% trong 20 giây. Khi Resonators có khiên, Crit. DMG của họ tăng thêm 30%.</t>
+          <t>Khi bất kỳ Resonator nào nhận hồi máu, ATK của tất cả Resonator trong đội tăng 30% trong 20 giây. Khi Resonator có khiên, Crit. DMG của họ tăng thêm 30%.</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi Resonators kích hoạt Resonance Liberation, Crit. DMG của họ tăng 4%, và họ nhận thêm 8% thưởng Sát Thương Resonance Skill trong 3 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng sẽ biến mất khi Resonators hiện tại rời khỏi chiến trường.</t>
+          <t>Khi Resonator kích hoạt Resonance Liberation, Crit. DMG của họ tăng 4%, và họ nhận thêm 8% thưởng Sát Thương Resonance Skill trong 3 giây, có thể chồng chất tối đa 4 lần. Hiệu ứng sẽ biến mất khi Resonator hiện tại rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14441,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Khuếch Đại DMG Tấn Công Phối Hợp</t>
+          <t>Khuếch đại DMG tấn công phối hợp</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Tăng cường Sát Thương Attack Phối Hợp cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Tấn Công Phối Hợp cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Glacio RES của Chủ Echo giảm 15%</t>
+          <t>Kháng Glacio của Chủ Echo giảm 15%</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Glacio RES của Chủ Echo tăng 40%</t>
+          <t>Kháng Glacio của Chủ Echo tăng 40%</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Fusion RES của Chủ Echo giảm 15%</t>
+          <t>Kháng Fusion của Chủ Echo giảm 15%</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Fusion RES của Chủ Echo tăng 40%</t>
+          <t>Kháng Fusion của Chủ Echo tăng 40%</t>
         </is>
       </c>
     </row>
@@ -14831,7 +14831,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Electro RES của Chủ Echo giảm 15%</t>
+          <t>Kháng Electro của Chủ Echo giảm 15%</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Electro RES của Chủ Echo tăng 40%</t>
+          <t>Kháng Electro của Chủ Echo tăng 40%</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Aero RES của Chủ Echo giảm 15%</t>
+          <t>Kháng Aero của Chủ Echo giảm 15%</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Aero RES của Chủ Echo tăng 40%</t>
+          <t>Kháng Aero của Chủ Echo tăng 40%</t>
         </is>
       </c>
     </row>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Havoc RES của Chủ Echo giảm 15%</t>
+          <t>Kháng Havoc của Chủ Echo giảm 15%</t>
         </is>
       </c>
     </row>
@@ -15481,7 +15481,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tấn Công của Chủ Echo tăng 10%</t>
+          <t>ATK của Chủ Tiếng Vọng tăng 10%</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Tấn Công của Chủ Echo tăng 15%</t>
+          <t>ATK của Chủ Tiếng Vọng tăng 15%</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Tấn Công của Chủ Echo tăng 20%</t>
+          <t>ATK của Chủ Echo tăng 20%</t>
         </is>
       </c>
     </row>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Vật liệu Vũ khí và Kỹ năng</t>
+          <t>Nguyên Liệu Vũ Khí và Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Luyện tập Kỹ năng</t>
+          <t>Huấn Luyện Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Materials Kỹ Năng Nâng Cao</t>
+          <t>Vật Liệu Kỹ Năng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Nhân Vật đều là &lt;color=#1891e7&gt;Glacio&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Glacio Concerto&lt;/color&gt; sẽ được kích hoạt, gây &lt;color=#1891e7&gt;Glacio&lt;/color&gt; lên mục tiêu.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Nhân Vật đều là &lt;color=#1891e7&gt;Glacio&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Glacio Concerto&lt;/color&gt; sẽ được kích hoạt, gây &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt; lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15937,8 +15937,8 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Kích hoạt Concerto Effect khi cả hai Resonator có Thuộc Tính lần lượt là &lt;color=#1891e7&gt;Hot and Cold Ensemble&lt;/color&gt; và &lt;color=#e15226&gt;Glacio&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Fusion&lt;/color&gt;.
-Sát Thương Giải Phóng Đồng Điệu của Resonator ra mắt sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không ra mắt.</t>
+          <t>Kích hoạt Hiệu Ứng Concerto khi cả hai Cộng Hưởng Giả có Thuộc Tính lần lượt là &lt;color=#e15226&gt;Glacio&lt;/color&gt; và &lt;color=#1891e7&gt;Fusion&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Bộ Hợp Khí Nóng Lạnh&lt;/color&gt;.
+Sát Thương Giải Phóng Đồng Điệu của Cộng Hưởng Giả ra mắt sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không ra mắt.</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu cả hai Resonator đều có thuộc tính &lt;color=#e15226&gt;Fusion&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Fusion flurry&lt;/color&gt;, gây sát thương &lt;color=#e15226&gt;Fusion&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu cả hai Cộng Hưởng Giả đều có thuộc tính &lt;color=#e15226&gt;Fusion&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cuồng Phong Fusion&lt;/color&gt;, gây DMG &lt;color=#e15226&gt;Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16069,8 +16069,8 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#9656d8&gt;Electro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cold and Electric Ensemble&lt;/color&gt;.
-Basic Attack và Heavy Attack của Resonator ra mắt sẽ gây &lt;color=#8c7e51&gt;40% more damage&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không phải là người ra mắt.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Cộng Hưởng Giả lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#9656d8&gt;Electro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Hợp Tấu Lạnh Điện&lt;/color&gt;.
+Basic Attack và Heavy Attack của Cộng Hưởng Giả ra mắt sẽ gây &lt;color=#8c7e51&gt;nhiều hơn 40% sát thương&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không phải là người ra mắt.</t>
         </is>
       </c>
     </row>
@@ -16136,8 +16136,8 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Kích hoạt Concerto Effect khi cả hai Resonator có Thuộc Tính lần lượt là &lt;color=#e15226&gt;Thermoelectric Ensemble&lt;/color&gt; và &lt;color=#9656d8&gt;Fusion&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Electro&lt;/color&gt;.
-Sát Thương Kỹ Năng Đồng Điệu của Resonator ra mắt sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không ra mắt.</t>
+          <t>Kích hoạt Hiệu Ứng Concerto khi cả hai Cộng Hưởng Giả có Thuộc Tính lần lượt là &lt;color=#9656d8&gt;Fusion&lt;/color&gt; và &lt;color=#e15226&gt;Electro&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Bộ Hợp Khí Nhiệt Điện&lt;/color&gt;.
+Sát Thương Kỹ Năng Đồng Điệu của Cộng Hưởng Giả ra mắt sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không ra mắt.</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu cả hai Resonator đều có thuộc tính &lt;color=#9656d8&gt;Electro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Electro flurry&lt;/color&gt;, gây sát thương &lt;color=#9656d8&gt;Electro&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu cả hai Cộng Hưởng Giả đều có thuộc tính &lt;color=#9656d8&gt;Electro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cuồng Phong Electro&lt;/color&gt;, gây sát thương &lt;color=#9656d8&gt;Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16268,8 +16268,8 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Kích hoạt Concerto Effect khi cả hai Resonator có Thuộc Tính lần lượt là &lt;color=#46c3d4&gt;Air Cold Ensemble&lt;/color&gt; và &lt;color=#1891e7&gt;Aero&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Glacio&lt;/color&gt;.
-Sát Thương Kỹ Năng Đồng Điệu của Resonator đang lên máy sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không lên máy.</t>
+          <t>Kích hoạt Hiệu Ứng Concerto khi cả hai Cộng Hưởng Giả có Thuộc Tính lần lượt là &lt;color=#1891e7&gt;Aero&lt;/color&gt; và &lt;color=#46c3d4&gt;Glacio&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Bộ Hợp Khí Lạnh Gió&lt;/color&gt;.
+Sát Thương Kỹ Năng Đồng Điệu của Cộng Hưởng Giả đang lên máy sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không lên máy.</t>
         </is>
       </c>
     </row>
@@ -16335,8 +16335,8 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#46c3d4&gt;Aero&lt;/color&gt; và &lt;color=#e15226&gt;Fusion&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Aerothermal Ensemble&lt;/color&gt;.
-Basic Attack và Heavy Attack của Resonator ra mắt sẽ tăng &lt;color=#8c7e51&gt;40% sát thương&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không phải là người ra mắt.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Cộng Hưởng Giả lần lượt là &lt;color=#46c3d4&gt;Aero&lt;/color&gt; và &lt;color=#e15226&gt;Fusion&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Hợp Tấu Nhiệt Phong&lt;/color&gt;.
+Basic Attack và Heavy Attack của Cộng Hưởng Giả ra mắt sẽ tăng &lt;color=#8c7e51&gt;40% sát thương&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không phải là người ra mắt.</t>
         </is>
       </c>
     </row>
@@ -16402,8 +16402,8 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Kích hoạt Concerto Effect khi cả hai Resonator có Thuộc Tính lần lượt là &lt;color=#9656d8&gt;Electro Ensemble&lt;/color&gt; và &lt;color=#46c3d4&gt;Electro&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Aero&lt;/color&gt;.
-Sát Thương Giải Phóng Đồng Điệu của Resonator đang lên máy sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Resonator không lên máy.</t>
+          <t>Kích hoạt Hiệu Ứng Concerto khi cả hai Cộng Hưởng Giả có Thuộc Tính lần lượt là &lt;color=#46c3d4&gt;Electro&lt;/color&gt; và &lt;color=#9656d8&gt;Aero&lt;/color&gt; sẽ kích hoạt &lt;color=#8c7e51&gt;Bộ Hợp Khí Điện Gió&lt;/color&gt;.
+Sát Thương Giải Phóng Đồng Điệu của Cộng Hưởng Giả đang lên máy sẽ tăng &lt;color=#8c7e51&gt;40%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây. Hiệu ứng không có tác dụng nếu Cộng Hưởng Giả không lên máy.</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu cả hai Resonator đều có thuộc tính &lt;color=#46c3d4&gt;Aero&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Aero flurry&lt;/color&gt;, gây sát thương &lt;color=#46c3d4&gt;Aero&lt;/color&gt; lên mục tiêu.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu cả hai Cộng Hưởng Giả đều có thuộc tính &lt;color=#46c3d4&gt;Aero&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cuồng Phong Aero&lt;/color&gt;, gây sát thương &lt;color=#46c3d4&gt;Aero&lt;/color&gt; lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -16534,8 +16534,8 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Glacio extension&lt;/color&gt;.
-Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Resonator ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Cộng Hưởng Giả lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Kéo Dài Glacio&lt;/color&gt;.
+Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Cộng Hưởng Giả ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Character lần lượt là &lt;color=#e15226&gt;Fusion&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Fusion extension&lt;/color&gt; sẽ tạo ra hiệu ứng ngưng động diện rộng trong thời gian ngắn và Character ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Nhân Vật lần lượt là &lt;color=#e15226&gt;Fusion&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, thì &lt;color=#8c7e51&gt;phần mở rộng Fusion&lt;/color&gt; sẽ tạo ra hiệu ứng ngưng động diện rộng trong thời gian ngắn và Nhân Vật ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16667,8 +16667,8 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#9656d8&gt;Electro&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Electro extension&lt;/color&gt;.
-Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Resonator ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Cộng Hưởng Giả lần lượt là &lt;color=#9656d8&gt;Electro&lt;/color&gt; và &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Kéo Dài Electro&lt;/color&gt;.
+Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Cộng Hưởng Giả ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16734,8 +16734,8 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Character lần lượt là &lt;color=#46c3d4&gt;Aero Delay&lt;/color&gt; và &lt;color=#d4bf5f&gt;Aero&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Spectro&lt;/color&gt; sẽ kích hoạt.
-Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Character ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Nhân Vật lần lượt là &lt;color=#d4bf5f&gt;Aero&lt;/color&gt; và &lt;color=#46c3d4&gt;Spectro&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Aero Delay&lt;/color&gt; sẽ kích hoạt.
+Tạo hiệu ứng ngưng động diện rộng trong thời gian ngắn và Nhân Vật ra mắt nhận được &lt;color=#8c7e51&gt;10&lt;/color&gt; điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Khi hiệu ứng Concerto được kích hoạt, nếu cả hai nhân vật đều thuộc thuộc tính &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Spectro flurry&lt;/color&gt;, gây sát thương &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;.</t>
+          <t>Khi hiệu ứng Concerto được kích hoạt, nếu cả hai nhân vật đều thuộc thuộc tính &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Spectro cuồng phong&lt;/color&gt;, gây sát thương &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16866,8 +16866,8 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonators lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Glacio Continuum&lt;/color&gt; sẽ kích hoạt.
-Sát thương từ Resonance Skill của Resonators mới vào tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi chuyển đổi Resonators, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#1891e7&gt;Glacio&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Glacio Continuum&lt;/color&gt; sẽ kích hoạt.
+Sát thương từ Resonance Skill của Resonator mới vào tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi chuyển đổi Resonator, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16933,8 +16933,8 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonators lần lượt là &lt;color=#e15226&gt;Fusion&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Fusion Continuum&lt;/color&gt; sẽ kích hoạt.
-Sát thương từ Resonance Skill của Resonators mới vào tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi chuyển đổi Resonators, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#e15226&gt;Fusion&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Fusion Continuum&lt;/color&gt; sẽ kích hoạt.
+Sát thương từ Resonance Skill của Resonator mới vào tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi chuyển đổi Resonator, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#9656d8&gt;Electro&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Electro continuum&lt;/color&gt;.
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#9656d8&gt;Electro&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Tiếp Nối Electro&lt;/color&gt;.
 Sát thương từ Resonance Skill của Resonator tiếp theo sẽ tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi ở trạng thái chưa đăng ký, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
@@ -17067,8 +17067,8 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Character lần lượt là &lt;color=#46c3d4&gt;Aero Consonance&lt;/color&gt; và &lt;color=#7e1f57&gt;Aero&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Havoc&lt;/color&gt; sẽ được kích hoạt.
-Sát thương từ Resonance Skill của Character ra mắt tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi ở trạng thái chưa đăng ký, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Nhân Vật lần lượt là &lt;color=#7e1f57&gt;Aero&lt;/color&gt; và &lt;color=#46c3d4&gt;Havoc&lt;/color&gt;, thì &lt;color=#8c7e51&gt;Aero Consonance&lt;/color&gt; sẽ được kích hoạt.
+Sát thương từ Resonance Skill của Nhân Vật ra mắt tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;15&lt;/color&gt; giây. Hiệu ứng không mất đi khi ở trạng thái chưa đăng ký, và sát thương từ Resonance Skill sẽ tăng thêm &lt;color=#8c7e51&gt;20%&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu thuộc tính của hai Resonator lần lượt là &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Diphase Replay&lt;/color&gt;.
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu thuộc tính của hai Cộng Hưởng Giả lần lượt là &lt;color=#d4bf5f&gt;Spectro&lt;/color&gt; và &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Tái Hiện Lưỡng Pha&lt;/color&gt;.
 Sát thương thuộc tính của toàn đội sẽ tăng &lt;color=#8c7e51&gt;20%&lt;/color&gt; trong &lt;color=#8c7e51&gt;12&lt;/color&gt; giây.</t>
         </is>
       </c>
@@ -17200,7 +17200,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Khi Concerto Effect được kích hoạt, nếu cả hai Resonator đều có thuộc tính &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cuồng Phong Havoc&lt;/color&gt;, gây sát thương &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;.</t>
+          <t>Khi Hiệu Ứng Concerto được kích hoạt, nếu cả hai Cộng Hưởng Giả đều có thuộc tính &lt;color=#7e1f57&gt;Havoc&lt;/ color&gt;, nó sẽ kích hoạt &lt;color=#8c7e51&gt;Cuồng Phong Havoc&lt;/color&gt;, gây sát thương &lt;color=#7e1f57&gt;Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Điểm Dẫn Đường, hay còn gọi là Đèn Hiệu tạm thời, sử dụng dữ liệu từ các Đèn Hiệu cố định gần đó để đánh dấu vị trí tạm thời. Với chức năng tương tự Đèn Hiệu Resonance nhưng linh hoạt hơn, chúng là công cụ đắc lực cho những ai hoạt động ngoài thực địa.</t>
+          <t>Điểm Dẫn Đường, hay còn gọi là Đèn Hiệu tạm thời, sử dụng dữ liệu từ các Đèn Hiệu cố định gần đó để đánh dấu vị trí tạm thời. Với chức năng tương tự Đèn Hiệu Cộng Hưởng nhưng linh hoạt hơn, chúng là công cụ đắc lực cho những ai hoạt động ngoài thực địa.</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Theo dấu Kẻ địch</t>
+          <t>Theo Dõi Kẻ Địch</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Kẻ Địch Mới</t>
+          <t>Kẻ Thù Mới</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Vật liệu Vũ khí và Kỹ năng</t>
+          <t>Nguyên Liệu Vũ Khí và Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng: Rectifier</t>
+          <t>Vật liệu Nâng Cấp Vũ Khí &amp; Kỹ Năng: Bộ chỉnh lưu</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng: Broadblade</t>
+          <t>Nguyên Liệu Vũ Khí và Kỹ Năng: Kiếm Rộng</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng: Gauntlets</t>
+          <t>Vật liệu Nâng Cấp Vũ Khí &amp; Kỹ Năng: Quả đấm</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Vật Liệu Vũ Khí và Kỹ Năng: Pistols</t>
+          <t>Vật liệu Nâng Cấp Vũ Khí &amp; Kỹ Năng: Súng ngắn</t>
         </is>
       </c>
     </row>
@@ -17980,7 +17980,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Đánh bại 1 kẻ địch cấp Overlord</t>
+          <t>Đánh bại 1 kẻ địch Cấp Chúa Tể</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Đánh bại 1 kẻ địch cấp Calamity</t>
+          <t>Đánh bại 1 kẻ địch Cấp Thảm Họa</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đánh bại tổng cộng 15 kẻ địch</t>
+          <t>Hạ gục tổng cộng 15 kẻ địch</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Thực hiện Intro Skill tổng cộng 3 lần.</t>
+          <t>Thực hiện Kỹ Năng Intro tổng cộng 3 lần.</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Difficulty: {0}</t>
+          <t>Độ Khó: {0}</t>
         </is>
       </c>
     </row>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>{0} Unlocked</t>
+          <t>{0} Đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Khu vực mục tiêu đã bị khóa</t>
+          <t>Đã khoá khu vực mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Khu vực mục tiêu đã bị khoá. Vui lòng hoàn thành Main Quests.</t>
+          <t>Khu vực mục tiêu đã bị khoá. Vui lòng hoàn thành Nhiệm Vụ Chính.</t>
         </is>
       </c>
     </row>
@@ -18695,7 +18695,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Resonators bỏ qua 25% Phòng Ngự của kẻ địch khi gây sát thương. Khi kẻ địch bị Trạng Thái Tiêu Cực, sát thương nhận vào sẽ tăng 20%.</t>
+          <t>Resonator bỏ qua 25% Phòng Ngự của kẻ địch khi gây DMG. Khi kẻ địch bị Trạng Thái Tiêu Cực, DMG nhận vào sẽ tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Khi Resonator sử dụng Intro Skill, họ sẽ nhận được một Lá Chắn có 3000 HP. Khi Resonator nhận Lá Chắn, Crit. DMG của họ sẽ tăng 10% trong 30 giây, có thể chồng chất tối đa 5 lần.</t>
+          <t>Khi Resonator sử dụng Kỹ Năng Khởi Động, họ sẽ nhận được một Lá Chắn có 3000 HP. Khi Resonator nhận Lá Chắn, Crit. DMG của họ sẽ tăng 10% trong 30 giây, có thể chồng chất tối đa 5 lần.</t>
         </is>
       </c>
     </row>
@@ -18825,7 +18825,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Total Sát Thương tăng 10%. Khi Resonators sử dụng kỹ năng Tune Break, tổng Sát Thương của tất cả Resonators trong đội tăng 10%. Hiệu ứng này có thể kích hoạt mỗi 15 giây và tích lũy tối đa 3 lần. Khi bất kỳ Resonators nào trong đội gây Sát Thương Tune Rupture, tổng Sát Thương của tất cả Resonators trong đội tăng 40% trong 30 giây.</t>
+          <t>Tổng Sát Thương tăng 10%. Khi Resonator sử dụng kỹ năng Tune Break, tổng Sát Thương của tất cả Resonator trong đội tăng 10%. Hiệu ứng này có thể kích hoạt mỗi 15 giây và tích lũy tối đa 3 lần. Khi bất kỳ Resonator nào trong đội gây Sát Thương Tune Rupture, tổng Sát Thương của tất cả Resonator trong đội tăng 40% trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -18890,7 +18890,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Kháng toàn bộ thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi kẻ địch chịu Sát Thương Vỡ Nhạc Tune hoặc Sát Thương Bùng Nổ Hợp Thể.</t>
+          <t>Kháng toàn bộ thuộc tính của kẻ địch tăng 15%. Hiệu ứng này sẽ bị loại bỏ khi kẻ địch chịu Sát Thương Vỡ Nhạc Điệu hoặc Sát Thương Bùng Nổ Hợp Thể.</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Total Sát Thương tăng 10%, và kẻ địch chịu thêm 100% tổng Fusion DMG Burst và 100% tổng Sát Thương Tune Rupture.
+          <t>Tổng Sát Thương tăng 10%, và kẻ địch chịu thêm 100% tổng Sát Thương Fusion Burst và 100% tổng Sát Thương Tune Rupture.
 Khi Resonator sử dụng Tune Break, tổng Sát Thương gây ra của họ tăng thêm 10%. Hiệu ứng này có thể kích hoạt mỗi 15 giây và tích lũy tối đa 3 lần.</t>
         </is>
       </c>
@@ -19022,7 +19022,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Ice&gt;Glacio DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Ice&gt;Tăng Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19087,7 +19087,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Resonators nhận 30% &lt;color=Light&gt;Spectro DMG Bonus&lt;/color&gt;.</t>
+          <t>Resonator nhận 30% &lt;color=Light&gt;Tăng Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; của kẻ địch giảm 10%.</t>
+          <t>Kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; của kẻ địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; của kẻ địch giảm 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; của kẻ địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; của kẻ địch giảm 10%.</t>
+          <t>Kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; của kẻ địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19347,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch giảm 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%.</t>
         </is>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=Dark&gt;Havoc RES&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=Dark&gt;giảm 10% Kháng Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; của kẻ địch tăng 10%.</t>
+          <t>Kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; của kẻ địch tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; của kẻ địch tăng 10%.</t>
+          <t>Kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; của kẻ địch tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19672,7 +19672,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; của kẻ địch tăng 10%.</t>
+          <t>Kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; của kẻ địch tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch tăng 10%.</t>
+          <t>Kháng &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch tăng 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19867,7 +19867,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Kẻ địch &lt;color=Dark&gt;Havoc RES&lt;/color&gt;.</t>
+          <t>Kẻ địch &lt;color=Dark&gt;tăng 10% Kháng Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Wind&gt;Aero&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; và &lt;color=Dark&gt;Havoc RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion RES&lt;/color&gt; và &lt;color=Wind&gt;Aero RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Light&gt;Spectro&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Wind&gt;Aero&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -20062,7 +20062,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Kháng &lt;color=Thunder&gt;Electro RES&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro RES&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Ice&gt;Glacio RES&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc RES&lt;/color&gt; tăng 10%.</t>
+          <t>Kháng &lt;color=Thunder&gt;Electro&lt;/color&gt; và kháng &lt;color=Light&gt;Spectro&lt;/color&gt; của kẻ địch giảm 10%, đồng thời kháng &lt;color=Ice&gt;Glacio&lt;/color&gt; và kháng &lt;color=Dark&gt;Havoc&lt;/color&gt; tăng 10%.</t>
         </is>
       </c>
     </row>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Resonators gây thêm một lần &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; tương đương 80% ATK khi gây sát thương. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Khi gây DMG, Resonator sẽ gây thêm một đòn Sát Thương Havoc tương đương 80% ATK của bản thân. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -20194,9 +20194,9 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>&lt;color=#9656d8&gt;[Electro]&lt;/color&gt;
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; với &lt;color=#9656d8&gt;Electro DMG&lt;/color&gt;.
-Thundering Mephis trông như sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tacet Field để di chuyển tốc độ cao. Nghiên cứu sơ bộ cho thấy nó là kết quả của quá trình tiến hóa tự nhiên của Tacet Discord. Có lời đồn ở Huanglong rằng nó đã nuốt chửng một đôi tình nhân gắn bó cả đời, nếm trải nỗi đau và ý chí chiến đấu của họ, rồi biến đổi thành hình dạng hiện tại trong một cơn giông bão.</t>
+          <t>&lt;color=#9656d8&gt;[Điện]&lt;/color&gt;
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; với &lt;color=#9656d8&gt;Sát Thương Điện&lt;/color&gt;.
+Thundering Mephis trông như sự kết hợp giữa người và thằn lằn. Nó có thể sử dụng Wutheron trong Tổ Tacet để di chuyển tốc độ cao. Nghiên cứu sơ bộ cho thấy nó là kết quả của quá trình tiến hóa tự nhiên của Tacet Discord. Có lời đồn ở Huanglong rằng nó đã nuốt chửng một đôi tình nhân gắn bó cả đời, nếm trải nỗi đau và ý chí chiến đấu của họ, rồi biến đổi thành hình dạng hiện tại trong một cơn giông bão.</t>
         </is>
       </c>
     </row>
@@ -20264,8 +20264,8 @@
       <c r="M300" t="inlineStr">
         <is>
           <t>&lt;color=#e15226&gt;[Fusion]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#e15226&gt;Fusion DMG&lt;/color&gt;. 
-Discord thường không cần "phương tiện" để di chuyển, nhưng hình dạng của Inferno Rider lại giống một tay đua trên xe máy. Có lẽ hình dạng này bắt nguồn từ sự bắt chước vụng về hành vi của con người. Cơn điên cuồng của Discord trên "phương tiện" này được dân Huanglong gọi là "Lửa Giận Dữ". Tuy nhiên, người dân nơi đây cũng nói: "Dù ngọn lửa giận dữ đến đâu, một ngày nó cũng sẽ tắt." Có lẽ Huanglong luôn biết cách khơi dậy hy vọng trong lòng người.&lt;/color&gt;</t>
+Kẻ địch này có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#e15226&gt;Sát Thương Fusion&lt;/color&gt;. 
+Tacet Discord thường không cần "phương tiện" để di chuyển, nhưng hình dạng của Inferno Rider lại giống một tay đua trên xe máy. Có lẽ hình dạng này bắt nguồn từ sự bắt chước vụng về hành vi của con người. Cơn điên cuồng của Tacet Discord trên "phương tiện" này được dân Huanglong gọi là "Lửa Giận Dữ". Tuy nhiên, người dân nơi đây cũng nói: "Dù ngọn lửa giận dữ đến đâu, một ngày nó cũng sẽ tắt." Có lẽ Huanglong luôn biết cách khơi dậy hy vọng trong lòng người.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20333,7 +20333,7 @@
       <c r="M301" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;.
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;.
 Lampylumen Myriad là tập hợp của những Tacet Discord nhỏ giống côn trùng gọi là "Glowflies", cực kỳ nhạy cảm với các tần số âm thanh khác nhau. Chúng có thể xác định vị trí con mồi qua âm thanh hoặc hấp thụ và bắt chước tần số của chúng. À, thiết bị này có thể bắt chước âm thanh của chúng đấy.</t>
         </is>
       </c>
@@ -20402,7 +20402,7 @@
       <c r="M302" t="inlineStr">
         <is>
           <t>&lt;color=#46c3d4&gt;[Aero]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#46c3d4&gt;higher RES&lt;/color&gt; đối với &lt;color=#46c3d4&gt;Aero DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#46c3d4&gt;Kháng cao&lt;/color&gt; đối với &lt;color=#46c3d4&gt;Sát Thương Aero&lt;/color&gt;. 
 Từng là trò tiêu khiển của con người, sau trở thành mục tiêu tấn công và cuối cùng là mối phiền toái, Felilian Beringal bị giam cầm trong rừng. Nhưng nó đã biến cột trói buộc mình thành vũ khí và trở thành kẻ thống trị bầy Hoochief. Giờ đây, nó trút lại những gì con người đã làm lên những kẻ bị khỉ bắt giữ. Vậy... rốt cuộc ai mới là kẻ bị nhốt trong lồng?</t>
         </is>
       </c>
@@ -20471,8 +20471,8 @@
       <c r="M303" t="inlineStr">
         <is>
           <t>&lt;color=#7e1f57&gt;[Havoc]&lt;/color&gt;
-Mục tiêu có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; trước &lt;color=#7e1f57&gt;Havoc DMG&lt;/color&gt;. 
-Một bản sao của "Crownless" đến từ Threnody. Ngoại hình giống một hiệp sĩ mặc giáp trắng, khi sức mạnh tăng lên, nó sẽ xòe đôi cánh đỏ như máu, được cho là kết quả của việc thao túng cấu trúc Wutheron trong cơ thể trong thời gian ngắn, giúp tăng khả năng di chuyển và sức tấn công tức thì. Gần đây, người ta còn phát hiện nó có thể tạo ra cấu trúc cơ thể bắt chước "vũ khí" của con người. Không ai biết nó có thể biến đổi đến mức nào, nhưng chắc chắn một điều: nó thuộc về Havoc, trái ngược hoàn toàn với vẻ ngoài. "Đừng đánh giá Discord qua vẻ bề ngoài", dựa trên một câu thành ngữ của Huanglong.</t>
+Mục tiêu có &lt;color=#b49f50&gt;Kháng cao&lt;/color&gt; trước &lt;color=#7e1f57&gt;Sát Thương Havoc&lt;/color&gt;. 
+Một bản sao của "Crownless" đến từ Threnody. Ngoại hình giống một hiệp sĩ mặc giáp trắng, khi sức mạnh tăng lên, nó sẽ xòe đôi cánh đỏ như máu, được cho là kết quả của việc thao túng cấu trúc Wutheron trong cơ thể trong thời gian ngắn, giúp tăng khả năng di chuyển và sức tấn công tức thì. Gần đây, người ta còn phát hiện nó có thể tạo ra cấu trúc cơ thể bắt chước "vũ khí" của con người. Không ai biết nó có thể biến đổi đến mức nào, nhưng chắc chắn một điều: nó thuộc về Havoc, trái ngược hoàn toàn với vẻ ngoài. "Đừng đánh giá Tacet Discord qua vẻ bề ngoài", dựa trên một câu thành ngữ của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -20540,7 +20540,7 @@
       <c r="M304" t="inlineStr">
         <is>
           <t>&lt;color=#1891e7&gt;[Glacio]&lt;/color&gt; 
-Kẻ địch này có &lt;color=#b49f50&gt;higher RES&lt;/color&gt; đối với &lt;color=#1891e7&gt;Glacio DMG&lt;/color&gt;. 
+Kẻ địch này có &lt;color=#b49f50&gt;kháng cao&lt;/color&gt; đối với &lt;color=#1891e7&gt;Sát Thương Glacio&lt;/color&gt;. 
 Chiếc chuông cổ trên lưng Geochelone che giấu lõi Tacetreite của nó. Khi bị đánh trúng, chuông sẽ cộng hưởng với lõi, tạo ra một làn sóng âm thanh năng lượng Glacio. Lưu ý rằng sóng âm này có thể gây tổn thương vĩnh viễn vùng Broca trong não người, dẫn đến mất ngôn ngữ vĩnh viễn. May mà với công nghệ y học hiện tại, chúng ta có 0.04% cơ hội đảo ngược tổn thương.</t>
         </is>
       </c>
@@ -20608,8 +20608,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; cao hơn. 
-Một Discord hình người sử dụng bộ dụng cụ săn bắn bắn tên sét. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; cao hơn. 
+Một Tacet Discord hình người sử dụng bộ dụng cụ săn bắn bắn tên sét. 
 Những cú giật dây của Electro Predator nhanh như tia chớp đầu xuân. Vùng hoang mạc là bãi săn của nó, và nó tận hưởng niềm vui truy đuổi con mồi.</t>
         </is>
       </c>
@@ -20677,8 +20677,8 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Một Discord hình người sử dụng vũ khí săn bắt đầu bằng băng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Một Tacet Discord hình người sử dụng vũ khí săn bắt đầu bằng băng.
 Những ngọn giáo của Glacio Predators sắc bén như tia chớp xé gió. Vùng đất hoang tàn là bãi săn của chúng, và chúng tận hưởng niềm vui trong việc truy đuổi con mồi.</t>
         </is>
       </c>
@@ -20746,8 +20746,8 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echo hình người sử dụng boomerang bão tố làm vũ khí săn mồi.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tổ Tacet hình người sử dụng boomerang bão tố làm vũ khí săn mồi.
 Boomerang của Kẻ Săn Mồi Aero là một cơn lốc khó lường biến hình trên biển cả. Vùng đất hoang tàn là bãi săn của nó, và nó luôn thích thú với việc truy đuổi con mồi.</t>
         </is>
       </c>
@@ -20815,8 +20815,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord hình người với những lưỡi kiếm mọc ra từ cánh tay.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord hình người với những lưỡi kiếm mọc ra từ cánh tay.
 Khao khát đối thủ mạnh mẽ, nó bùng cháy với tinh thần chiến đấu mãnh liệt như những lưỡi kiếm trên đôi tay.</t>
         </is>
       </c>
@@ -20884,8 +20884,8 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord hình người với đôi lưỡi hái mọc ra từ cánh tay.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord hình người với đôi lưỡi hái mọc ra từ cánh tay.
 Nó thích những đối thủ yếu đuối hơn, bởi chỉ kẻ yếu mới phải chịu đựng những thử thách và bản án của nó.</t>
         </is>
       </c>
@@ -20953,8 +20953,8 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord hình người chưa trưởng thành, rỉ ra những dòng nham thạch nhỏ như thể chúng đang ở điểm sôi sục.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord hình người chưa trưởng thành, rỉ ra những dòng nham thạch nhỏ như thể chúng đang ở điểm sôi sục.
 Khi chiến đấu, nham thạch trên cơ thể chúng bùng lên tia lửa và phát ra âm thanh răng rắc giống như tiếng "lách tách".</t>
         </is>
       </c>
@@ -21021,8 +21021,8 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Discord dạng người chưa trưởng thành, thường phát ra âm thanh "zig zag" khi tập trung và phóng tia sáng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord dạng người chưa trưởng thành, thường phát ra âm thanh "zig zag" khi tập trung và phóng tia sáng.</t>
         </is>
       </c>
     </row>
@@ -21089,8 +21089,8 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echo hình người chưa trưởng thành, lơ lửng trên không nhờ luồng gió. Nó có thể thay đổi tốc độ di chuyển bằng cách hấp thụ khí đơn giản.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tổ Tacet hình người chưa trưởng thành, lơ lửng trên không nhờ luồng gió. Nó có thể thay đổi tốc độ di chuyển bằng cách hấp thụ khí đơn giản.
 Khi thở ra phía sau và tăng tốc, nó thường phát ra âm thanh giống như "vù vù".</t>
         </is>
       </c>
@@ -21157,8 +21157,8 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Discord hình người chưa trưởng thành. Có lẽ bắt chước tiếng cười của con người, chúng luôn phát ra âm thanh "tíc tắc" mỗi khi gặp gỡ loài người.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình người chưa trưởng thành. Có lẽ bắt chước tiếng cười của con người, chúng luôn phát ra âm thanh "tíc tắc" mỗi khi gặp gỡ loài người.</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Loài thủy sinh hình cá phổ biến ở các vùng nước. Gulpuff thường ẩn mình dưới nước, chỉ để chiếc lá sen trên đầu nổi lên mặt nước.
 Khi bị đe dọa, chúng nuốt một lượng nước lớn, phình to người lên và phát ra tiếng kêu ục ục để hù dọa kẻ thù.</t>
         </is>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Aero DMG&lt;/color&gt;&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;&lt;/color&gt; cao hơn.
 Đây là loài cá dạng động vật thủy sinh phân bố rộng rãi ở vùng ven sông, có cấu trúc hoa tảo đặc biệt trên đỉnh sọ và có thể trôi theo gió.
 Khi bị đe dọa, Chirpuff sẽ nhanh chóng phồng khí và phát ra tiếng kêu cảnh báo.</t>
         </is>
@@ -21428,8 +21428,8 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Echo khoáng vật thường xuất hiện trong các mạch quặng. Những tinh thể găm trên thân đá của nó phản chiếu ánh sáng lạnh lẽo.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tổ Tacet khoáng vật thường xuất hiện trong các mạch quặng. Những tinh thể găm trên thân đá của nó phản chiếu ánh sáng lạnh lẽo.
 Dù khả năng chiến đấu khá yếu, nhưng khi bị tiêu diệt, năng lượng nó giải phóng sẽ tăng cường sức mạnh cho các Tacet Discord xung quanh.</t>
         </is>
       </c>
@@ -21497,8 +21497,8 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Echo khoáng vật thường thấy trong các mạch quặng. Bên dưới lớp vỏ đá là dòng nham thạch nóng bỏng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tổ Tacet khoáng vật thường thấy trong các mạch quặng. Bên dưới lớp vỏ đá là dòng nham thạch nóng bỏng.
 Dù khả năng chiến đấu khá yếu, khi bị tiêu diệt, năng lượng nó giải phóng sẽ tăng cường sức mạnh cho các Tacet Discord xung quanh.</t>
         </is>
       </c>
@@ -21566,7 +21566,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Một Tacet Discord khoáng vật thường thấy trong các mạch quặng. Thân đá của nó phát ra ánh sáng chói lòa.
 Dù khả năng chiến đấu khá yếu, nhưng khi bị tiêu diệt, năng lượng nó giải phóng sẽ tăng cường sức mạnh cho các Tacet Discord xung quanh.</t>
         </is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
 Một Tacet Discord khoáng vật thường thấy trong các mạch quặng. Thân thể đá của nó chứa đựng những năng lượng đen tối và sâu thẳm.
 Dù khả năng chiến đấu khá yếu ớt, nhưng khi bị tiêu diệt, năng lượng nó giải phóng sẽ tăng cường sức mạnh cho các Tacet Discord xung quanh.</t>
         </is>
@@ -21703,7 +21703,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Loài sinh vật phù du với thân hình nhẹ nhàng. Chúng có đôi cánh như bướm và rất giỏi vòng quanh kẻ thù bằng những động tác linh hoạt.</t>
         </is>
       </c>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21838,7 +21838,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Loài sinh vật giống lưỡng cư cỡ lớn, chủ yếu xuất hiện trong các khu rừng. Da chúng tỏa ra hơi nóng.
 Nghiên cứu cho thấy độ cứng của da Viridblaze Saurian tỉ lệ thuận với nhiệt độ cơ thể.</t>
         </is>
@@ -21907,7 +21907,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21974,9 +21974,9 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Các sinh vật giống khỉ đột thường tụ tập trong những khu rừng sâu. Những tên Hoochief thích khoe khoang uy quyền bằng cách cướp đoạt đồ đạc của con người.
-Chúng là những Tacet Discord trong lãnh thổ Huanglong, được phát hiện có khả năng nhận thức tương đối phức tạp, thậm chí có thể bắt chước con người sử dụng một số công cụ và vũ khí thô sơ. Trong trường hợp này, là Dodgem đá.</t>
+Chúng là những Tacet Discord trong lãnh thổ Huanglong, được phát hiện có khả năng nhận thức tương đối phức tạp, thậm chí có thể bắt chước con người sử dụng một số công cụ và vũ khí thô sơ. Trong trường hợp này, là ném đá.</t>
         </is>
       </c>
     </row>
@@ -22108,7 +22108,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Loài sinh vật lưỡng cư giống rùa, thường xuất hiện dọc bờ sông. Mai của chúng gắn liền với những tinh thể băng giá. Chúng thích ngủ trưa ở những nơi lạnh lẽo.
 Môi trường ấm hơn sẽ đánh thức Hoartoise, đồng thời khơi dậy bản tính nóng nảy của chúng.</t>
         </is>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Loài thú giống sói lang thang ở những vùng khô cằn, nổi tiếng với sự hung dữ và khát máu.
 Để đối phó với kẻ thù mạnh hơn, Annihilation Dreadmane thường săn mồi theo bầy. Chiến thuật của chúng là nghệ thuật tàn sát.</t>
         </is>
@@ -22315,9 +22315,9 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. 
 Một loài vượn hình người xuất hiện ở những khu rừng rậm rạp, thường lấy trộm đồ của con người làm chiến lợi phẩm như một lời tuyên bố. 
-Đây là một trong những Echo phức tạp nhất với hành vi thông minh ở lãnh thổ Huanglong cho đến nay, và sẽ dùng móng vuốt sắc bén để bảo vệ lãnh thổ của mình.</t>
+Đây là một trong những Tổ Tacet phức tạp nhất với hành vi thông minh ở lãnh thổ Huanglong cho đến nay, và sẽ dùng móng vuốt sắc bén để bảo vệ lãnh thổ của mình.</t>
         </is>
       </c>
     </row>
@@ -22385,8 +22385,8 @@
       <c r="M331" t="inlineStr">
         <is>
           <t>Những tín đồ trung thành của Fractsidus.
-Thiếu đi Forte nhưng lại khao khát quyền lực mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Echo, biến thân hình thành những khẩu pháo gắn trên vai.
-Tuy nhiên, tần số của Echo bóp méo tinh thần và ăn mòn cơ thể chúng. Chúng chọn cách che mặt để giấu đi khuôn mặt bị biến dạng.</t>
+Thiếu đi Forte nhưng lại khao khát quyền lực mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Tổ Tacet, biến thân hình thành những khẩu pháo gắn trên vai.
+Tuy nhiên, tần số của Tổ Tacet bóp méo tinh thần và ăn mòn cơ thể chúng. Chúng chọn cách che mặt để giấu đi khuôn mặt bị biến dạng.</t>
         </is>
       </c>
     </row>
@@ -22454,8 +22454,8 @@
       <c r="M332" t="inlineStr">
         <is>
           <t>Những tín đồ trung thành của Fractsidus.
-Thiếu đi Forte nhưng lại khao khát quyền lực mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Echo, biến cơ thể thành những khẩu súng hùng mạnh.
-Tuy nhiên, tần số của Echo bóp méo tinh thần và ăn mòn cơ thể chúng. Chúng chọn cách băng bó bản thân để che giấu khuôn mặt bị biến dạng.</t>
+Thiếu đi Forte nhưng lại khao khát quyền lực mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, cơ thể người của chúng được kết hợp với chi của Tổ Tacet, biến cơ thể thành những khẩu súng hùng mạnh.
+Tuy nhiên, tần số của Tổ Tacet bóp méo tinh thần và ăn mòn cơ thể chúng. Chúng chọn cách băng bó bản thân để che giấu khuôn mặt bị biến dạng.</t>
         </is>
       </c>
     </row>
@@ -22522,7 +22522,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Kẻ địch nhỏ này kết hợp với đèn giao thông, sử dụng quy tắc phổ biến "đèn đỏ dừng, đèn xanh đi" để trừng phạt những ai vi phạm luật lệ.
 Vậy nên, hãy nhớ tuân thủ luật giao thông nhé!</t>
         </is>
@@ -22592,10 +22592,10 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Buling có thể giữ tối đa {0} Trigram. Khi số lượng Trigram đạt tối đa, việc nhận thêm Trigram mới sẽ đẩy tất cả Trigram dịch chuyển {1} ô sang trái, và Trigram ở vị trí ngoài cùng bên trái sẽ bị loại bỏ.
-- Trigram - Sơn nhận được khi &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; gây sát thương.
-- Trigram - Lôi nhận được khi &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; gây sát thương.
-- Trigram - Lôi nhận được khi sử dụng &lt;color=Highlight&gt;Resonance Skill - In Shadow Thunder Stirs&lt;/color&gt;.</t>
+          <t>Buling có thể giữ tối đa {0} Quẻ. Khi số lượng Quẻ đạt tối đa, việc nhận thêm Quẻ mới sẽ đẩy tất cả Quẻ dịch chuyển {1} ô sang trái, và Quẻ ở vị trí ngoài cùng bên trái sẽ bị loại bỏ.
+- Quẻ - Sơn nhận được khi &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 2&lt;/color&gt; gây sát thương.
+- Quẻ - Lôi nhận được khi &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Đòn Mid-air Attack&lt;/color&gt; gây sát thương.
+- Quẻ - Lôi nhận được khi sử dụng &lt;color=Highlight&gt;Resonance Skill - Trong Bóng Tối Sấm Rền&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Khi Buling thu được Âm Nhỏ và Dương Nhỏ, cô sẽ bước vào trạng thái &lt;color=Highlight&gt;Yin-Yang Balance&lt;/color&gt;, thay thế &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell&lt;/color&gt; bằng &lt;color=Highlight&gt;Resonance Liberation - Flashing Thunder Spell: Harmony&lt;/color&gt;.</t>
+          <t>Khi Buling thu được Âm Nhỏ và Dương Nhỏ, cô sẽ bước vào trạng thái &lt;color=Highlight&gt;Cân Bằng Âm Dương&lt;/color&gt;, thay thế &lt;color=Highlight&gt;Resonance Liberation - Phép Thuật Sấm Chớp&lt;/color&gt; bằng &lt;color=Highlight&gt;Resonance Liberation - Phép Thuật Sấm Chớp: Hòa Điệu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22725,7 +22725,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Thunder Spell - Heaven, Earth, Mind&lt;/color&gt; tăng {0} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; cho Resonators đang hoạt động trong đội.</t>
+          <t>&lt;color=Highlight&gt;Thần Chú Sấm - Thiên, Địa, Tâm&lt;/color&gt; tăng {0} &lt;color=Highlight&gt;Sát Thương Resonance Skill&lt;/color&gt; cho các Resonator đang hoạt động trong đội.</t>
         </is>
       </c>
     </row>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Các Tacet Discord bắt chước ấu trùng chủ yếu sinh sống dưới lớp băng vĩnh cửu, gần nguồn nhiệt địa nhiệt.
 Bằng cách hấp thụ năng lượng địa nhiệt, chúng tạo ra dung nham qua một cơ quan đặc biệt để làm tan lớp đất đóng băng và đào các đường hầm tỏa ra mọi hướng.
 Dấu vết của Lava Larva thường dẫn đến những khu vực giàu năng lượng địa nhiệt.</t>
@@ -22863,9 +22863,9 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Echo bắt chước đá với lớp Fool's Gold trên lưng. Nó thường bị nhầm lẫn với quặng vàng chưa khai thác.
-Golden Junrock luôn tỉ mỉ đánh bóng lớp Fool's Gold mà nó mang theo, một cuộc đời theo đuổi để làm tăng độ lấp lánh của nó.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tổ Tacet bắt chước đá với lớp Vàng Giả trên lưng. Nó thường bị nhầm lẫn với quặng vàng chưa khai thác.
+Golden Junrock luôn tỉ mỉ đánh bóng lớp Vàng Giả mà nó mang theo, một cuộc đời theo đuổi để làm tăng độ lấp lánh của nó.</t>
         </is>
       </c>
     </row>
@@ -22932,7 +22932,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Một Tacet Discord bắt chước đá mang theo Resonant Calcite. Năng lượng Tàn Dư bên trong lấp lánh với ánh sáng ngọc trai luôn biến đổi.
 Khi bị kích động, Calcified Junrock sẽ phát ra ánh sáng chói lóa từ lớp vỏ đá hóa của mình.</t>
         </is>
@@ -23001,8 +23001,8 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echo khoáng vật thường thấy trong các mạch quặng. Thân thể đá của nó chứa đựng những luồng khí mạnh mẽ.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tổ Tacet khoáng vật thường thấy trong các mạch quặng. Thân thể đá của nó chứa đựng những luồng khí mạnh mẽ.
 Dù khả năng chiến đấu tương đối yếu, khi bị tiêu diệt, năng lượng nó giải phóng sẽ tăng cường cho các Tacet Discord xung quanh.</t>
         </is>
       </c>
@@ -23070,9 +23070,9 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Echoes cầm cung giống như bức tượng, có nhiệm vụ giám sát thành phố Ragunna và báo cáo chi tiết về cho Hội.
-Dưới sự giám sát của nó, bất kỳ cá nhân hay Echoes khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Phòng Discipline để đảm bảo an ninh cho thành phố.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Echo cầm cung giống như bức tượng, có nhiệm vụ giám sát thành phố Ragunna và báo cáo chi tiết về cho Hội.
+Dưới sự giám sát của nó, bất kỳ cá nhân hay Echo khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Phòng Kỷ Luật để đảm bảo an ninh cho thành phố.</t>
         </is>
       </c>
     </row>
@@ -23139,9 +23139,9 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echoes giống tượng, tượng trưng cho lòng thương xót và từ bi, luôn lắng nghe lời cầu nguyện của Ragunnesi và ca ngợi Order.
-Dưới sự giám sát của nó, bất kỳ cá nhân hoặc Echoes khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Chamber of Discipline để đảm bảo an ninh cho thành phố.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Echo giống tượng, tượng trưng cho lòng thương xót và từ bi, luôn lắng nghe lời cầu nguyện của Ragunnesi và ca ngợi Order.
+Dưới sự giám sát của nó, bất kỳ cá nhân hoặc Echo khả nghi nào cũng sẽ bị bắt giữ ngay lập tức và đưa đến Chamber of Discipline để đảm bảo an ninh cho thành phố.</t>
         </is>
       </c>
     </row>
@@ -23208,8 +23208,8 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echo bắt chước hình dáng một con rồng con, với những luồng gió xoáy giữa các móng vuốt. Chúng thường sống thành đàn trong hoang dã.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tổ Tacet bắt chước hình dáng một con rồng con, với những luồng gió xoáy giữa các móng vuốt. Chúng thường sống thành đàn trong hoang dã.
 Dù kích thước nhỏ bé, chúng lại cực kỳ bảo vệ lãnh thổ, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và móng vuốt sắc nhọn.</t>
         </is>
       </c>
@@ -23277,8 +23277,8 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Echo bắt chước hình dáng con non của loài mãng xà, với những tia lửa điện loé lên giữa các móng vuốt. Chúng thường sống thành đàn trong hoang dã.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tổ Tacet bắt chước hình dáng con non của loài mãng xà, với những tia lửa điện loé lên giữa các móng vuốt. Chúng thường sống thành đàn trong hoang dã.
 Dù kích thước nhỏ bé, chúng lại cực kỳ hung hãn trong việc bảo vệ lãnh thổ, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và vuốt sắc.</t>
         </is>
       </c>
@@ -23346,8 +23346,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Echo giả dạng con non của loài mãng xà băng, với băng giá và sương muối kết tụ giữa những móng vuốt. Chúng thường sống thành bầy trong hoang dã.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tổ Tacet giả dạng con non của loài mãng xà băng, với băng giá và sương muối kết tụ giữa những móng vuốt. Chúng thường sống thành bầy trong hoang dã.
 Dù kích thước nhỏ bé, chúng lại cực kỳ hung dữ với lãnh thổ của mình, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và vuốt sắc.</t>
         </is>
       </c>
@@ -23415,7 +23415,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Một Tacet Discord bắt chước hình dáng con non của loài mãng xà, với ngọn lửa rực cháy giữa những móng vuốt. Chúng thường sống thành đàn trong hoang dã.
 Dù kích thước nhỏ bé, chúng lại vô cùng hung hãn, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và vuốt sắc.</t>
         </is>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Một Tacet Discord bắt chước hình dáng một con rồng con, với những luồng ánh sáng nhấp nháy giữa các móng vuốt. Thường sống theo bầy đàn trong hoang dã.
 Dù kích thước nhỏ bé, nó lại rất hung dữ khi bảo vệ lãnh thổ, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và móng vuốt.</t>
         </is>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một Tacet Discord bắt chước hình dáng con rồng con, với những dòng chảy bóng tối cuồn cuộn giữa các móng vuốt. Thường sống thành đàn trong hoang dã.
 Dù kích thước nhỏ bé, nó cực kỳ hung dữ và bảo vệ lãnh thổ, luôn sẵn sàng xua đuổi kẻ xâm phạm bằng hơi thở và vuốt sắc.</t>
         </is>
@@ -23622,7 +23622,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Aero DMG&lt;/color&gt;&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;&lt;/color&gt; cao hơn.
 Với san hô làm xương, rong biển làm thịt, và niềm tin mù quáng làm chất xúc tác, chúng hợp thành hiện thân của tín ngưỡng Thủy Triều Đen.
 Chúng là những tín đồ, thân thể bị bỏ rơi trong hư không, xác khô được khâu vá từ đống đổ nát. Những lời thì thầm và tụng niệm mơ hồ vang vọng trong vỏ rỗng của chúng khi không ngừng hành hương để tìm kiếm lòng thương xót và sự dẫn dắt của Thủy Triều Đen.</t>
         </is>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Xạ thủ Fractsidus bắn ra những tần số biển sâu méo mó và hòa trộn.
 Sự biến đổi của giai điệu tạo nên bản giao hưởng của nỗi đau xé lòng, trong khi những tần số bị bóp méo dệt nên một lồng băng giá giam cầm.</t>
         </is>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Một TD được xây dựng từ đá. Chậm chạp và vụng về, nó sở hữu sức mạnh cánh tay kinh hoàng và thích Dodgem đá để tấn công kẻ thù.</t>
+          <t>Một TD được xây dựng từ đá. Chậm chạp và vụng về, nó sở hữu sức mạnh cánh tay kinh hoàng và thích ném đá để tấn công kẻ thù.</t>
         </is>
       </c>
     </row>
@@ -23824,7 +23824,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
 Loài chim giống diệc hoạt động ở rừng núi và ven nước. Dù sinh ra với đôi cánh tím rộng, chúng chỉ dang cánh bay khi cơn bão sấm nổ ra dữ dội.</t>
         </is>
       </c>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. 
 Loài chim giống diệc hoạt động ở rừng núi và ven nước. Dù sinh ra với đôi cánh xanh rộng lớn, chúng chỉ giang cánh bay khi gió gào thét.</t>
         </is>
       </c>
@@ -23958,7 +23958,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
 Một Tacet Discord hình người sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi thổi sáo truyền tin của con người, nhưng giai điệu nó tạo ra chỉ là những âm thanh chói tai và khàn khàn.</t>
         </is>
       </c>
@@ -24025,7 +24025,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một Tacet Discord hình người sử dụng sức mạnh bằng cách chơi nhạc cụ. Bắt chước hành vi đánh chuông và cầu nguyện của con người, nhưng những lời nó thốt ra không phải lời chúc phúc, mà là lời nguyền rủa.</t>
         </is>
       </c>
@@ -24093,8 +24093,8 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Echo hộ pháp cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối trên núi.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tổ Tacet hộ pháp cao lớn. Dáng vẻ của nó giống như những tảng đá nguyên khối trên núi.
 Dù trông như một pháo đài bất khả xâm phạm, bản chất của Rocksteady Guardian không phải để bảo vệ, mà là để nghiền nát bất cứ vật cản nào chặn đường tiến của nó.</t>
         </is>
       </c>
@@ -24162,9 +24162,9 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Echo canh giữ cao lớn. Dáng vẻ của nó giống như tảng đá khổng lồ từ vực thẳm sâu thẳm.
-Dù trông như pháo đài bất khả xâm phạm, bản chất của Guardian Vực Nứt không phải để bảo vệ, mà là nghiền nát mọi chướng ngại cản bước tiến của nó.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tổ Tacet canh giữ cao lớn. Dáng vẻ của nó giống như tảng đá khổng lồ từ vực thẳm sâu thẳm.
+Dù trông như pháo đài bất khả xâm phạm, bản chất của Người Bảo Vệ Vực Nứt không phải để bảo vệ, mà là nghiền nát mọi chướng ngại cản bước tiến của nó.</t>
         </is>
       </c>
     </row>
@@ -24231,7 +24231,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Loài sinh vật giống lưỡng cư cỡ lớn, chủ yếu xuất hiện trong các khu rừng. Da chúng tỏa ra hơi nóng.
 Nghiên cứu cho thấy độ cứng của da Viridblaze Saurian tỉ lệ thuận với nhiệt độ cơ thể.</t>
         </is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Roseshroom là loài sinh vật nấm sống ở vùng đầm lầy, khi nở rộ, mũ của chúng trông như những cánh hoa hồng, vì thế mà có tên gọi này.
 Dù đứng yên, lõi trên mũ của chúng có thể hấp thu và phóng ra những tia sáng để tấn công sinh vật đi ngang qua.</t>
         </is>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Loài sói đồng cỏ, nổi tiếng với bản tính cơ hội.
 Để đối phó với kẻ địch mạnh hơn, Havoc Dreadmane thường săn mồi theo bầy. Chiến thuật của chúng là phục kích.</t>
         </is>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Các sinh vật giống khỉ đột thường tụ tập trong những khu rừng sâu. Những tên Hoochief thích khoe khoang uy quyền bằng cách cướp đoạt đồ đạc của con người.
 Khác với các Hoochief khác, Hoochief Cyclone có thể tạo ra luồng gió để không chỉ tấn công tầm xa mà còn hạn chế di chuyển của mục tiêu.</t>
         </is>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Tacet Discord sống trong những phương tiện bị bỏ hoang. Chúng ngụy trang giữa đống đổ nát và cây cối. Một khi bị quấy rối, chúng sẽ thể hiện những hành vi đáng sợ.</t>
         </is>
       </c>
@@ -24574,7 +24574,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -24641,8 +24641,8 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Các Resonators nữ thuộc nhóm Exile. Là thợ máy, Exile Technician chịu trách nhiệm chế tạo và sửa chữa vũ khí cùng trang thiết bị.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Các Resonator nữ thuộc nhóm Exile. Là thợ máy, Exile Technician chịu trách nhiệm chế tạo và sửa chữa vũ khí cùng trang thiết bị.
 Tay nghề khéo léo có thể tăng đáng kể khả năng sống sót của nhóm, còn vũ khí sắc bén sẽ đảm bảo chiến thắng trong cuộc tranh giành tài nguyên.</t>
         </is>
       </c>
@@ -24711,10 +24711,10 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Những tín đồ trung thành của Fractsidus.
-Dù thiếu Tần số nhưng lại khao khát sức mạnh mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, thân thể con người của chúng được kết hợp với chi của Echo, nhờ đó có khả năng tàng hình.
-Tuy nhiên, Tần số Echo bóp méo tâm trí và ăn mòn cơ thể của những tín đồ này. Những Đao Phủ có nhiệm vụ loại bỏ các thành viên Fractsidus vi phạm quy tắc hoặc mất kiểm soát.</t>
+Dù thiếu Tần số nhưng lại khao khát sức mạnh mãnh liệt, chúng đã vượt qua những giới hạn khoa học cấm kỵ. Bằng cách sử dụng các bộ phận cơ khí đặc biệt, thân thể con người của chúng được kết hợp với chi của Tổ Tacet, nhờ đó có khả năng tàng hình.
+Tuy nhiên, Tần số Tổ Tacet bóp méo tâm trí và ăn mòn cơ thể của những tín đồ này. Những Đao Phủ có nhiệm vụ loại bỏ các thành viên Fractsidus vi phạm quy tắc hoặc mất kiểm soát.</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. 
 Những con vượn bắt chước xuất hiện ở khu rừng rậm, thường lấy trộm đồ của con người làm chiến lợi phẩm như một lời khiêu khích. 
 Hoochief Menace đặc biệt điên cuồng so với các loài vượn bắt chước khác, và nắm đấm của nó có thể tung ra hàng loạt đòn tấn công dữ dội.</t>
         </is>
@@ -24849,8 +24849,8 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;. 
-Echo này là ký sinh trùng của Xe Tuần Tra, ngụy trang dưới lớp vỏ giáp han gỉ và hư hại. Nó đóng vai trò "lính canh", giám sát mọi động thái trong thành phố và loại bỏ mọi mối đe dọa tiềm tàng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;. 
+Tổ Tacet này là ký sinh trùng của Xe Tuần Tra, ngụy trang dưới lớp vỏ giáp han gỉ và hư hại. Nó đóng vai trò "lính canh", giám sát mọi động thái trong thành phố và loại bỏ mọi mối đe dọa tiềm tàng.</t>
         </is>
       </c>
     </row>
@@ -24917,8 +24917,8 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Echo bắt chước loài sói hoành hành trên vùng tuyết nguyên, tinh thông kỹ năng ẩn nấp.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tổ Tacet bắt chước loài sói hoành hành trên vùng tuyết nguyên, tinh thông kỹ năng ẩn nấp.
 Glacio Dreadmane sử dụng chiến thuật phối hợp và ngụy trang để đối phó với những đối thủ mạnh hơn.</t>
         </is>
       </c>
@@ -24986,7 +24986,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kẻ địch có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+          <t>Kẻ địch có &lt;color=HighlightB&gt;Kháng cao hơn&lt;/color&gt; đối với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
 Lumiscale Constructs được cấu thành từ các mô-đun phòng thủ của Jué, thường được gọi là "Vảy Rồng".
 Chúng xuất hiện khắp nơi trong đống đổ nát Court of Savantae trên Núi Firmament, với nhiệm vụ tiêu diệt kẻ xâm nhập và các mối đe dọa tiềm tàng đối với Jué.</t>
         </is>
@@ -25055,9 +25055,9 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Echo khổng lồ bắt chước hình dáng loài mèo, chỉ xuất hiện ở Mt. Firmament tại Huanglong.
-Theo Hồng Chân Lục, đây là một Echo đơn độc với bốn móng vuốt và lưng phủ vảy. Nó được gọi là "Lightcrusher" vì những vệt sáng rực rỡ để lại trên đường đi.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tổ Tacet khổng lồ bắt chước hình dáng loài mèo, chỉ xuất hiện ở Mt. Firmament tại Huanglong.
+Theo Hồng Chân Lục, đây là một Tổ Tacet đơn độc với bốn móng vuốt và lưng phủ vảy. Nó được gọi là "Lightcrusher" vì những vệt sáng rực rỡ để lại trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -25124,8 +25124,8 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord hình người, cơ thể được ghép từ những mảnh kính màu vỡ vụn. Ánh sáng lấp lánh tỏa ra từ thân thể mỗi khi di chuyển. Nó toát lên vẻ đẹp kiên cường, tái sinh từ sự hủy diệt.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord hình người, cơ thể được ghép từ những mảnh kính màu vỡ vụn. Ánh sáng lấp lánh tỏa ra từ thân thể mỗi khi di chuyển. Nó toát lên vẻ đẹp kiên cường, tái sinh từ sự hủy diệt.
 Những mảnh kính tạo nên Vitreum Dancer đều khác biệt và độc nhất, khiến mỗi cá thể trở thành một sinh mệnh riêng biệt.</t>
         </is>
       </c>
@@ -25193,9 +25193,9 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Echo đá hình tượng trưng cho sự phân rã và tái tạo. Dù di chuyển chậm chạp và vụng về, cú đấm của nó lại vô cùng tàn khốc.
-Nó Dodgem đá và các Tacet Discord bắt chước đá khác để tấn công.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tổ Tacet đá hình tượng trưng cho sự phân rã và tái tạo. Dù di chuyển chậm chạp và vụng về, cú đấm của nó lại vô cùng tàn khốc.
+Nó ném đá và các Tacet Discord bắt chước đá khác để tấn công.</t>
         </is>
       </c>
     </row>
@@ -25261,8 +25261,8 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Echo bắt chước gấu hung dữ, với những gai Tacetite trên đầu, cổ và vai. Những cú vung của nó mạnh như bão tố.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tổ Tacet bắt chước gấu hung dữ, với những gai Tacetite trên đầu, cổ và vai. Những cú vung của nó mạnh như bão tố.</t>
         </is>
       </c>
     </row>
@@ -25329,9 +25329,9 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Nó nắm quyền chỉ huy các Echoes khác của Order, thực thi ý chí của Order để loại bỏ mọi kẻ vi phạm.
-Giống như quyền uy của Order bất khả xâm phạm, sức mạnh của Echoes cũng vậy.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Nó nắm quyền chỉ huy các Echo khác của Order, thực thi ý chí của Order để loại bỏ mọi kẻ vi phạm.
+Giống như quyền uy của Order bất khả xâm phạm, sức mạnh của Echo cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -25399,10 +25399,10 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Kerasaurs là những Tacet Discord lưỡng cư hung dữ, bắt chước loài Saurosuchus. Chúng được đặt tên theo những chiếc vảy gai nhọn bao phủ cơ thể.
 Kerasaurs không phải loài bản địa của Septimont. Chúng được đưa vào làm đối thủ trong các trận đấu giác đấu vì ngoại hình đặc biệt và tính cách hung hãn.
-Bản năng lãnh thổ mạnh mẽ cũng khiến chúng trở thành những Echoes lý tưởng để phục vụ trong lực lượng phòng thủ thành phố sau khi được thuần hóa.</t>
+Bản năng lãnh thổ mạnh mẽ cũng khiến chúng trở thành những Echo lý tưởng để phục vụ trong lực lượng phòng thủ thành phố sau khi được thuần hóa.</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Aero DMG&lt;/color&gt;&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;&lt;/color&gt; cao hơn.
 Với san hô làm xương, rong biển làm thịt, và niềm tin mù quáng làm chất xúc tác, chúng hợp thành hiện thân của tín ngưỡng Thủy Triều Đen.
 Lưng gù của chúng chỉ chứa đựng san hô hóa đá, xương khô và những di vật thất lạc dưới biển. Từng là những nhà truyền giáo sùng đạo nhất, giờ đây chúng lang thang như những pháp sư khấn nguyện ý chí của Thủy Triều Đen, tiếng thì thầm của chúng vang lên tên những kẻ sẽ trở về vòng tay vực thẳm.</t>
         </is>
@@ -25538,7 +25538,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Các Chiến Binh Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn theo đuổi những kẻ mạnh mẽ.
 Flamecrest Gladiators thể hiện khát vọng bất diệt của chiến binh. Vết thương hóa thành lửa, gian khổ là lò rèn. Trận chiến nối tiếp trận chiến, họ đi trên con đường nhuốm máu để tìm về hình hài chân thật nhất.</t>
         </is>
@@ -25607,8 +25607,8 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Những chiến binh của Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn theo đuổi sức mạnh.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Những chiến binh của Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn theo đuổi sức mạnh.
 Galecrest Gladiator tuân theo ý chí tự do. Không bị ràng buộc bởi luật lệ hay vinh quang, chúng trở thành lưỡi kiếm chặt đứt mọi xiềng xích.</t>
         </is>
       </c>
@@ -25676,8 +25676,8 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn truy tìm sức mạnh.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn truy tìm sức mạnh.
 Lightcrest Gladiator theo đuổi lý tưởng công lý. Chúng không cúi đầu trước bạo chúa, không khuất phục trước bóng tối. Nếu công lý đã mục rữa, chúng sẽ rèn lại nó trong ánh sáng.</t>
         </is>
       </c>
@@ -25745,8 +25745,8 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn theo đuổi sức mạnh.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn theo đuổi sức mạnh.
 Chiến binh Băng Giá sở hữu ý chí bất khuất. Sự kiên cường của họ không gì lay chuyển được, dù băng giá hay giá lạnh. Dù lưỡi kiếm có gãy, tín điều của họ vẫn trường tồn.</t>
         </is>
       </c>
@@ -25814,8 +25814,8 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn truy tìm sức mạnh.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Những chiến binh Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn truy tìm sức mạnh.
 Thundercrest Gladiator vận dụng sức mạnh bão tố. Không màng ân huệ, không cúi đầu trước quyền uy. Dưới sự phán xét của sấm sét, thiện ác phân minh.</t>
         </is>
       </c>
@@ -25883,8 +25883,8 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Những võ sĩ của Septimont chiến đấu không giới hạn, sát cánh cùng Echoes, luôn truy tìm kẻ mạnh.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Những võ sĩ của Septimont chiến đấu không giới hạn, sát cánh cùng Echo, luôn truy tìm kẻ mạnh.
 Những Võ Sĩ Vực Sâu tin vào giáo lý vô ngã. Im lặng trong vô danh, ẩn mình trong bóng tối. Họ tự đặt mình trên hành trình tìm kiếm ánh sáng thoáng qua của chân lý.</t>
         </is>
       </c>
@@ -25952,8 +25952,8 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Những Fractsidus Inspector với thân thể cải tiến tận tụy phục vụ cho lý tưởng cuồng tín của chúng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Những Thanh Tra Fractsidus với thân thể cải tiến tận tụy phục vụ cho lý tưởng cuồng tín của chúng.
 Dưới lớp vỏ kim loại lạnh lẽo vẫn còn vương vấn chút lý trí. Nhưng qua những vết nứt, thứ duy nhất nhìn thấy được chỉ là hố đen vô tận.</t>
         </is>
       </c>
@@ -26020,7 +26020,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; cao hơn. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; cao hơn. 
 Một Tacet Discord hùng mạnh lang thang trên Đồng bằng Trung tâm. Với sự trợ giúp của bão sét, nó không ngừng nuốt chửng những âm thanh bảo vệ của con người. Được xem là tiên phong của Crownless.</t>
         </is>
       </c>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Một "tay đua" nóng bỏng sinh ra tại Thành phố Cảng Guixu. Nó đặt ra những thử thách dũng cảm bằng ngọn lửa bất khuất cho những kẻ dám xâm phạm lãnh địa.
 Qua năm tháng dài đằng đẵng, sự thật lịch sử dần cháy thành tro tàn, và hiệp sĩ từng hát vang bài ca tử thần giờ trở thành điềm gở trong lời đồn của nhân loại.
 "Đó là kỵ sĩ biến nỗi sợ thành nhiên liệu, mang tai họa đến."
@@ -26163,7 +26163,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một sinh vật khổng lồ hình chim bay lượn trên Desorock Highland. Ba cái đầu của nó lần lượt đảm nhiệm việc ăn, tấn công và phòng thủ.
 "Trái ngốc, phải độc, đầu giữa mới là ác ma," như lời đồng dao ở Jinzhou.</t>
         </is>
@@ -26233,7 +26233,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Một kẻ phục kích ngủ yên trong hầm mỏ băng giá, ám ảnh với việc thu thập và bắt chước âm thanh. Nó có thể bắt chước giọng nói con người qua tiếng rung động.
 Lampylumen Myriad dùng âm thanh làm mồi nhử con mồi, rồi đóng băng chúng trong cái lạnh thấu xương. Sự mất đi hơi ấm và ảo giác trước khi chết khiến con người thốt ra những lời cuối cùng chứa đầy cảm xúc mãnh liệt.
 Với Lampylumen Myriad, đây chính là tần số của hương vị tuyệt hảo.</t>
@@ -26303,9 +26303,9 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng cao&lt;/color&gt; với &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;. 
 Một con quái thú khổng lồ hình dạng như vượn, cư ngụ tại Cây Bồ Đề Trung Tâm cao chót vót, canh giữ lãnh thổ của loài vượn khỏi sự xâm nhập. 
-Để tránh đụng độ bất ngờ với nó, Midnight Rangers và Huaxu Academy từng hợp tác trong một chiến dịch đặc biệt, gắn vòng theo dõi lên Feilian Beringal, giúp giám sát chuyển động của nó trong rừng.</t>
+Để tránh đụng độ bất ngờ với nó, Midnight Rangers và Học viện Huaxu từng hợp tác trong một chiến dịch đặc biệt, gắn vòng theo dõi lên Feilian Beringal, giúp giám sát chuyển động của nó trong rừng.</t>
         </is>
       </c>
     </row>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Một loài chim săn mồi đậu tại Whining Aix's Mire, tiếng kêu như khúc ai oán.
 Truyền thuyết kể rằng loài chim này từng có đôi lứa, tiếng hót của chúng là âm thanh tuyệt đẹp. Tên của chúng không được lưu truyền, nhưng những khúc ca ấy đã được con người ghi lại và bảo tồn.
 Cho đến khi một trong hai qua đời. Con còn lại khóc suốt ngày đêm, tiếng kêu bi thương đến mức được gọi là Mourning Aix.
@@ -26443,7 +26443,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Một Tacet Discord cấp Overlord loại Howler đang lơ lửng trên Bãi Lầy Whining Aix. Nó bay lượn trên bầu trời, cất lên khúc bi ca và tấn công dữ dội bất kỳ kẻ thù nào đến gần.</t>
+          <t>Một Tacet Discord cấp Overlord loại Howler đang lơ lửng trên Whining Aix's Mire. Nó bay lượn trên bầu trời, cất lên khúc bi ca và tấn công dữ dội bất kỳ kẻ thù nào đến gần.</t>
         </is>
       </c>
     </row>
@@ -26510,8 +26510,8 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. 
-Crownless là một Discord Whisperin sinh ra bên ngoài Gorges of Spirits cùng với sự phun trào của Tacet Field kỳ lạ. Một hỗn hợp rộng lớn các tần số con người được phát hiện trong hình hài của nó. Chẳng hạn như sự hưng phấn và khát khao chiến thắng, nỗi sợ hãi và oán giận trước thất bại... Bản năng man rợ bị kìm Dodgen lâu ngày của loài người được hiện thực hóa trong Crownless và tự phản bội chính mình.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. 
+Crownless là một Tacet Discord Whisperin sinh ra bên ngoài Gorges of Spirits cùng với sự phun trào của Tổ Tacet kỳ lạ. Một hỗn hợp rộng lớn các tần số con người được phát hiện trong hình hài của nó. Chẳng hạn như sự hưng phấn và khát khao chiến thắng, nỗi sợ hãi và oán giận trước thất bại... Bản năng man rợ bị kìm nén lâu ngày của loài người được hiện thực hóa trong Crownless và tự phản bội chính mình.
 Sinh vật này là một con tốt được kẻ địch cử đến dưới vỏ bọc, đồng thời là điềm báo về tai họa chiến tranh.</t>
         </is>
       </c>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Một con rùa snapping uể oải trong hồ băng, mang trên lưng một chiếc chuông cổ xưa.
 Một số nhà nghiên cứu từng cố phiên dịch những dòng chữ trên chuông, nhưng vô tình đánh thức giấc mơ của con rùa khổng lồ này.
 Khi thức giấc, tiếng chuông ngân dài sẽ vang vọng khắp Gorges of Spirits.</t>
@@ -26650,7 +26650,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Kẻ thống trị hung bạo của đại dương sâu thẳm, lang thang trên mặt nước để tìm kiếm tiếng hát của đồng loại.
 Giữa những con sóng cuộn trào, tiếng hát cô đơn của cá voi vang lên, thu hút những kẻ du hành tò mò, reo hò hòa theo để tìm kiếm "Nhà soạn nhạc đại dương" này.</t>
         </is>
@@ -26721,8 +26721,8 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; khi ở dạng người. 
-Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; khi ở dạng người. 
+Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một trong những Fractsidus Overseers.
 Một kẻ nổi loạn say mê Overclocking, phớt lờ vẻ đẹp và trật tự. Hắn thích hủy diệt và hỗn loạn, vui sướng trước nỗi đau của người khác. Hắn coi thường luật lệ và danh tiếng, sẵn sàng dùng mọi thủ đoạn để đạt mục tiêu. Với sự tỉnh táo nội tâm thúc đẩy, hắn tìm đến ngươi để chứng kiến sự ra đời của một thế giới mới, vẫn còn trong giai đoạn sơ khai.
 &lt;i&gt;"Sự sống mới nở rộ từ tro tàn, vươn lên từ đống đổ nát."&lt;/i&gt;</t>
@@ -26793,7 +26793,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; cao hơn. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; cao hơn. 
 Được tạo ra trong phòng thí nghiệm CSC, Tacet Discord Cơ khí này đã tiến hóa bằng cách nuốt chửng xác máy móc.
 Khi phát hiện dấu vết tần số con người, nó trở nên ám ảnh với việc đạt đến sự hoàn hảo và ngày càng lớn mạnh khi cải thiện cấu trúc của mình. 
 Một biểu tượng ám ảnh về sự theo đuổi không ngừng của nhân loại trong tiến bộ khoa học, sự hiện diện của nó như lời nhắc nhở tinh tế về nỗi ám ảnh và sự sa đọa vào điên loạn của chúng ta.</t>
@@ -26863,7 +26863,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;. 
 Cùng với Trăng Tròn Hư Không ma quái, Tacet Discord Whisperin này đã xuất hiện ở cuối vùng Norfall Barrens. 
 Sự hiện diện của nó là lời nhắc nhở u ám về cuộc chiến tàn khốc từng tàn phá vùng đất này. Sinh ra từ những tàn dư năng lượng của chiến tranh, nó không ngừng tiến hóa và trở thành vũ khí đáng sợ nhất trong kho vũ khí của Threnodian. Với sự hủy diệt không thương tiếc, nó đánh thức nỗi sợ nguyên thủy của loài người về chiến tranh. Và giờ đây, nó chào đón chủ nhân của mình, sẵn sàng gieo rắc hỗn loạn lên thế giới.</t>
         </is>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; cao hơn. 
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; cao hơn. 
 Một Tacet Discord mạnh mẽ ở Desorock Highland, sở hữu sức mạnh sấm sét. Nó được coi là một trong những tiên phong của quân đội Threnody.</t>
         </is>
       </c>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;, và &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;, và &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Một trong Tứ Vệ của Huanglong, mang hình dáng của một con Long. Là sức mạnh dẫn dắt nền văn minh Jinzhou.
 Một "thần linh" uy nghiêm với sức mạnh không thể chối cãi, thấu suốt quá khứ, hiện tại và tương lai của Jinzhou. Jué, kẻ nắm giữ dòng chảy thời gian, coi vạn kỷ chỉ như khoảnh khắc. Trong nháy mắt, Jué có thể thay đổi cả vũ trụ.
 "Bốn mùa thay đổi theo mệnh lệnh, vạn vật tuân theo quy luật. Đó chính là bản chất của vũ trụ."</t>
@@ -27071,7 +27071,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Đây là tuyến phòng thủ cuối cùng do Hệ thống Tethys dựng nên, tuần tra biên giới giữa thực tại và thế giới kỹ thuật số.
 Sự an toàn và ổn định tuyệt đối của hệ thống này phải được bảo vệ bằng mọi giá, dù phải tiêu hao sức mạnh tính toán của các vì sao, hay tước đoạt quyền năng điều biến—
 Đó là logic cốt lõi của hệ thống, nền tảng để tiếp tục quan sát, và giao thức bất di bất dịch của Tethys.</t>
@@ -27141,8 +27141,8 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Aero DMG&lt;/color&gt;&lt;/color&gt; cao hơn.
-Một Discord giống sói thống trị vùng cao độ, nổi tiếng với bản năng săn mồi không ngừng nghỉ.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;&lt;/color&gt; cao hơn.
+Một Tacet Discord giống sói thống trị vùng cao độ, nổi tiếng với bản năng săn mồi không ngừng nghỉ.
 Chúng thường săn theo bầy, truy đuổi con mồi với tốc độ hung hãn.</t>
         </is>
       </c>
@@ -27210,8 +27210,8 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord hình sói lang thang ở những vùng đất bị bão tố vây quanh, nổi tiếng với bản tính hung hãn và tốc độ như chớp.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình sói lang thang ở những vùng đất bị bão tố vây quanh, nổi tiếng với bản tính hung hãn và tốc độ như chớp.
 Chúng thường săn mồi theo bầy, nhắm đến những đòn kết liễu nhanh gọn và chính xác.</t>
         </is>
       </c>
@@ -27279,8 +27279,8 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Một Discord giống sói hoành hành ở vùng băng giá, nổi tiếng với bản tính lạnh lùng và tàn nhẫn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Một Tacet Discord giống sói hoành hành ở vùng băng giá, nổi tiếng với bản tính lạnh lùng và tàn nhẫn.
 Chúng thường săn mồi theo bầy, thực hành nghệ thuật giết chóc dã man.</t>
         </is>
       </c>
@@ -27347,8 +27347,8 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord luôn tìm kiếm "thân xác" phù hợp. Nó đóng vai trò "đầu" của Chop Chop.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord luôn tìm kiếm "thân xác" phù hợp. Nó đóng vai trò "đầu" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -27414,8 +27414,8 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Discord luôn tìm kiếm một "thân thể" phù hợp. Nó đóng vai trò "bàn tay trái" của Chop Chop.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord luôn tìm kiếm một "thân thể" phù hợp. Nó đóng vai trò "bàn tay trái" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -27481,8 +27481,8 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Một Discord luôn tìm kiếm một "thân xác" phù hợp. Nó đóng vai trò như "cánh tay phải" của Chop Chop.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Một Tacet Discord luôn tìm kiếm một "thân xác" phù hợp. Nó đóng vai trò như "cánh tay phải" của Chop Chop.</t>
         </is>
       </c>
     </row>
@@ -27549,9 +27549,9 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Một Discord hình chim săn mồi ở Penitent's End. Trong bóng tối, hình dáng của nó hòa vào màn đêm, chỉ còn chiếc mặt nạ lấp lánh như ignis fatuus.
-Fae Ignis dùng ngọn lửa ma quái để thiêu đốt mọi thứ xung quanh, thích thú với sự hỗn loạn mà nó gây ra. Sự nghịch ngợm này thường kích động các Discord khác vào cơn điên cuồng, đồng thời phá hoại tài sản của những kẻ xấu số đi ngang qua.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Một Tacet Discord hình chim săn mồi ở Penitent's End. Trong bóng tối, hình dáng của nó hòa vào màn đêm, chỉ còn chiếc mặt nạ lấp lánh như ignis fatuus.
+Fae Ignis dùng ngọn lửa ma quái để thiêu đốt mọi thứ xung quanh, thích thú với sự hỗn loạn mà nó gây ra. Sự nghịch ngợm này thường kích động các Tacet Discord khác vào cơn điên cuồng, đồng thời phá hoại tài sản của những kẻ xấu số đi ngang qua.</t>
         </is>
       </c>
     </row>
@@ -27618,8 +27618,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Từng là sinh vật còn sót lại trong Nimbus Sanctum, nó dần thoái hóa thành Discord khi tần số suy yếu, để rồi lang thang trong nỗi buồn triền miên.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Từng là sinh vật còn sót lại trong Nimbus Sanctum, nó dần thoái hóa thành Tacet Discord khi tần số suy yếu, để rồi lang thang trong nỗi buồn triền miên.
 Kể từ khi Lorelei tự giam mình trong Atrium of Reflections và ngừng cất tiếng hát, những Nimbus Wraiths từng thịnh vượng dưới sự hiện diện của nàng giờ đây trở nên bất an, trôi dạt vô định khắp vùng.</t>
         </is>
       </c>
@@ -27686,8 +27686,8 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Một Discord vô hình trú ngụ trong thân xác của một con thú nhồi bông đẹp đẽ, quyến rũ. Hắn say sưa trong những tràng vỗ tay và tiếng hoan hô từ những màn ảo thuật mắt chói tai hoa—những tần số mà hắn thấy ngon lành nhất.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Một Tacet Discord vô hình trú ngụ trong thân xác của một con thú nhồi bông đẹp đẽ, quyến rũ. Hắn say sưa trong những tràng vỗ tay và tiếng hoan hô từ những màn ảo thuật mắt chói tai hoa—những tần số mà hắn thấy ngon lành nhất.</t>
         </is>
       </c>
     </row>
@@ -27753,8 +27753,8 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Discord vô hình trú ngụ trong thân xác của một con thú nhồi bông dịu dàng, giàu lòng trắc ẩn. Cô ta đối xử với bản thân bằng những bí mật và cảm xúc ẩn giấu—những tần số mà cô ta thấy ngon lành nhất.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord vô hình trú ngụ trong thân xác của một con thú nhồi bông dịu dàng, giàu lòng trắc ẩn. Cô ta đối xử với bản thân bằng những bí mật và cảm xúc ẩn giấu—những tần số mà cô ta thấy ngon lành nhất.</t>
         </is>
       </c>
     </row>
@@ -27820,8 +27820,8 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Discord ngụy trang thành rương tiếp tế, lợi dụng lòng tham của nạn nhân rồi nuốt chửng những kẻ đến gần. Đến nay, chưa học giả nào xác định được khả năng tiêu thụ của Chest Mimic lớn đến đâu. Một số ghi chép cho thấy nó có xu hướng kỳ lạ là nuốt chửng đồng loại, hấp thụ luôn kho báu mà chúng đã chiếm đoạt. Do đó, trong báo cáo Ecoacoustics của Pioneer Association, nó thường được gọi là "Búp Bê Lồng Rinascita".</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord ngụy trang thành rương tiếp tế, lợi dụng lòng tham của nạn nhân rồi nuốt chửng những kẻ đến gần. Đến nay, chưa học giả nào xác định được khả năng tiêu thụ của Chest Mimic lớn đến đâu. Một số ghi chép cho thấy nó có xu hướng kỳ lạ là nuốt chửng đồng loại, hấp thụ luôn kho báu mà chúng đã chiếm đoạt. Do đó, trong báo cáo Ecoacoustics của Hiệp hội Pioneer, nó thường được gọi là "Búp Bê Lồng Rinascita".</t>
         </is>
       </c>
     </row>
@@ -27889,9 +27889,9 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord hình người, khoác trang phục sang trọng, cầm lưỡi kiếm sắc bén và sở hữu sức mạnh phi thường chỉ có trong truyền thuyết.
-Tương truyền đó là linh hồn của những anh hùng đã ngã xuống, từng được chứng kiến tiêu diệt các Discord khác để bảo vệ dân làng. Nhưng những hành động ấy chỉ xuất phát từ bản năng thèm khát chiến đấu.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình người, khoác trang phục sang trọng, cầm lưỡi kiếm sắc bén và sở hữu sức mạnh phi thường chỉ có trong truyền thuyết.
+Tương truyền đó là linh hồn của những anh hùng đã ngã xuống, từng được chứng kiến tiêu diệt các Tacet Discord khác để bảo vệ dân làng. Nhưng những hành động ấy chỉ xuất phát từ bản năng thèm khát chiến đấu.
 Dù đã mất đi trái tim, nó vẫn cố níu giữ những tàn tích danh dự xưa cũ, lang thang cô độc giữa thế gian đầy thách thức.</t>
         </is>
       </c>
@@ -27960,9 +27960,9 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Một Discord hình người, khoác bộ lễ phục trang nhã, cầm lưỡi kiếm sắc bén. Chỉ xuất hiện dưới ánh mặt trời rực rỡ.
-Người ta nói đó là linh hồn lạc lối của những anh hùng đã ngã xuống, vẫn giữ được khí chất uy nghiêm ngay cả khi trở thành Discord.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình người, khoác bộ lễ phục trang nhã, cầm lưỡi kiếm sắc bén. Chỉ xuất hiện dưới ánh mặt trời rực rỡ.
+Người ta nói đó là linh hồn lạc lối của những anh hùng đã ngã xuống, vẫn giữ được khí chất uy nghiêm ngay cả khi trở thành Tacet Discord.
 Từng là một hiệp sĩ đã quên mất danh hiệu mình từng mang, nó đã mất tất cả những gì mình thề bảo vệ. Giờ đây, chỉ còn lại nỗi ám ảnh không lay chuyển về danh dự.</t>
         </is>
       </c>
@@ -28031,8 +28031,8 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Một Discord hình người, khoác lên mình bộ trang phục sang trọng, tay cầm lưỡi kiếm sắc bén. Chỉ xuất hiện dưới ánh trăng mờ ảo.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
+Một Tacet Discord hình người, khoác lên mình bộ trang phục sang trọng, tay cầm lưỡi kiếm sắc bén. Chỉ xuất hiện dưới ánh trăng mờ ảo.
 Tương truyền, chúng là những bóng ma của các anh hùng ngày xưa, dù đã mục rữa thành TD nhưng vẫn giữ được phong thái hiệp sĩ.
 Những hiệp sĩ vinh quang đã quên mất danh hiệu của mình. Những người bảo vệ chẳng còn gì để bảo vệ, chỉ còn bị ám ảnh bởi danh dự không ngừng nghỉ.</t>
         </is>
@@ -28103,8 +28103,8 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Discord hình người sinh ra từ vực thẳm biển cả, mang dáng dấp của một quý tộc, là hình thái hoàn thiện của Primordia Bloom.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tacet Discord hình người sinh ra từ vực thẳm biển cả, mang dáng dấp của một quý tộc, là hình thái hoàn thiện của Primordia Bloom.
 Ban đầu, Abyssal Patricius chẳng khác gì một Primordia Bloom, sinh vật có thể hấp thụ tần số của kẻ khác để bắt chước hình hài và hòa nhập hoàn hảo với đồng loại của con mồi.
 Có lẽ hắn từng là một quý tộc bất hạnh cố trở về Thorncrown Rises, chỉ để trở thành thức ăn cho vô số tế bào gai.
 "Hãy nhìn xem, chỉ có sự sa ngã của một quý tộc mới sinh ra kẻ khác," đám Fisalias từng nói như vậy.</t>
@@ -28175,8 +28175,8 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Discord hình người sinh ra từ biển sâu, mang hình dáng của một hiệp sĩ quý tộc, là dạng hoàn thiện của Primordia Bloom.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình người sinh ra từ biển sâu, mang hình dáng của một hiệp sĩ quý tộc, là dạng hoàn thiện của Primordia Bloom.
 Ở giai đoạn đầu, Abyssal Gladius không khác gì Primordia Bloom, một sinh vật có khả năng hấp thụ tần số của kẻ khác để bắt chước hình dạng và hòa nhập hoàn hảo với đồng loại của con mồi.
 Có lẽ hắn từng là một hiệp sĩ liều lĩnh xông vào Thorncrown Rises, chỉ để trở thành thức ăn cho vô số tế bào gai.</t>
         </is>
@@ -28246,8 +28246,8 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Discord hình người sinh ra từ biển sâu, mang hình dáng của một thương nhân quý tộc, là dạng hoàn thiện của Primordia Bloom.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;DMG Glacio&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord hình người sinh ra từ biển sâu, mang hình dáng của một thương nhân quý tộc, là dạng hoàn thiện của Primordia Bloom.
 Ở giai đoạn đầu, Abyssal Mercator không khác gì Primordia Bloom, một sinh vật có khả năng hấp thụ tần số của kẻ khác để bắt chước hình dạng và hòa nhập hoàn hảo với đồng loại của con mồi.
 Có lẽ hắn từng là một thương nhân tham lam đánh giá thấp hiểm nguy của Thorncrown Rises, chỉ để trở thành thức ăn cho vô số tế bào gai.</t>
         </is>
@@ -28317,10 +28317,10 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord luôn tìm kiếm "thân xác" phù hợp.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord luôn tìm kiếm "thân xác" phù hợp.
 Tương truyền rằng sau khi các hiệp sĩ đánh bại gã khổng lồ độc ác, Dư Âm của nó phân rã thành những Chop Chop lang thang, vô định tìm cách khôi phục hình hài huy hoàng ngày nào.
-Discord này thường lơ lửng trên những công trình lớn, giả vờ tạo dáng uy nghiêm như thể tòa nhà là phần thân thể của nó. Bóng dáng nó hòa vào kiến trúc, sừng sững như một gã khổng lồ đầy đe dọa.</t>
+Tacet Discord này thường lơ lửng trên những công trình lớn, giả vờ tạo dáng uy nghiêm như thể tòa nhà là phần thân thể của nó. Bóng dáng nó hòa vào kiến trúc, sừng sững như một gã khổng lồ đầy đe dọa.</t>
         </is>
       </c>
     </row>
@@ -28388,7 +28388,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28456,7 +28456,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
 Một cỗ máy chiến đấu chính xác và mạnh mẽ, được cải tiến bằng công nghệ đặc biệt. Nó thực hiện mệnh lệnh của chủ nhân với lòng trung thành tuyệt đối.
 Mọi dấu vết về hình hài ban đầu đều đã phai mờ, chỉ còn lại bản năng chiến đấu sắc bén trong tần số của nó. Là một kẻ bảo vệ bất khuất, nó thích nghi hoàn hảo với mọi loại hình chiến đấu. Khi cần, nó kích hoạt một bộ phận đặc biệt để tăng cường khả năng di chuyển hoặc giải phóng toàn bộ năng lượng trong một vụ nổ hủy diệt.
 Gia tộc Montelli, những kẻ du hành từ phương xa, đã chứng kiến một thế giới rộng lớn hơn—và họ sẵn sàng trả bất cứ giá nào để có được sức mạnh cần thiết hồi sinh quê hương.</t>
@@ -28527,10 +28527,10 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord hình rồng ẩn náu trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số không phân biệt. Bị vặn xoắn bởi những tần số của sự mục nát và cái chết mà nó hấp thụ, giờ đây nó hiện lên như một quái thú khủng khiếp với bộ xương trần trụi.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord hình rồng ẩn náu trên đỉnh Penitent's End vì lý do bí ẩn, nuốt chửng mọi tần số không phân biệt. Bị vặn xoắn bởi những tần số của sự mục nát và cái chết mà nó hấp thụ, giờ đây nó hiện lên như một quái thú khủng khiếp với bộ xương trần trụi.
 Nơi từng là thánh địa nay đã trở thành nấm mồ của đau thương, và bất cứ ai đến tìm sự cứu rỗi đều phải đối mặt với ngọn lửa phán xét của nó.
-Đó chính là Gehinom, Dragon Than Khóc, ngọn lửa của nó thiêu đốt đến tận xương tủy, nỗi đau vang vọng, khao khát một sự giải thoát cuối cùng.</t>
+Đó chính là Gehinom, Rồng Than Khóc, ngọn lửa của nó thiêu đốt đến tận xương tủy, nỗi đau vang vọng, khao khát một sự giải thoát cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -28596,8 +28596,8 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -28663,8 +28663,8 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -28730,8 +28730,8 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
         </is>
       </c>
     </row>
@@ -28797,8 +28797,8 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
         </is>
       </c>
     </row>
@@ -28864,8 +28864,8 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -28931,8 +28931,8 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -28998,8 +28998,8 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Các Nút Giấc Mơ. Nó thu thập tần số của một loại cảm xúc tiêu cực nhất định.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Các Nút Giấc Mơ. Nó thu thập tần số của một loại cảm xúc tiêu cực nhất định.</t>
         </is>
       </c>
     </row>
@@ -29067,8 +29067,8 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere – nơi hội tụ mọi tần số suy tàn, còn gọi là "Vùng Ngoài". Nó hiện thân như một Phù Thủy Ba Mặt của Âm Phủ.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere – nơi hội tụ mọi tần số suy tàn, còn gọi là "Vùng Ngoài". Nó hiện thân như một Phù Thủy Ba Mặt của Âm Phủ.
 Kẻ phàm tục chỉ là tù nhân của số phận, những đấu tranh của họ chẳng qua là ảo ảnh thoáng qua. Khi trăng tròn khuyết, chỉ có cái chết và sự lãng quên là bất biến.
 Trên sân khấu dệt từ những đóa Lycoris đỏ thẫm, nàng hòa tấu cùng Phrolova, cùng nhau dệt nên một bản giao hưởng "hoàn hảo" của tuyệt vọng.</t>
         </is>
@@ -29139,11 +29139,10 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Maiden giả tạo, một chiếc bình được tạo ra bởi đôi tay thần thánh.
+          <t>Thiếu nữ nhân tạo, một chiếc bình được tạo ra bởi đôi tay thần thánh.
 Sự ra đời của nàng chỉ là một âm mưu được dàn dựng kỹ lưỡng. Cuộc đời nàng chỉ là điệu múa của con rối trên sợi dây định mệnh.
-Thế nhưng, khi nàng nhìn vào quá khứ được sắp đặt và khao khát một tương lai mà nàng hằng mong ước, thanh kiếm nàng cầm sẽ chặt đứt chính những xiềng xích của số phận.
-Và giờ đây, nàng khao khát một &lt;ano=Rebirth&gt;End&lt;/ano&gt;.</t>
+Thế nhưng, khi nhìn vào quá khứ được thiết kế sẵn và khao khát tương lai mà nàng hằng mong ước, thanh kiếm nàng cầm sẽ chặt đứt gông cùm của số phận.
+Và giờ đây, nàng khao khát một &lt;ano=Rebirth&gt;Kết thúc&lt;/ano&gt;.</t>
         </is>
       </c>
     </row>
@@ -29209,8 +29208,8 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -29276,8 +29275,8 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -29345,8 +29344,8 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Nàng là người bảo vệ Thành Phố Glory, một sư tử cái dũng mãnh của đấu trường.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Nàng là người bảo vệ Thành Phố Vinh Quang, một sư tử cái dũng mãnh của đấu trường.
 Được đúc từ những viên đá trắng tinh khiết như tượng Gryphon, tôi luyện trong tiếng gào thét chiến trận và nụ cười của những anh hùng.
 Đây là Arsinosa, kiên trung bất khuất, mãi mãi canh giữ vinh quang của Septimont.</t>
         </is>
@@ -29416,7 +29415,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Một tín đồ của tuyệt vọng, linh hồn sa ngã bị nuốt chửng bởi thiên đường ảo mộng.
 Khi mặt nạ của Dark Tide rơi xuống, hắn mới nhận ra chân tướng ở cuối con đường—hy vọng và cứu rỗi đã đổi lấy một thân xác mục nát.
 Hắn sẽ mãi yên giấc dưới đáy biển đen tối, bởi đó cũng là con đường về nhà.</t>
@@ -29485,8 +29484,8 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -29552,8 +29551,8 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -29619,8 +29618,8 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -29686,8 +29685,8 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -29753,8 +29752,8 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
         </is>
       </c>
     </row>
@@ -29820,8 +29819,8 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -29887,8 +29886,8 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số cảm xúc tiêu cực đặc trưng.</t>
         </is>
       </c>
     </row>
@@ -29954,8 +29953,8 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -30021,8 +30020,8 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -30088,8 +30087,8 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -30156,8 +30155,8 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord khổng lồ hiếm thấy cư ngụ tại High nguyên Sanguis, được bảo vệ bởi lớp vảy cứng và phun ra nham thạch nóng chảy. Chiếc mào lởm chởm vươn cao, biểu tượng cho sự thống trị của nó.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord khổng lồ hiếm thấy cư ngụ tại Cao nguyên Sanguis, được bảo vệ bởi lớp vảy cứng và phun ra nham thạch nóng chảy. Chiếc mào lởm chởm vươn cao, biểu tượng cho sự thống trị của nó.
 Xuất hiện cùng với Dark Tide, tiếng gầm của Corrosaurus báo hiệu khởi đầu cho một cuộc săn lùng huy hoàng của các Chiến Binh Septimont.</t>
         </is>
       </c>
@@ -30226,9 +30225,9 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một bản sao hình người được tạo từ bùn nhơ, kẻ giả vương, ý chí của Dark Tide hiện thân.
-Sinh ra từ giấc mơ utopia về Sự Thống Nhất của Threnodian, nó là khối bùn đen vô định hình được trao cho hình hài, một chiếc bình chỉ để nuốt chửng. Mọi thứ đều phải hòa nhập vào thân thể của False Sovereign và tái sinh thành tôi tớ, con cái của Leviathan.
+Sinh ra từ giấc mơ utopia về Sự Thống Nhất của Threnodian, nó là khối bùn đen vô định hình được trao cho hình hài, một chiếc bình chỉ để nuốt chửng. Mọi thứ đều phải hòa nhập vào thân thể của Kẻ Giả Vương và tái sinh thành tôi tớ, con cái của Leviathan.
 Nó không suy nghĩ. Nó không cảm nhận. Chỉ có những làn sóng bùn nhơ thì thầm những bài thánh ca giả dối, ca tụng quyền năng của Leviathan đến muôn đời.</t>
         </is>
       </c>
@@ -30297,7 +30296,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Một xác chết trôi dạt trong dòng nước băng giá, nơi năng lượng còn sót lại của Threnodian trú ngụ.
 Nàng đã tự đâm xuyên trái tim mình và rơi xuống biển sâu. Nhưng số phận, tàn nhẫn như những xoáy nước dưới kia, lại kéo nàng xuống sâu hơn nữa.
 Giờ đây, kẻ tạo ra nàng đã chiếm lấy xác thất bại này, nằm chờ dưới đáy biển để nuốt chửng cả thế giới.</t>
@@ -30366,8 +30365,8 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -30433,8 +30432,8 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực.</t>
         </is>
       </c>
     </row>
@@ -30501,8 +30500,8 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Một Discord hình người, lưng gù với dòng điện chạy khắp các mạch máu và một phần phụ giống roi điện trên đầu.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
+Một Tacet Discord hình người, lưng gù với dòng điện chạy khắp các mạch máu và một phần phụ giống roi điện trên đầu.
 Quan sát cho thấy roi phân đoạn của nó có thể bất ngờ phóng điện cao thế. Đầu roi cực kỳ nhạy cảm với kích thích, cho phép kẻ địch này khóa chặt và khống chế mục tiêu trong nháy mắt. Nó chủ yếu tấn công bằng vuốt nhanh và những cú quất roi liên tục.</t>
         </is>
       </c>
@@ -30569,8 +30568,8 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực đặc biệt từ khắp Ragunna.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực đặc biệt từ khắp Ragunna.</t>
         </is>
       </c>
     </row>
@@ -30636,7 +30635,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
 Để khám phá Lahai-Roi hiệu quả hơn, Viện Nghiên Cứu đã triển khai robot Geospider. Ở phiên bản S4, khả năng di chuyển và thu thập thông tin của Geospider là vô song. Chúng thường được mang theo trong các chuyến thám hiểm khoa học và trang bị bộ cảm biến chính xác cao để tự vệ cũng như bảo vệ nhân sự.</t>
         </is>
       </c>
@@ -30703,7 +30702,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.
 Những kẻ Roya bị bộ tộc trục xuất vì bán tế bào Exostrider. Tuy nhiên, chúng tự cho mình thoát khỏi những lề thói cũ. Để chế giễu truyền thống, chúng đeo mặt nạ làm từ đầu Exoswarm và sử dụng Shepherd's Staff làm vũ khí, trở thành thế lực hỗn loạn không gì kiềm chế nổi ở Lahai-Roi.</t>
         </is>
       </c>
@@ -30772,7 +30771,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
 Zip Zap là một loại Murmurin TD bọc thép điện từ, thu hút kim loại để tạo vỏ bảo vệ quanh mình. Những tia lửa điện lấp lánh hiện ra qua các vết nứt trên lớp giáp kim loại.
 Chúng có thể bám vào các Tacet Discord Clamorling khác để khuếch đại năng lượng. Khi cạn kiệt, Zip Zap sẽ đảo chiều dòng điện để tự nạp lại.
 Người dân ở Lahai-Roi thường bắt Zip Zap ngoài tự nhiên để dùng làm nguồn điện dự phòng.</t>
@@ -30841,8 +30840,8 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực đặc biệt từ khắp Ragunna.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập các tần số của một loại cảm xúc tiêu cực đặc biệt từ khắp Ragunna.</t>
         </is>
       </c>
     </row>
@@ -30908,8 +30907,8 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes. Nó thu thập những tần số của một loại cảm xúc tiêu cực cụ thể.</t>
         </is>
       </c>
     </row>
@@ -30978,8 +30977,8 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Twin Nova: Nebulous Cannon sở hữu Mô-đun Đồng Bộ Combat hàng đầu. Kết hợp với Twin Nova: Collapsar Blade, khả năng phối hợp chiến đấu của chúng biến thành một điệu nhảy chết chóc với những đòn tấn công đa hướng.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Twin Nova: Nebulous Cannon sở hữu Mô-đun Đồng Bộ Chiến Đấu hàng đầu. Kết hợp với Twin Nova: Collapsar Blade, khả năng phối hợp chiến đấu của chúng biến thành một điệu nhảy chết chóc với những đòn tấn công đa hướng.
 Khi Twin Nova: Nebulous Cannon bị Tune Break, nó chịu thêm 20% tổng Sát Thương trong 30 giây, có thể chồng chất lên đến 3 lần.
 Các mech Twin Nova được chế tạo để thám hiểm bên ngoài Stridergate. Nebulous Cannon là phiên bản tầm xa. Hình dáng người của chúng thể hiện khát vọng khám phá vực thẳm của nhân loại khi ngước nhìn bầu trời sao.
 Khi hợp nhất, cặp Twin Nova thể hiện khả năng chiến đấu chưa từng có.</t>
@@ -31051,9 +31050,9 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Twin Nova: Collapsar Blade được trang bị Mô-đun Đồng Bộ Combat tối tân. Khi kết hợp với Twin Nova: Nebulous Cannon, sự phối hợp giữa chúng biến thành điệu nhảy chết chóc với những đòn tấn công đa hướng.
-Khi Twin Nova: Collapsar Blade bị Tune Break, tổng sát thương nhận vào sẽ tăng 20% trong 30 giây, tối đa 3 lần cộng dồn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Twin Nova: Collapsar Blade được trang bị Mô-đun Đồng Bộ Chiến Đấu tối tân. Khi kết hợp với Twin Nova: Nebulous Cannon, sự phối hợp giữa chúng biến thành điệu nhảy chết chóc với những đòn tấn công đa hướng.
+Khi Twin Nova: Collapsar Blade bị Tune Break, tổng DMG nhận vào sẽ tăng 20% trong 30 giây, tối đa 3 lần cộng dồn.
 Cặp mech Twin Nova được chế tạo để khám phá bên ngoài Stridergate. Collapsar Blade là phiên bản cận chiến. Hình dáng người máy của chúng thể hiện khát vọng vươn tới vực thẳm vũ trụ của nhân loại khi ngước nhìn bầu trời sao.
 Khi kết hợp, cặp Twin Nova sẽ phát huy sức mạnh chiến đấu vượt trội chưa từng có.</t>
         </is>
@@ -31122,7 +31121,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Những chiếc gạc cơ khí trên đầu nó có thể bị phá hủy bằng Phản Đòn. Phá vỡ thành công gạc sẽ làm giảm sức tấn công của nó.
 Sau khi quét dữ liệu các loài động vật trong quá khứ ở Lahai-Roi, Exostrider đã sử dụng chính bộ phận của mình để phát triển và nhân bản những con tuần lộc cơ khí. Những Flora Reindeer này là bạn đồng hành của Roya và hỗ trợ Roya trong việc tìm kiếm thực vật.</t>
         </is>
@@ -31192,8 +31191,8 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Chùm xung kích của Mining Reindeer có thể bị phản đòn để gây sát thương cho chính nó.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
+Chùm xung kích của Mining Reindeer có thể bị phản đòn để gây DMG cho chính nó.
 Các nhánh gạc cơ khí trên đầu có thể bị phá hủy bằng phản công. Phá vỡ thành công sẽ làm giảm sức tấn công của nó.
 Sau khi quét dữ liệu các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân bản và phát triển những chú tuần lộc cơ khí. Những chú Mining Reindeer này là bạn đồng hành của Roya và hỗ trợ chúng khai thác quặng.</t>
         </is>
@@ -31263,9 +31262,9 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
 Hai chiếc sừng cơ khí trên đầu nó có thể bị phá hủy bằng phản công. Phá vỡ sừng sẽ làm giảm sức tấn công và tầm đánh của nó.
-Khi Ironhoof ở trạng thái Tacet Discord - Dịch Chuyển và bị Tune Break, nó sẽ chịu thêm 30% tổng sát thương trong 15 giây.
+Khi Ironhoof ở trạng thái Tacet Discord - Dịch Chuyển và bị Tune Break, nó sẽ chịu thêm 30% tổng DMG trong 15 giây.
 Sau khi quét dữ liệu của các loài động vật cổ xưa ở Lahai-Roi, Exostrider đã dùng chính bộ phận của mình để nhân giống và phát triển loài bò xạ cơ khí. Nhờ lớp giáp cứng cáp giúp Ironhoof chịu đựng được cái lạnh khắc nghiệt trong những chuyến đi dài, người Roya thường dùng chúng để vận chuyển hàng hóa nặng.</t>
         </is>
       </c>
@@ -31334,7 +31333,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
 Spacetrek Explorer sở hữu giáp trụ vững chắc cùng khả năng cơ động vượt trội. Nó được trang bị súng điện từ và máy phát khiên có thể mở rộng bảo vệ cho đồng minh.
 Tấn công Spacetrek Explorer bằng Tune Break sẽ vô hiệu hóa máy phát khiên, loại bỏ khiên hiện tại và ngăn không cho khiên mới xuất hiện.
 Trước những vùng đất bí ẩn rộng lớn ở Lahai-Roi, Spacetrek Collective đã phát triển Spacetrek Explorer đa năng để phục vụ vận tải, lưu trữ và phòng thủ. Chân bánh xe và lốp chịu lực giúp nó di chuyển linh hoạt trên cả bề mặt thẳng đứng, phù hợp cho cả địa hình đô thị lẫn hoang dã. Các khoang chứa trên bo mạch được thiết kế để hỗ trợ các chuyến thám hiểm khoa học dài hạn.</t>
@@ -31404,8 +31403,8 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Khi Sabercat Reaver ở trạng thái Tacet Discord - Dịch Chuyển và bị Tune Break, nó sẽ chịu thêm sát thương bằng 25% HP tối đa, chỉ kích hoạt một lần.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; cao hơn đối với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Khi Sabercat Reaver ở trạng thái Tacet Discord - Dịch Chuyển và bị Tune Break, nó sẽ chịu thêm DMG bằng 25% HP tối đa, chỉ kích hoạt một lần.
 Cỗ máy săn mồi này chỉ có một mục đích duy nhất: xé nát mọi thứ trên đường đi. Nó rình rập khắp vùng hoang dã Lahai-Roi, săn lùng bất kỳ dấu hiệu chuyển động nào. Với tiếng gầm rít không ngừng của lưỡi cưa gắn đuôi, nó truy sát mục tiêu với hiệu quả tàn nhẫn.</t>
         </is>
       </c>
@@ -31475,10 +31474,10 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Khi Sabercat Prowler ở trạng thái Tàng Hình, toàn bộ Kháng Thuộc Tính của nó tăng thêm 30%.
 Tấn công bằng Tune Break sẽ buộc nó phải rời khỏi trạng thái Tàng Hình.
-Khi Sabercat Prowler chịu hiệu ứng Tune Rupture - Shifting và bị tấn công bằng Tune Break, nó sẽ nhận thêm sát thương bằng 25% HP tối đa, chỉ kích hoạt một lần.
+Khi Sabercat Prowler chịu hiệu ứng Tune Rupture - Shifting và bị tấn công bằng Tune Break, nó sẽ nhận thêm DMG bằng 25% HP tối đa, chỉ kích hoạt một lần.
 Một cỗ máy có khả năng ngụy trang, nhưng các bộ phận đã bị Voidmatter ăn mòn nặng, khiến thị giác và thính giác bị suy giảm nghiêm trọng. Tuy nhiên, điều này lại làm tăng cường các giác quan khác. Nó theo dõi chuyển động của kẻ địch bằng cách sử dụng cảm biến trên đuôi để phát hiện sự thay đổi tần số.</t>
         </is>
       </c>
@@ -31611,8 +31610,8 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
-Băng Giá Coleoid miễn nhiễm với Trạng Thái Tiêu Cực Glacio Chafe, nhưng chịu thêm 80% tổng sát thương từ các Trạng Thái Tiêu Cực khác và Kỹ Năng Echo.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
+Băng Giá Coleoid miễn nhiễm với Trạng Thái Tiêu Cực Glacio Chafe, nhưng chịu thêm 80% tổng DMG từ các Trạng Thái Tiêu Cực khác và Kỹ Năng Echo.
 Một sinh vật ký sinh sống bên trong Tacet Discord Whisperin, dùng cơ thể vật chủ như kén và hấp thụ tần số của nó. Nhiễm Băng Giá Coleoid khiến vật chủ trở nên hung hãn và thôi thúc chúng hấp thụ tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Băng Giá Coleoid sẽ rời khỏi vật chủ bằng cách phá vỡ lưng nó.</t>
         </is>
       </c>
@@ -31680,7 +31679,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; cao hơn.
 Windlash Coleoid miễn nhiễm với Aero Erosion, nhưng chịu thêm 80% tổng Sát Thương từ các Trạng Thái Tiêu Cực và Kỹ Năng Echo khác.
 Một sinh vật ký sinh sống bên trong Whisperin Tacet Discord, sử dụng cơ thể vật chủ như kén và hút lấy tần số của nó. Nhiễm Windlash Coleoid khiến vật chủ trở nên hung hăng và thôi thúc ăn tần số của các Tacet Discord khác. Sau thời gian ủ bệnh, Windlash Coleoid sẽ rời vật chủ bằng cách phá vỡ lưng nó.</t>
         </is>
@@ -31751,8 +31750,8 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; khi ở dạng người. 
-Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; khi ở dạng người. 
+Khi nổi giận, hắn biến thành một tử thần dê u ám với &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; đối với &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một trong những Fractsidus Overseers.
 Một kẻ nổi loạn say mê Overclocking, phớt lờ vẻ đẹp và trật tự. Hắn thích hủy diệt và hỗn loạn, vui sướng trước nỗi đau của người khác. Hắn coi thường luật lệ và danh tiếng, sẵn sàng dùng mọi thủ đoạn để đạt mục tiêu. Với sự tỉnh táo nội tâm thúc đẩy, hắn tìm đến ngươi để chứng kiến sự ra đời của một thế giới mới, vẫn còn trong giai đoạn sơ khai.
 &lt;i&gt;"Sự sống mới nở rộ từ tro tàn, vươn lên từ đống đổ nát."&lt;/i&gt;</t>
@@ -31823,8 +31822,8 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere – nơi hội tụ mọi tần số suy tàn, còn gọi là "Vùng Ngoài". Nó hiện thân như một Phù Thủy Ba Mặt của Âm Phủ.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord đặc biệt được Phrolova triệu hồi từ Sonoro Sphere – nơi hội tụ mọi tần số suy tàn, còn gọi là "Vùng Ngoài". Nó hiện thân như một Phù Thủy Ba Mặt của Âm Phủ.
 Kẻ phàm tục chỉ là tù nhân của số phận, những đấu tranh của họ chẳng qua là ảo ảnh thoáng qua. Khi trăng tròn khuyết, chỉ có cái chết và sự lãng quên là bất biến.
 Trên sân khấu dệt từ những đóa Lycoris đỏ thẫm, nàng hòa tấu cùng Phrolova, cùng nhau dệt nên một bản giao hưởng "hoàn hảo" của tuyệt vọng.</t>
         </is>
@@ -31895,7 +31894,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
 "Thần tính" nắm giữ sức mạnh hợp nhất. Một Threnodian bắt nguồn từ nền văn minh Rinascita.
 Tần số của nó, từng bị xiềng xích bởi Sentinel, đã được tái sinh qua Viên Ngọc. Mang hình hài của Blessed Maiden xưa kia, Fleurdelys, nó đã tạo nên một thân xác mới cho mình.
 Sinh ra từ khao khát sống và nuôi dưỡng bởi nỗi sợ hãi vĩnh cửu ám ảnh mọi sinh linh, nó không ngừng dõi theo, im lặng như vực thẳm.
@@ -31969,8 +31968,8 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Khi Hyvatia mở Mắt Tiên Tri, nó sẽ quan sát và ghi lại những pha Dodge và Phản Đòn của Resonators. Sau khi Mắt đóng lại, đòn tấn công tiếp theo của Hyvatia sẽ không thể Dodge hay Phản Đòn được.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Khi Hyvatia mở Mắt Tiên Tri, nó sẽ quan sát và ghi lại những pha Né Tránh và Phản Đòn của Resonator. Sau khi Mắt đóng lại, đòn tấn công tiếp theo của Hyvatia sẽ không thể Né Tránh hay Phản Đòn được.
 Hyvatia chịu tổng Sát Thương Vỡ Nhịp gấp 100%. Khi đang chịu hiệu ứng Vỡ Nhịp - Dao Động và bị Vỡ Nhịp, nó sẽ chịu thêm 15% tổng Sát Thương trong 15 giây.
 Hyvatia là hệ thống dò tìm đầu tiên của Spacetrek Collective được xây dựng tại Sundermere để giám sát và ổn định trạng thái năng lượng của Reactor Drive theo thời gian thực.
 Viện Nghiên Cứu đã cấy mô-đun hiệu chỉnh lỗi không-thời gian của Exostrider vào lõi của Hyvatia, cho phép nó điều chỉnh quỹ đạo của Exostrider và phát hiện các mối đe dọa ẩn trong không gian với độ chính xác cao. Do đó, Hyvatia sở hữu đủ sức mạnh tính toán để dự đoán vòng quay của Reactor Drive.
@@ -32045,10 +32044,10 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Đòn tấn công tầm xa đặc biệt Cinder Cut của Reactor Husk có thể bị phản đòn, gây sát thương ngược lại và giảm Vibration Strength của nó.
-Sau khi tấn công hoặc chịu phản đòn nhiều lần, một Vulnerable Core sẽ lộ ra trên cánh tay trái của Reactor Husk. Attack lõi này sẽ phá hủy giáp của Reactor Husk, khiến nó không thể tấn công.
-Gây Trạng Thái Tiêu Cực cho Reactor Husk sẽ ngay lập tức lộ ra Vulnerable Core. Nếu giáp của Reactor Husk bị phá hủy trong khi đang chịu Trạng Thái Tiêu Cực, tổng sát thương từ các Trạng Thái Tiêu Cực sẽ tăng 100% trong 30 giây. Trong thời gian hiệu ứng này, lõi sẽ không còn lộ ra.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Đòn tấn công tầm xa đặc biệt Cinder Cut của Reactor Husk có thể bị phản đòn, gây DMG ngược lại và giảm Vibration Strength của nó.
+Sau khi tấn công hoặc chịu phản đòn nhiều lần, một Lõi Dễ Tổn Thương sẽ lộ ra trên cánh tay trái của Reactor Husk. Tấn công lõi này sẽ phá hủy giáp của Reactor Husk, khiến nó không thể tấn công.
+Gây Trạng Thái Tiêu Cực cho Reactor Husk sẽ ngay lập tức lộ ra Lõi Dễ Tổn Thương. Nếu giáp của Reactor Husk bị phá hủy trong khi đang chịu Trạng Thái Tiêu Cực, tổng DMG từ các Trạng Thái Tiêu Cực sẽ tăng 100% trong 30 giây. Trong thời gian hiệu ứng này, lõi sẽ không còn lộ ra.
 Sau khi Reactor Drive được Exostrider thiết lập phía trên Lahai-Roi, nó luôn cảnh giác cao độ với các hoạt động của Aleph-1.
 Khi phản ứng miễn dịch của Drive được kích hoạt, một "Reactor Husk" cơ khí sẽ trỗi dậy từ lòng giếng năng lượng, với mục đích duy nhất là tiêu diệt kẻ xâm nhập bằng mọi giá.
 Nghiên cứu của Spacetrek Collective cho thấy Reactor Husk từng là một phần của Exostrider. Cả hai đều chung sứ mệnh chống lại mối đe dọa Threnodian và bảo vệ nền văn minh.</t>
@@ -32117,8 +32116,8 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Khoác trên mình chiếc váy băng giá bay phấp phới, Discord hình người này di chuyển với dáng vẻ uyển chuyển như gió. Những lưỡi dao sắc bén dưới chân vẽ nên những vòng cung băng giá, giống như môn trượt băng nghệ thuật nhưng chỉ mang lại cái chết. Nó cảm nhận từng rung động trên mặt băng và đọc thế giới qua tấm gương băng. Từ những phản chiếu ấy, nó học được sự tao nhã, rồi biến sự tao nhã ấy thành vũ khí. Một môn nghệ thuật cao quý nay đã trở thành điệu múa im lặng của tử thần trong tay hắn.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Khoác trên mình chiếc váy băng giá bay phấp phới, Tacet Discord hình người này di chuyển với dáng vẻ uyển chuyển như gió. Những lưỡi dao sắc bén dưới chân vẽ nên những vòng cung băng giá, giống như môn trượt băng nghệ thuật nhưng chỉ mang lại cái chết. Nó cảm nhận từng rung động trên mặt băng và đọc thế giới qua tấm gương băng. Từ những phản chiếu ấy, nó học được sự tao nhã, rồi biến sự tao nhã ấy thành vũ khí. Một môn nghệ thuật cao quý nay đã trở thành điệu múa im lặng của tử thần trong tay hắn.</t>
         </is>
       </c>
     </row>
@@ -32184,8 +32183,8 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
-Một Discord hình người không mặt, thân thể tan chảy, phân rã rồi kết tụ như một bóng tối sống động. Bằng cách phân mảnh tần số của chính mình, nó có thể tạo ra một vùng không gian bóng tối để ẩn nấp. Khi con mồi đến gần, nó sẽ bùng nổ từ bóng đêm, tấn công từ những góc bất ngờ.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
+Một Tacet Discord hình người không mặt, thân thể tan chảy, phân rã rồi kết tụ như một bóng tối sống động. Bằng cách phân mảnh tần số của chính mình, nó có thể tạo ra một vùng không gian bóng tối để ẩn nấp. Khi con mồi đến gần, nó sẽ bùng nổ từ bóng đêm, tấn công từ những góc bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -32260,7 +32259,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Electro DMG&lt;/color&gt; &lt;color=Thunder&gt;cao hơn&lt;/color&gt;.
 Kẻ địch này có kháng tất cả thuộc tính cao hơn.
 Kẻ địch sở hữu khả năng Rage Feather và ba điểm yếu.
 Sau một thời gian chiến đấu, Kronablight sẽ bước vào trạng thái Rage Feather, tăng cường đáng kể sức tấn công.
@@ -32345,17 +32344,16 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; đối với &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Kẻ địch này có RES toàn thuộc tính cao hơn.
-Kẻ địch này sở hữu khả năng Rage Feather và ba điểm yếu.
-Sau một khoảng thời gian duy trì chiến đấu, Kronaclaw sẽ bước vào trạng thái Rage Feather, tăng mạnh ATK của nó.
-Điểm yếu I: Một đòn phản công thành công có thể làm tổn thương mào và cánh của nó, làm suy yếu các đòn tấn công và giảm số lượng đạn tầm xa.
-Điểm yếu II: Tune Break có thể loại bỏ trạng thái Rage Feather và giảm đạn tầm xa của nó.
-Điểm yếu đặc biệt: Khi Kronaclaw chịu hiệu ứng Tune Rupture - Shifting, sử dụng Tune Break sẽ làm giảm mạnh RES toàn thuộc tính của nó.
-Một loài mãnh thú cổ đại tuyệt chủng được tái tạo thông qua Upphaf Life Chamber.
-Trong quá khứ xa xưa, những con mãnh thú này từng thống trị bầu trời Lahai-Roi, bá quyền không đối thủ kể từ Kỷ Nguyên Đầu Tiên.
-Truyền thuyết kể rằng Kronaclaw là một sáng tạo của Sol, chia sẻ thị lực thần thánh của Eye of Sol và quan sát mọi thứ trên và dưới Lahai-Roi.
-Nhưng khi các cực từ thay đổi và cảnh quan bị biến đổi, loài Kronaclaw dần dần tuyệt chủng. Vị trí của chúng cuối cùng bị thay thế bởi Kronablight, một Exoswarm sinh ra từ Exostrider.</t>
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng toàn bộ thuộc tính&lt;/color&gt; cao hơn.
+Kẻ địch sở hữu khả năng Lông Tức Giận và ba điểm yếu.
+Sau một thời gian chiến đấu, Kronaclaw sẽ bước vào trạng thái Lông Tức Giận, tăng mạnh ATK.
+Điểm yếu I: Một đòn Phản Đòn thành công có thể làm tổn thương mào và cánh của nó, làm suy yếu đòn tấn công và giảm số lượng đạn tầm xa.
+Điểm yếu II: Phá Tần có thể loại bỏ trạng thái Lông Tức Giận và giảm đạn tầm xa của nó.
+Điểm yếu đặc biệt: Khi Kronaclaw đang chịu hiệu ứng Phá Tần - Dịch Chuyển, đánh trúng bằng Phá Tần sẽ làm giảm mạnh kháng toàn bộ thuộc tính của nó.
+Một loài mãnh long cổ đại đã tuyệt chủng, được tái sinh từ Buồng Sự Sống Upphaf.
+Trong quá khứ xa xưa, những con mãnh long này từng thống trị bầu trời Lahai-Roi, vương quyền của chúng không bị thách thức kể từ Kỷ Nguyên Đầu Tiên.
+Truyền thuyết kể rằng Kronaclaw là tạo vật của Sol, chia sẻ thị lực thần thánh của Mắt Sol và nhìn thấu mọi thứ trên và dưới Lahai-Roi.
+Nhưng khi cực từ thay đổi và cảnh quan bị biến đổi, loài Kronaclaw dần tuyệt chủng. Vị trí của chúng cuối cùng bị thay thế bởi Kronablight, một Exoswarm sinh ra từ Exostrider.</t>
         </is>
       </c>
     </row>
@@ -32426,7 +32424,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; cao hơn.
 Trong chiến đấu, Glommoth sẽ nhận được Frost Armor, làm tăng Kháng toàn thuộc tính.
 Frost Armor sẽ bị loại bỏ khi Fusion Burst trên nó đạt 3 tầng.
 Điểm yếu: Phá vỡ ngà trái của Glommoth sẽ khiến nó mất một phần bộ kỹ năng.
@@ -32501,9 +32499,9 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Khi bị trúng Kỹ Năng Echoes, Sigillum nhận 1 tầng Off Course, tối đa 5 tầng. Các Echoes cùng tên chỉ kích hoạt hiệu ứng này một lần.
-Mỗi tầng Off Course khiến nó chịu thêm 10% tổng sát thương. Khi đạt 5 tầng, Sigillum chịu thêm 30% tổng sát thương.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
+Khi bị trúng Kỹ Năng Echo, Sigillum nhận 1 tầng Off Course, tối đa 5 tầng. Các Echo cùng tên chỉ kích hoạt hiệu ứng này một lần.
+Mỗi tầng Off Course khiến nó chịu thêm 10% tổng DMG. Khi đạt 5 tầng, Sigillum chịu thêm 30% tổng DMG.
 Giận dữ và nước mắt. Đau khổ và niềm vui. Nỗi buồn và đau đớn. Tất cả được cô đọng cùng tiếng thở dài của nàng vào một tần số vàng.
 Nó ngước nhìn trời, lạc trong những ký ức đã phai mờ theo thời gian. Người lữ khách lạc lối vẫn đang tìm đường về nhà.</t>
         </is>
@@ -32577,10 +32575,10 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Aero DMG&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
-Resonators có thể gây thêm tối đa 2 tầng Tune Strain - Interfered lên Nameless Explorer.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng&lt;/color&gt; &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; &lt;color=HighlightB&gt;cao hơn&lt;/color&gt;.
+Resonator có thể gây thêm tối đa 2 tầng Tune Strain - Interfered lên Nameless Explorer.
 Khi Nameless Explorer đang chịu hiệu ứng Tune Strain - Interfered và bị trúng Tune Break, hắn sẽ nhận thêm 1 tầng Tune Strain - Interfered.
-Mỗi tầng Tune Strain - Interfered khiến hắn chịu thêm 4% tổng sát thương.
+Mỗi tầng Tune Strain - Interfered khiến hắn chịu thêm 4% tổng DMG.
 Trạm không gian rơi xuống như một ngôi sao đang tàn, chôn vùi giấc mơ của một thời đại dưới băng và đất.
 Hắn từng là một trong những kẻ mộng mơ, từng sải bước giữa các vì sao.
 Nhưng giờ đây, hắn lẩn trốn trong bóng tối, bị Void tha hóa.
@@ -32652,9 +32650,9 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
 Một tác phẩm quý giá của Fractsidus.
-Bằng công nghệ của New Federation, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của một Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền nát con mồi thành tro bụi.
+Bằng công nghệ của Liên Bang Mới, chúng đã kết hợp chiếc mũ hình ảnh với bản chất của một Tacet Discord, tạo ra một cỗ máy cưa khủng khiếp có thể xé nát thép và nghiền nát con mồi thành tro bụi.
 Nhưng mọi sự siêu việt đều phải trả giá. Những kẻ đón nhận sản phẩm này đã trở thành nô lệ cho chính thiết kế của mình, chỉ còn lại những cái vỏ rỗng tuếch.</t>
         </is>
       </c>
@@ -32724,7 +32722,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
 Một sản phẩm của Fractsidus. Một thất bại dị dạng bị vứt bỏ vào bóng tối.
 Niềm vui và nỗi buồn, tiếng cười và nước mắt... Tất cả rồi cũng sẽ tìm thấy nấm mồ của mình ở đâu đó, khắc những vết sẹo vào bóng đêm.
 Làm sao để thoát khỏi cái bóng của chính mình? Làm sao đối diện với những gì mình đã trở thành?
@@ -32796,7 +32794,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; trước &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao hơn&lt;/color&gt; trước &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.
 Một sản phẩm của Fractsidus. Một thất bại lỗi bị vứt bỏ vào bóng tối.
 Niềm vui và nỗi buồn, tiếng cười và nước mắt... Tất cả cảm xúc cuối cùng đều tìm thấy nấm mồ của mình ở đâu đó, khắc sâu những vết sẹo trong bóng tối.
 Tại nơi vụ tai nạn của cực lạc xảy ra, bạn không còn phân biệt được tiếng cười với tiếng khóc.</t>
@@ -32867,7 +32865,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; cao hơn.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;Kháng&lt;/color&gt; &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; cao hơn.
 Một sản phẩm của Fractsidus. Một thất bại dị dạng bị vứt bỏ vào bóng tối.
 Niềm vui và nỗi buồn, tiếng cười và nước mắt... Tất cả rồi cũng sẽ tìm thấy nấm mồ của mình ở đâu đó, khắc những vết sẹo vào bóng đêm.
 Nhưng nỗi buồn chẳng bao giờ chạm tới đích, khi bóng tối của số phận vẫn luôn rình rập ngay sau lưng.</t>
@@ -32942,11 +32940,11 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng Spectro DMG&lt;/color&gt; &lt;color=Light&gt;cao hơn&lt;/color&gt;.
 Khi Voidwing Moth thoát khỏi trạng thái Bất Động, nó sẽ luân phiên chuyển đổi giữa các trạng thái: Xòe Cánh, Gập Cánh và Co Rúm.
 Ở trạng thái Xòe Cánh, Vibration Strength của nó giảm nhanh hơn.
-Ở trạng thái Gập Cánh, nó giảm Vibration Strength chậm hơn và chịu ít hơn 30% tổng sát thương.
-Ở trạng thái Co Rúm, nó chịu thêm 50% tổng sát thương.
+Ở trạng thái Gập Cánh, nó giảm Vibration Strength chậm hơn và chịu ít hơn 30% tổng DMG.
+Ở trạng thái Co Rúm, nó chịu thêm 50% tổng DMG.
 Một loài Tacet Discord đặc hữu của Dimmr Plains, thường xuất hiện ở những khu vực bị Voidmatter ô nhiễm nặng. Chúng mang hình dáng loài bướm đêm với đôi cánh tỏa ra các hạt Voidmatter.
 Di chuyển theo bản năng dưới ảnh hưởng của Voidmatter, những sinh vật này từng là đội tiên phong trong cuộc xâm lăng của Aleph-1.
 Dù bản chất hiền lành, một khi bị kích động, chúng sẽ không ngừng truy diệt mục tiêu.</t>
@@ -33019,11 +33017,11 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Kẻ địch này có &lt;color=HighlightB&gt;higher RES&lt;/color&gt; với &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Denia chịu thêm 25% sát thương từ tất cả Trạng Thái Tiêu Cực.
-Cô chịu thêm 30% tổng sát thương trong 15 giây khi bị Frostbind.
-"Một sinh viên Khoa Vật Chất Hư Không tại Startorch Academy. Đồng thời là một kẻ lười biếng chuyên nghiệp, tinh thông nghệ thuật ngủ gật trong giờ học. Dù vậy, cô hầu như không bỏ lỡ sự kiện nào của trường, luôn xuất hiện với nụ cười 'dịu dàng' dành cho mọi người."
-Nhưng tên tuổi, danh tính, Năng Lực Resonance, thậm chí cả những mối quan hệ mà cô từng tuyên bố... tất cả đều là dối trá.
+          <t>Kẻ địch này có &lt;color=HighlightB&gt;kháng cao&lt;/color&gt; với &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Denia chịu thêm 25% DMG từ tất cả Trạng Thái Tiêu Cực.
+Cô chịu thêm 30% tổng DMG trong 15 giây khi bị Frostbind.
+"Một sinh viên Khoa Vật Chất Hư Không tại Học viện Startorch. Đồng thời là một kẻ lười biếng chuyên nghiệp, tinh thông nghệ thuật ngủ gật trong giờ học. Dù vậy, cô hầu như không bỏ lỡ sự kiện nào của trường, luôn xuất hiện với nụ cười 'dịu dàng' dành cho mọi người."
+Nhưng tên tuổi, danh tính, Năng Lực Cộng Hưởng, thậm chí cả những mối quan hệ mà cô từng tuyên bố... tất cả đều là dối trá.
 Giữa ngươi và Keystone giờ chỉ còn một con rối, sinh ra chỉ vì Aleph-1.</t>
         </is>
       </c>
@@ -33089,7 +33087,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Mất 40% HP hiện tại và nhận được 300 Dream Fragments.</t>
+          <t>Mất 40% HP hiện tại và nhận được 300 Mảnh Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33152,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Mất 80% HP hiện tại và nhận được 600 Dream Fragments.</t>
+          <t>Mất 80% HP hiện tại và nhận được 600 Mảnh Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -33219,7 +33217,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Phục hồi 30% HP.</t>
+          <t>Hồi phục 30% HP.</t>
         </is>
       </c>
     </row>
@@ -33349,7 +33347,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Nhận Concerto Metaphor: Yinlin.</t>
+          <t>Nhận được Concerto Metaphor: Yinlin.</t>
         </is>
       </c>
     </row>
@@ -33544,7 +33542,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Nhận Concerto Metaphor: Verina.</t>
+          <t>Nhận được Concerto Metaphor: Verina.</t>
         </is>
       </c>
     </row>
@@ -33739,7 +33737,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Nhận Concerto Metaphor: Yuanwu.</t>
+          <t>Nhận được Concerto Metaphor: Yuanwu.</t>
         </is>
       </c>
     </row>
@@ -33934,7 +33932,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Mất 90% HP hiện tại để nhận 1 Metaphor Cấp 3.</t>
+          <t>Mất 90% HP hiện tại để nhận 1 Ẩn Dụ Cấp 3.</t>
         </is>
       </c>
     </row>
@@ -33999,7 +33997,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Phục hồi toàn bộ HP.</t>
+          <t>Hồi phục toàn bộ HP của bạn.</t>
         </is>
       </c>
     </row>
@@ -34064,7 +34062,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -34129,7 +34127,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
